--- a/artifacts/traceability_reports/source_spec_integrated_reqs.xlsx
+++ b/artifacts/traceability_reports/source_spec_integrated_reqs.xlsx
@@ -9,9 +9,13 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Spec Integrated Requirem" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report Metadata" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Upstream Coverage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirement Presence" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Source Spec Integrated Requirem'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Upstream Coverage'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Requirement Presence'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +23,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0&quot;%&quot;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -62,7 +68,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -72,6 +78,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -149,8 +156,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ReportData" displayName="ReportData" ref="A1:AB315" headerRowCount="1">
-  <autoFilter ref="A1:AB315"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ReportData" displayName="ReportData" ref="A1:AB358" headerRowCount="1">
+  <autoFilter ref="A1:AB358"/>
   <tableColumns count="28">
     <tableColumn id="1" name="id"/>
     <tableColumn id="2" name="source_req_id"/>
@@ -180,6 +187,51 @@
     <tableColumn id="26" name="ingestion_id"/>
     <tableColumn id="27" name="req_class"/>
     <tableColumn id="28" name="classification"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ReportData2" displayName="ReportData2" ref="A1:P12" headerRowCount="1">
+  <autoFilter ref="A1:P12"/>
+  <tableColumns count="16">
+    <tableColumn id="1" name="covering_level"/>
+    <tableColumn id="2" name="covering_block"/>
+    <tableColumn id="3" name="covered_upstream_level"/>
+    <tableColumn id="4" name="covered_upstream_block"/>
+    <tableColumn id="5" name="denominator_scope"/>
+    <tableColumn id="6" name="covered_unique_upstream_requirements"/>
+    <tableColumn id="7" name="total_unique_upstream_requirements"/>
+    <tableColumn id="8" name="uncovered_upstream_requirements"/>
+    <tableColumn id="9" name="coverage_percentage"/>
+    <tableColumn id="10" name="coverage_status"/>
+    <tableColumn id="11" name="coverage_basis"/>
+    <tableColumn id="12" name="covered_upstream_requirement_ids"/>
+    <tableColumn id="13" name="uncovered_upstream_requirement_ids"/>
+    <tableColumn id="14" name="snapshot_id"/>
+    <tableColumn id="15" name="covering_node_id"/>
+    <tableColumn id="16" name="covered_upstream_node_id"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ReportData3" displayName="ReportData3" ref="A1:K2" headerRowCount="1">
+  <autoFilter ref="A1:K2"/>
+  <tableColumns count="11">
+    <tableColumn id="1" name="hierarchy_level"/>
+    <tableColumn id="2" name="block"/>
+    <tableColumn id="3" name="scope"/>
+    <tableColumn id="4" name="expected_requirements"/>
+    <tableColumn id="5" name="represented_requirements"/>
+    <tableColumn id="6" name="missing_requirements"/>
+    <tableColumn id="7" name="presence_percentage"/>
+    <tableColumn id="8" name="presence_status"/>
+    <tableColumn id="9" name="coverage_basis"/>
+    <tableColumn id="10" name="missing_requirement_ids"/>
+    <tableColumn id="11" name="snapshot_id"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -474,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB315"/>
+  <dimension ref="A1:AB358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -26785,6 +26837,3532 @@
       <c r="AA315" t="inlineStr"/>
       <c r="AB315" t="inlineStr"/>
     </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_015</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_015</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr"/>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>When the user selects the ECG, BIA, the wave velocity mode or the ppg ioff calibration, the device Shall go to WAIT_SU state.</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr"/>
+      <c r="H316" t="inlineStr"/>
+      <c r="I316" t="inlineStr"/>
+      <c r="J316" t="inlineStr"/>
+      <c r="K316" t="inlineStr"/>
+      <c r="L316" t="inlineStr"/>
+      <c r="M316" t="inlineStr"/>
+      <c r="N316" t="inlineStr"/>
+      <c r="O316" t="inlineStr"/>
+      <c r="P316" t="inlineStr"/>
+      <c r="Q316" t="inlineStr"/>
+      <c r="R316" t="inlineStr"/>
+      <c r="S316" t="inlineStr"/>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_015</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V316" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W316" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="X316" t="inlineStr">
+        <is>
+          <t>p060:l6</t>
+        </is>
+      </c>
+      <c r="Y316" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z316" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB316" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_020</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_020</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr"/>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>When DEVICE_FSM FSM is in WAIT_SU state, if IMP_EN (IMP_CTRL register [0]) is equal to 1 and BIA_SEL (DEVICE_CONFIG_CHANNEL register [2]) is equal to 1, 15ms after the falling of O_PD_IMP, the O_RST_IMP shall go low.</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr"/>
+      <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr"/>
+      <c r="J317" t="inlineStr"/>
+      <c r="K317" t="inlineStr"/>
+      <c r="L317" t="inlineStr"/>
+      <c r="M317" t="inlineStr"/>
+      <c r="N317" t="inlineStr"/>
+      <c r="O317" t="inlineStr"/>
+      <c r="P317" t="inlineStr"/>
+      <c r="Q317" t="inlineStr"/>
+      <c r="R317" t="inlineStr"/>
+      <c r="S317" t="inlineStr"/>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_020</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W317" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="X317" t="inlineStr">
+        <is>
+          <t>p061:l2</t>
+        </is>
+      </c>
+      <c r="Y317" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z317" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB317" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_022</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_022</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr"/>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>When DEVICE_FSM FSM is in WAIT_SU state, if IMP_EN (IMP_CTRL register [0]) is equal to 1 and BIA_SEL (DEVICE_CONFIG_CHANNEL register [2]) is equal to 1; 30ms after the falling of O_RST_IMP, O_RSTI_IMP shall go low.</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr"/>
+      <c r="H318" t="inlineStr"/>
+      <c r="I318" t="inlineStr"/>
+      <c r="J318" t="inlineStr"/>
+      <c r="K318" t="inlineStr"/>
+      <c r="L318" t="inlineStr"/>
+      <c r="M318" t="inlineStr"/>
+      <c r="N318" t="inlineStr"/>
+      <c r="O318" t="inlineStr"/>
+      <c r="P318" t="inlineStr"/>
+      <c r="Q318" t="inlineStr"/>
+      <c r="R318" t="inlineStr"/>
+      <c r="S318" t="inlineStr"/>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_022</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W318" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="X318" t="inlineStr">
+        <is>
+          <t>p061:l14</t>
+        </is>
+      </c>
+      <c r="Y318" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z318" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB318" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_027</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_027</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr"/>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr"/>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>When DEVICE_FSM FSM is in IDLE STATE (main_controller_status_register (DEVICE_STATUS_REG register [2:0]) is equal to 0x02) if IMP_EN (IMP_CTRL register [0]) is set to 1 and BIA_SEL (DEVICE_CONFIG_CHANNEL [2]) is set to 1, after WAIT_SU the device_fsm shall go in OPERATIVE (DEVICE_STATUS_REG register [2:0] is equal to 0x04).</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr"/>
+      <c r="H319" t="inlineStr"/>
+      <c r="I319" t="inlineStr"/>
+      <c r="J319" t="inlineStr"/>
+      <c r="K319" t="inlineStr"/>
+      <c r="L319" t="inlineStr"/>
+      <c r="M319" t="inlineStr"/>
+      <c r="N319" t="inlineStr"/>
+      <c r="O319" t="inlineStr"/>
+      <c r="P319" t="inlineStr"/>
+      <c r="Q319" t="inlineStr"/>
+      <c r="R319" t="inlineStr"/>
+      <c r="S319" t="inlineStr"/>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_027</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W319" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="X319" t="inlineStr">
+        <is>
+          <t>p062:l22</t>
+        </is>
+      </c>
+      <c r="Y319" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z319" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB319" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_4034</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_4034</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr"/>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Every Time a new measurement cycle starts (DEVICE FSM goes in OPERATIVE from another state), the o_irq_start_measurement shall be set to 1 for at least 1 clock cycle</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr"/>
+      <c r="H320" t="inlineStr"/>
+      <c r="I320" t="inlineStr"/>
+      <c r="J320" t="inlineStr"/>
+      <c r="K320" t="inlineStr"/>
+      <c r="L320" t="inlineStr"/>
+      <c r="M320" t="inlineStr"/>
+      <c r="N320" t="inlineStr"/>
+      <c r="O320" t="inlineStr"/>
+      <c r="P320" t="inlineStr"/>
+      <c r="Q320" t="inlineStr"/>
+      <c r="R320" t="inlineStr"/>
+      <c r="S320" t="inlineStr"/>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_4034</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W320" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="X320" t="inlineStr">
+        <is>
+          <t>p063:l36</t>
+        </is>
+      </c>
+      <c r="Y320" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z320" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB320" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_040</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_040</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr"/>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>When the ELAB_FSM is in BIA State (Check ELAB_STATUS_REG), the ADC_Mux (o_adc_mux_biochannel on digital top) output shall be set equal to 011, 100, 101 or 110.</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr"/>
+      <c r="H321" t="inlineStr"/>
+      <c r="I321" t="inlineStr"/>
+      <c r="J321" t="inlineStr"/>
+      <c r="K321" t="inlineStr"/>
+      <c r="L321" t="inlineStr"/>
+      <c r="M321" t="inlineStr"/>
+      <c r="N321" t="inlineStr"/>
+      <c r="O321" t="inlineStr"/>
+      <c r="P321" t="inlineStr"/>
+      <c r="Q321" t="inlineStr"/>
+      <c r="R321" t="inlineStr"/>
+      <c r="S321" t="inlineStr"/>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_040</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W321" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="X321" t="inlineStr">
+        <is>
+          <t>p064:l31</t>
+        </is>
+      </c>
+      <c r="Y321" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z321" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB321" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_3130</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_3130</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr"/>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>When the wave velocity mode and the ppg ioff calibration are selected, the wave velocity mode shall be performed first.</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr"/>
+      <c r="H322" t="inlineStr"/>
+      <c r="I322" t="inlineStr"/>
+      <c r="J322" t="inlineStr"/>
+      <c r="K322" t="inlineStr"/>
+      <c r="L322" t="inlineStr"/>
+      <c r="M322" t="inlineStr"/>
+      <c r="N322" t="inlineStr"/>
+      <c r="O322" t="inlineStr"/>
+      <c r="P322" t="inlineStr"/>
+      <c r="Q322" t="inlineStr"/>
+      <c r="R322" t="inlineStr"/>
+      <c r="S322" t="inlineStr"/>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_3130</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W322" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="X322" t="inlineStr">
+        <is>
+          <t>p065:l11</t>
+        </is>
+      </c>
+      <c r="Y322" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z322" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB322" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_3131</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_3131</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr"/>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>When the ppg ioff calibration is selected and device fsm is in WAIT_SU State, the Elab FSM shall go into the Timer Buffer state and then PPG IOFF CALIB state.</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr"/>
+      <c r="H323" t="inlineStr"/>
+      <c r="I323" t="inlineStr"/>
+      <c r="J323" t="inlineStr"/>
+      <c r="K323" t="inlineStr"/>
+      <c r="L323" t="inlineStr"/>
+      <c r="M323" t="inlineStr"/>
+      <c r="N323" t="inlineStr"/>
+      <c r="O323" t="inlineStr"/>
+      <c r="P323" t="inlineStr"/>
+      <c r="Q323" t="inlineStr"/>
+      <c r="R323" t="inlineStr"/>
+      <c r="S323" t="inlineStr"/>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_3131</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W323" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="X323" t="inlineStr">
+        <is>
+          <t>p065:l14</t>
+        </is>
+      </c>
+      <c r="Y323" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z323" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB323" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_043</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_043</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr"/>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>The ADC_PHGEN shall work at 16 MHz clock frequency.</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr"/>
+      <c r="H324" t="inlineStr"/>
+      <c r="I324" t="inlineStr"/>
+      <c r="J324" t="inlineStr"/>
+      <c r="K324" t="inlineStr"/>
+      <c r="L324" t="inlineStr"/>
+      <c r="M324" t="inlineStr"/>
+      <c r="N324" t="inlineStr"/>
+      <c r="O324" t="inlineStr"/>
+      <c r="P324" t="inlineStr"/>
+      <c r="Q324" t="inlineStr"/>
+      <c r="R324" t="inlineStr"/>
+      <c r="S324" t="inlineStr"/>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_043</t>
+        </is>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W324" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="X324" t="inlineStr">
+        <is>
+          <t>p069:l16</t>
+        </is>
+      </c>
+      <c r="Y324" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z324" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>refines</t>
+        </is>
+      </c>
+      <c r="AB324" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_048</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_048</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr"/>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>When the i_reset_end_calibration , i_do_calibration and i_mode_operation are set to 1, the o_end_cal_phase shall be set to 0.</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr"/>
+      <c r="H325" t="inlineStr"/>
+      <c r="I325" t="inlineStr"/>
+      <c r="J325" t="inlineStr"/>
+      <c r="K325" t="inlineStr"/>
+      <c r="L325" t="inlineStr"/>
+      <c r="M325" t="inlineStr"/>
+      <c r="N325" t="inlineStr"/>
+      <c r="O325" t="inlineStr"/>
+      <c r="P325" t="inlineStr"/>
+      <c r="Q325" t="inlineStr"/>
+      <c r="R325" t="inlineStr"/>
+      <c r="S325" t="inlineStr"/>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_048</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V325" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W325" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="X325" t="inlineStr">
+        <is>
+          <t>p070:l7</t>
+        </is>
+      </c>
+      <c r="Y325" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z325" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB325" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_6059</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_6059</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr"/>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>I_noise shall be set to 0 during the ADC calibration.</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr"/>
+      <c r="H326" t="inlineStr"/>
+      <c r="I326" t="inlineStr"/>
+      <c r="J326" t="inlineStr"/>
+      <c r="K326" t="inlineStr"/>
+      <c r="L326" t="inlineStr"/>
+      <c r="M326" t="inlineStr"/>
+      <c r="N326" t="inlineStr"/>
+      <c r="O326" t="inlineStr"/>
+      <c r="P326" t="inlineStr"/>
+      <c r="Q326" t="inlineStr"/>
+      <c r="R326" t="inlineStr"/>
+      <c r="S326" t="inlineStr"/>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_6059</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V326" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W326" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="X326" t="inlineStr">
+        <is>
+          <t>p071:l10</t>
+        </is>
+      </c>
+      <c r="Y326" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z326" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB326" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_072</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_072</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr"/>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>When the i_hc_en is set to 1 and i_imp_en is set to 0 and i_n_ecg_channel is equal to 1, ECG0 shall be active so the o_pd_hc2 shall go low and counter shall be work.</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr"/>
+      <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr"/>
+      <c r="J327" t="inlineStr"/>
+      <c r="K327" t="inlineStr"/>
+      <c r="L327" t="inlineStr"/>
+      <c r="M327" t="inlineStr"/>
+      <c r="N327" t="inlineStr"/>
+      <c r="O327" t="inlineStr"/>
+      <c r="P327" t="inlineStr"/>
+      <c r="Q327" t="inlineStr"/>
+      <c r="R327" t="inlineStr"/>
+      <c r="S327" t="inlineStr"/>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_072</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W327" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="X327" t="inlineStr">
+        <is>
+          <t>p074:l8</t>
+        </is>
+      </c>
+      <c r="Y327" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z327" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB327" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_075</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_075</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr"/>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>The counter that defines the timing during the start-up phase shall work at 32KHz.</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr"/>
+      <c r="H328" t="inlineStr"/>
+      <c r="I328" t="inlineStr"/>
+      <c r="J328" t="inlineStr"/>
+      <c r="K328" t="inlineStr"/>
+      <c r="L328" t="inlineStr"/>
+      <c r="M328" t="inlineStr"/>
+      <c r="N328" t="inlineStr"/>
+      <c r="O328" t="inlineStr"/>
+      <c r="P328" t="inlineStr"/>
+      <c r="Q328" t="inlineStr"/>
+      <c r="R328" t="inlineStr"/>
+      <c r="S328" t="inlineStr"/>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_075</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V328" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W328" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="X328" t="inlineStr">
+        <is>
+          <t>p074:l19</t>
+        </is>
+      </c>
+      <c r="Y328" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z328" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA328" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB328" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_076</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_076</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr"/>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>15ms after that the o_pd_hc2 is gone low, the o_rst_hc2 shall go low.</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr"/>
+      <c r="H329" t="inlineStr"/>
+      <c r="I329" t="inlineStr"/>
+      <c r="J329" t="inlineStr"/>
+      <c r="K329" t="inlineStr"/>
+      <c r="L329" t="inlineStr"/>
+      <c r="M329" t="inlineStr"/>
+      <c r="N329" t="inlineStr"/>
+      <c r="O329" t="inlineStr"/>
+      <c r="P329" t="inlineStr"/>
+      <c r="Q329" t="inlineStr"/>
+      <c r="R329" t="inlineStr"/>
+      <c r="S329" t="inlineStr"/>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_076</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W329" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="X329" t="inlineStr">
+        <is>
+          <t>p074:l21</t>
+        </is>
+      </c>
+      <c r="Y329" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z329" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA329" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB329" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_5080</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_5080</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr"/>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr"/>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>i_rst_async_ecg Shall be used only when the Device FSM is in SLEEP or Operative State.</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr"/>
+      <c r="H330" t="inlineStr"/>
+      <c r="I330" t="inlineStr"/>
+      <c r="J330" t="inlineStr"/>
+      <c r="K330" t="inlineStr"/>
+      <c r="L330" t="inlineStr"/>
+      <c r="M330" t="inlineStr"/>
+      <c r="N330" t="inlineStr"/>
+      <c r="O330" t="inlineStr"/>
+      <c r="P330" t="inlineStr"/>
+      <c r="Q330" t="inlineStr"/>
+      <c r="R330" t="inlineStr"/>
+      <c r="S330" t="inlineStr"/>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_5080</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V330" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W330" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="X330" t="inlineStr">
+        <is>
+          <t>p075:l10</t>
+        </is>
+      </c>
+      <c r="Y330" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z330" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB330" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_081</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_081</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr"/>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>When i_imp_en signal is equal to 1, the o_pd_imp_from_bia shall be go low.</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr"/>
+      <c r="H331" t="inlineStr"/>
+      <c r="I331" t="inlineStr"/>
+      <c r="J331" t="inlineStr"/>
+      <c r="K331" t="inlineStr"/>
+      <c r="L331" t="inlineStr"/>
+      <c r="M331" t="inlineStr"/>
+      <c r="N331" t="inlineStr"/>
+      <c r="O331" t="inlineStr"/>
+      <c r="P331" t="inlineStr"/>
+      <c r="Q331" t="inlineStr"/>
+      <c r="R331" t="inlineStr"/>
+      <c r="S331" t="inlineStr"/>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_081</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W331" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="X331" t="inlineStr">
+        <is>
+          <t>p078:l10</t>
+        </is>
+      </c>
+      <c r="Y331" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z331" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB331" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_084</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_084</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr"/>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>At least 15ms after the falling of o_pd_imp_from_bia, the o_rst_imp shall go low.</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr"/>
+      <c r="H332" t="inlineStr"/>
+      <c r="I332" t="inlineStr"/>
+      <c r="J332" t="inlineStr"/>
+      <c r="K332" t="inlineStr"/>
+      <c r="L332" t="inlineStr"/>
+      <c r="M332" t="inlineStr"/>
+      <c r="N332" t="inlineStr"/>
+      <c r="O332" t="inlineStr"/>
+      <c r="P332" t="inlineStr"/>
+      <c r="Q332" t="inlineStr"/>
+      <c r="R332" t="inlineStr"/>
+      <c r="S332" t="inlineStr"/>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_084</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V332" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W332" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="X332" t="inlineStr">
+        <is>
+          <t>p078:l20</t>
+        </is>
+      </c>
+      <c r="Y332" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z332" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB332" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_086</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_086</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr"/>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr"/>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>30ms after the falling of o_rst_imp, o_rsti_imp shall go low.</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr"/>
+      <c r="H333" t="inlineStr"/>
+      <c r="I333" t="inlineStr"/>
+      <c r="J333" t="inlineStr"/>
+      <c r="K333" t="inlineStr"/>
+      <c r="L333" t="inlineStr"/>
+      <c r="M333" t="inlineStr"/>
+      <c r="N333" t="inlineStr"/>
+      <c r="O333" t="inlineStr"/>
+      <c r="P333" t="inlineStr"/>
+      <c r="Q333" t="inlineStr"/>
+      <c r="R333" t="inlineStr"/>
+      <c r="S333" t="inlineStr"/>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_086</t>
+        </is>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W333" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="X333" t="inlineStr">
+        <is>
+          <t>p078:l26</t>
+        </is>
+      </c>
+      <c r="Y333" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z333" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA333" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB333" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_5091</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_5091</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr"/>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>i_rst_async_bia shall be used only when Device FSM is in OPERATIVE or SLEEP state.</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr"/>
+      <c r="H334" t="inlineStr"/>
+      <c r="I334" t="inlineStr"/>
+      <c r="J334" t="inlineStr"/>
+      <c r="K334" t="inlineStr"/>
+      <c r="L334" t="inlineStr"/>
+      <c r="M334" t="inlineStr"/>
+      <c r="N334" t="inlineStr"/>
+      <c r="O334" t="inlineStr"/>
+      <c r="P334" t="inlineStr"/>
+      <c r="Q334" t="inlineStr"/>
+      <c r="R334" t="inlineStr"/>
+      <c r="S334" t="inlineStr"/>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_5091</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V334" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W334" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="X334" t="inlineStr">
+        <is>
+          <t>p080:l8</t>
+        </is>
+      </c>
+      <c r="Y334" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z334" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA334" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB334" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_090</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_090</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr"/>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr"/>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>The gsr_on shall set high at least 300us before the start of the sampling.</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr"/>
+      <c r="H335" t="inlineStr"/>
+      <c r="I335" t="inlineStr"/>
+      <c r="J335" t="inlineStr"/>
+      <c r="K335" t="inlineStr"/>
+      <c r="L335" t="inlineStr"/>
+      <c r="M335" t="inlineStr"/>
+      <c r="N335" t="inlineStr"/>
+      <c r="O335" t="inlineStr"/>
+      <c r="P335" t="inlineStr"/>
+      <c r="Q335" t="inlineStr"/>
+      <c r="R335" t="inlineStr"/>
+      <c r="S335" t="inlineStr"/>
+      <c r="T335" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_090</t>
+        </is>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V335" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W335" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="X335" t="inlineStr">
+        <is>
+          <t>p081:l16</t>
+        </is>
+      </c>
+      <c r="Y335" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z335" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA335" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB335" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_300</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_300</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr"/>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>When the rstn_i is asserted low, the PPG FSM shall return in Reset state immediately.</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr"/>
+      <c r="H336" t="inlineStr"/>
+      <c r="I336" t="inlineStr"/>
+      <c r="J336" t="inlineStr"/>
+      <c r="K336" t="inlineStr"/>
+      <c r="L336" t="inlineStr"/>
+      <c r="M336" t="inlineStr"/>
+      <c r="N336" t="inlineStr"/>
+      <c r="O336" t="inlineStr"/>
+      <c r="P336" t="inlineStr"/>
+      <c r="Q336" t="inlineStr"/>
+      <c r="R336" t="inlineStr"/>
+      <c r="S336" t="inlineStr"/>
+      <c r="T336" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_300</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V336" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W336" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="X336" t="inlineStr">
+        <is>
+          <t>p089:l17</t>
+        </is>
+      </c>
+      <c r="Y336" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z336" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA336" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB336" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_097</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_097</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr"/>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>When in Reset state, if the rstn_i is de-asserted , i_wave_velocity_mode is and the i_start_ppg_fsm is high, if i_ID_Frame is equal to 0 or two successively frame have two different i_rx_ch_frame , then the PPG FSM shall go to ALC Compensation state.</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr"/>
+      <c r="H337" t="inlineStr"/>
+      <c r="I337" t="inlineStr"/>
+      <c r="J337" t="inlineStr"/>
+      <c r="K337" t="inlineStr"/>
+      <c r="L337" t="inlineStr"/>
+      <c r="M337" t="inlineStr"/>
+      <c r="N337" t="inlineStr"/>
+      <c r="O337" t="inlineStr"/>
+      <c r="P337" t="inlineStr"/>
+      <c r="Q337" t="inlineStr"/>
+      <c r="R337" t="inlineStr"/>
+      <c r="S337" t="inlineStr"/>
+      <c r="T337" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_097</t>
+        </is>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V337" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W337" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="X337" t="inlineStr">
+        <is>
+          <t>p089:l24</t>
+        </is>
+      </c>
+      <c r="Y337" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z337" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA337" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB337" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_1105</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_1105</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr"/>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>If no multiple frame is selected (i_frame_repetition in ppg_fsm set to 0), when Tx Preset falls from 1 to 0, also the en_tx shall pass from 1 to 0.</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr"/>
+      <c r="H338" t="inlineStr"/>
+      <c r="I338" t="inlineStr"/>
+      <c r="J338" t="inlineStr"/>
+      <c r="K338" t="inlineStr"/>
+      <c r="L338" t="inlineStr"/>
+      <c r="M338" t="inlineStr"/>
+      <c r="N338" t="inlineStr"/>
+      <c r="O338" t="inlineStr"/>
+      <c r="P338" t="inlineStr"/>
+      <c r="Q338" t="inlineStr"/>
+      <c r="R338" t="inlineStr"/>
+      <c r="S338" t="inlineStr"/>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_1105</t>
+        </is>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V338" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W338" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="X338" t="inlineStr">
+        <is>
+          <t>p091:l7</t>
+        </is>
+      </c>
+      <c r="Y338" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z338" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA338" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB338" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_107</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_107</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr"/>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>When in Measurement state, after the wait at least of the TX_ledset time related to the frame that is being executed. (TX_LEDSET_FRAME {n}]), the o_start_adc signal shall be set high.</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr"/>
+      <c r="H339" t="inlineStr"/>
+      <c r="I339" t="inlineStr"/>
+      <c r="J339" t="inlineStr"/>
+      <c r="K339" t="inlineStr"/>
+      <c r="L339" t="inlineStr"/>
+      <c r="M339" t="inlineStr"/>
+      <c r="N339" t="inlineStr"/>
+      <c r="O339" t="inlineStr"/>
+      <c r="P339" t="inlineStr"/>
+      <c r="Q339" t="inlineStr"/>
+      <c r="R339" t="inlineStr"/>
+      <c r="S339" t="inlineStr"/>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_107</t>
+        </is>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V339" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W339" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="X339" t="inlineStr">
+        <is>
+          <t>p091:l25</t>
+        </is>
+      </c>
+      <c r="Y339" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z339" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB339" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_1118</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_1118</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr"/>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Nm0 shall be the result of average on 8 acquired samples.</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr"/>
+      <c r="H340" t="inlineStr"/>
+      <c r="I340" t="inlineStr"/>
+      <c r="J340" t="inlineStr"/>
+      <c r="K340" t="inlineStr"/>
+      <c r="L340" t="inlineStr"/>
+      <c r="M340" t="inlineStr"/>
+      <c r="N340" t="inlineStr"/>
+      <c r="O340" t="inlineStr"/>
+      <c r="P340" t="inlineStr"/>
+      <c r="Q340" t="inlineStr"/>
+      <c r="R340" t="inlineStr"/>
+      <c r="S340" t="inlineStr"/>
+      <c r="T340" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_1118</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V340" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W340" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="X340" t="inlineStr">
+        <is>
+          <t>p093:l6</t>
+        </is>
+      </c>
+      <c r="Y340" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z340" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA340" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB340" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_1119</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_1119</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr"/>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Nm1 shall be the result of average on 8 acquired samples.</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr"/>
+      <c r="H341" t="inlineStr"/>
+      <c r="I341" t="inlineStr"/>
+      <c r="J341" t="inlineStr"/>
+      <c r="K341" t="inlineStr"/>
+      <c r="L341" t="inlineStr"/>
+      <c r="M341" t="inlineStr"/>
+      <c r="N341" t="inlineStr"/>
+      <c r="O341" t="inlineStr"/>
+      <c r="P341" t="inlineStr"/>
+      <c r="Q341" t="inlineStr"/>
+      <c r="R341" t="inlineStr"/>
+      <c r="S341" t="inlineStr"/>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_1119</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V341" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W341" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="X341" t="inlineStr">
+        <is>
+          <t>p093:l8</t>
+        </is>
+      </c>
+      <c r="Y341" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z341" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA341" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB341" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_8116</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_8116</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr"/>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>i_n_start_case shall be lesser or equal than i_Nmax_to_reg.</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr"/>
+      <c r="H342" t="inlineStr"/>
+      <c r="I342" t="inlineStr"/>
+      <c r="J342" t="inlineStr"/>
+      <c r="K342" t="inlineStr"/>
+      <c r="L342" t="inlineStr"/>
+      <c r="M342" t="inlineStr"/>
+      <c r="N342" t="inlineStr"/>
+      <c r="O342" t="inlineStr"/>
+      <c r="P342" t="inlineStr"/>
+      <c r="Q342" t="inlineStr"/>
+      <c r="R342" t="inlineStr"/>
+      <c r="S342" t="inlineStr"/>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_8116</t>
+        </is>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V342" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W342" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="X342" t="inlineStr">
+        <is>
+          <t>p096:l17</t>
+        </is>
+      </c>
+      <c r="Y342" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z342" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA342" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB342" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_2117</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_2117</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr"/>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>When the PPG_FSM is in the RX_START_UP state, the o_PD_PGA shall go to 0.</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr"/>
+      <c r="H343" t="inlineStr"/>
+      <c r="I343" t="inlineStr"/>
+      <c r="J343" t="inlineStr"/>
+      <c r="K343" t="inlineStr"/>
+      <c r="L343" t="inlineStr"/>
+      <c r="M343" t="inlineStr"/>
+      <c r="N343" t="inlineStr"/>
+      <c r="O343" t="inlineStr"/>
+      <c r="P343" t="inlineStr"/>
+      <c r="Q343" t="inlineStr"/>
+      <c r="R343" t="inlineStr"/>
+      <c r="S343" t="inlineStr"/>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_2117</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V343" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W343" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="X343" t="inlineStr">
+        <is>
+          <t>p096:l19</t>
+        </is>
+      </c>
+      <c r="Y343" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z343" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA343" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB343" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_121</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_121</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr"/>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr"/>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Nmax shall be a value between 1 and 15 configurable by user.</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr"/>
+      <c r="H344" t="inlineStr"/>
+      <c r="I344" t="inlineStr"/>
+      <c r="J344" t="inlineStr"/>
+      <c r="K344" t="inlineStr"/>
+      <c r="L344" t="inlineStr"/>
+      <c r="M344" t="inlineStr"/>
+      <c r="N344" t="inlineStr"/>
+      <c r="O344" t="inlineStr"/>
+      <c r="P344" t="inlineStr"/>
+      <c r="Q344" t="inlineStr"/>
+      <c r="R344" t="inlineStr"/>
+      <c r="S344" t="inlineStr"/>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_121</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V344" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W344" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="X344" t="inlineStr">
+        <is>
+          <t>p098:l8</t>
+        </is>
+      </c>
+      <c r="Y344" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z344" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB344" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_122</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_122</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr"/>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>When o_ TX_Vref is equal to i_Nmax_to_reg (N_MAX (DIGITAL_RAMP_CONFIG_PARAM_1 register [3:0])), o_rising_ramp_end shall go high.</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr"/>
+      <c r="H345" t="inlineStr"/>
+      <c r="I345" t="inlineStr"/>
+      <c r="J345" t="inlineStr"/>
+      <c r="K345" t="inlineStr"/>
+      <c r="L345" t="inlineStr"/>
+      <c r="M345" t="inlineStr"/>
+      <c r="N345" t="inlineStr"/>
+      <c r="O345" t="inlineStr"/>
+      <c r="P345" t="inlineStr"/>
+      <c r="Q345" t="inlineStr"/>
+      <c r="R345" t="inlineStr"/>
+      <c r="S345" t="inlineStr"/>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_122</t>
+        </is>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V345" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W345" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="X345" t="inlineStr">
+        <is>
+          <t>p098:l10</t>
+        </is>
+      </c>
+      <c r="Y345" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z345" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB345" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_123</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_123</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr"/>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>When o_Tx_Vref is equal to 0 during the falling and the rising ramp is ended (o_rising_ramp_end ==0), o_falling_ramp_end shall go high.</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr"/>
+      <c r="H346" t="inlineStr"/>
+      <c r="I346" t="inlineStr"/>
+      <c r="J346" t="inlineStr"/>
+      <c r="K346" t="inlineStr"/>
+      <c r="L346" t="inlineStr"/>
+      <c r="M346" t="inlineStr"/>
+      <c r="N346" t="inlineStr"/>
+      <c r="O346" t="inlineStr"/>
+      <c r="P346" t="inlineStr"/>
+      <c r="Q346" t="inlineStr"/>
+      <c r="R346" t="inlineStr"/>
+      <c r="S346" t="inlineStr"/>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_123</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V346" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W346" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="X346" t="inlineStr">
+        <is>
+          <t>p098:l13</t>
+        </is>
+      </c>
+      <c r="Y346" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z346" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA346" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB346" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_124</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_124</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr"/>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>When the rising ramp reaches half its value, o_half_rising_ramp shall go high.</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr"/>
+      <c r="H347" t="inlineStr"/>
+      <c r="I347" t="inlineStr"/>
+      <c r="J347" t="inlineStr"/>
+      <c r="K347" t="inlineStr"/>
+      <c r="L347" t="inlineStr"/>
+      <c r="M347" t="inlineStr"/>
+      <c r="N347" t="inlineStr"/>
+      <c r="O347" t="inlineStr"/>
+      <c r="P347" t="inlineStr"/>
+      <c r="Q347" t="inlineStr"/>
+      <c r="R347" t="inlineStr"/>
+      <c r="S347" t="inlineStr"/>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_124</t>
+        </is>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V347" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W347" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="X347" t="inlineStr">
+        <is>
+          <t>p098:l16</t>
+        </is>
+      </c>
+      <c r="Y347" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z347" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA347" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB347" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_125</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_125</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr"/>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>When i_reset_ramp is high all output shall be down.</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr"/>
+      <c r="H348" t="inlineStr"/>
+      <c r="I348" t="inlineStr"/>
+      <c r="J348" t="inlineStr"/>
+      <c r="K348" t="inlineStr"/>
+      <c r="L348" t="inlineStr"/>
+      <c r="M348" t="inlineStr"/>
+      <c r="N348" t="inlineStr"/>
+      <c r="O348" t="inlineStr"/>
+      <c r="P348" t="inlineStr"/>
+      <c r="Q348" t="inlineStr"/>
+      <c r="R348" t="inlineStr"/>
+      <c r="S348" t="inlineStr"/>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_125</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V348" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W348" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="X348" t="inlineStr">
+        <is>
+          <t>p098:l18</t>
+        </is>
+      </c>
+      <c r="Y348" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z348" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA348" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB348" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_127</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_127</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr"/>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>ALC cycle algorithm shall be done until the set of the last o_w_BTIA_ALC bit.</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr"/>
+      <c r="H349" t="inlineStr"/>
+      <c r="I349" t="inlineStr"/>
+      <c r="J349" t="inlineStr"/>
+      <c r="K349" t="inlineStr"/>
+      <c r="L349" t="inlineStr"/>
+      <c r="M349" t="inlineStr"/>
+      <c r="N349" t="inlineStr"/>
+      <c r="O349" t="inlineStr"/>
+      <c r="P349" t="inlineStr"/>
+      <c r="Q349" t="inlineStr"/>
+      <c r="R349" t="inlineStr"/>
+      <c r="S349" t="inlineStr"/>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_127</t>
+        </is>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V349" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W349" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="X349" t="inlineStr">
+        <is>
+          <t>p102:l10</t>
+        </is>
+      </c>
+      <c r="Y349" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z349" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA349" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB349" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_129</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_129</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr"/>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>When i_ALC_comp_start is set to 1 and the o_BTIA_ALC (ALC Compensation) change is value, after a configurable time T1 (PPG_ALC_CONFIG_PARAM_1 register [3:0]), o_comp_rx_ck shall be high.</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr"/>
+      <c r="H350" t="inlineStr"/>
+      <c r="I350" t="inlineStr"/>
+      <c r="J350" t="inlineStr"/>
+      <c r="K350" t="inlineStr"/>
+      <c r="L350" t="inlineStr"/>
+      <c r="M350" t="inlineStr"/>
+      <c r="N350" t="inlineStr"/>
+      <c r="O350" t="inlineStr"/>
+      <c r="P350" t="inlineStr"/>
+      <c r="Q350" t="inlineStr"/>
+      <c r="R350" t="inlineStr"/>
+      <c r="S350" t="inlineStr"/>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_129</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V350" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W350" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="X350" t="inlineStr">
+        <is>
+          <t>p102:l19</t>
+        </is>
+      </c>
+      <c r="Y350" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z350" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA350" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB350" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_132</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_132</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr"/>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>After T1+T2 (PPG_ALC_CONFIG_PARAM_2 register [1:0]), if o_BTIA_gain (2:0) &lt; i_gain_max_set (PPG_ALC_CONFIG_PARAM_2 register [7:5]), during ALC_COMPENSATION state of PPG fsm with o_end_compensation set to 0, o_BTIA_gain increase its value of 1. Instead, if o_BTIA_gain 2:0) &gt;= i_gain_max_set (PPG_ALC_CONFIG_PARAM_2 register [7:5]), o_BTIA_gain shall remain at its old value.</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr"/>
+      <c r="H351" t="inlineStr"/>
+      <c r="I351" t="inlineStr"/>
+      <c r="J351" t="inlineStr"/>
+      <c r="K351" t="inlineStr"/>
+      <c r="L351" t="inlineStr"/>
+      <c r="M351" t="inlineStr"/>
+      <c r="N351" t="inlineStr"/>
+      <c r="O351" t="inlineStr"/>
+      <c r="P351" t="inlineStr"/>
+      <c r="Q351" t="inlineStr"/>
+      <c r="R351" t="inlineStr"/>
+      <c r="S351" t="inlineStr"/>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_132</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V351" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W351" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="X351" t="inlineStr">
+        <is>
+          <t>p102:l28</t>
+        </is>
+      </c>
+      <c r="Y351" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z351" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA351" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB351" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_133</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_133</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr"/>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Once is set to 1, o_comp_rx_ck shall be set to 0 after a T2+1 clock cycle.</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr"/>
+      <c r="H352" t="inlineStr"/>
+      <c r="I352" t="inlineStr"/>
+      <c r="J352" t="inlineStr"/>
+      <c r="K352" t="inlineStr"/>
+      <c r="L352" t="inlineStr"/>
+      <c r="M352" t="inlineStr"/>
+      <c r="N352" t="inlineStr"/>
+      <c r="O352" t="inlineStr"/>
+      <c r="P352" t="inlineStr"/>
+      <c r="Q352" t="inlineStr"/>
+      <c r="R352" t="inlineStr"/>
+      <c r="S352" t="inlineStr"/>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_133</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V352" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W352" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="X352" t="inlineStr">
+        <is>
+          <t>p103:l2</t>
+        </is>
+      </c>
+      <c r="Y352" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z352" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA352" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB352" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_9116</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_9116</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr"/>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr"/>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>GAIN_START shall be lesser or equal than GAIN_MAX.</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr"/>
+      <c r="H353" t="inlineStr"/>
+      <c r="I353" t="inlineStr"/>
+      <c r="J353" t="inlineStr"/>
+      <c r="K353" t="inlineStr"/>
+      <c r="L353" t="inlineStr"/>
+      <c r="M353" t="inlineStr"/>
+      <c r="N353" t="inlineStr"/>
+      <c r="O353" t="inlineStr"/>
+      <c r="P353" t="inlineStr"/>
+      <c r="Q353" t="inlineStr"/>
+      <c r="R353" t="inlineStr"/>
+      <c r="S353" t="inlineStr"/>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_9116</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V353" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W353" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="X353" t="inlineStr">
+        <is>
+          <t>p103:l4</t>
+        </is>
+      </c>
+      <c r="Y353" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z353" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA353" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB353" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_7135</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_7135</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr"/>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>If the ALC_COARSE (o_w_BTIA_ALC) result is equal to zero, it shall be brought to 1</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr"/>
+      <c r="H354" t="inlineStr"/>
+      <c r="I354" t="inlineStr"/>
+      <c r="J354" t="inlineStr"/>
+      <c r="K354" t="inlineStr"/>
+      <c r="L354" t="inlineStr"/>
+      <c r="M354" t="inlineStr"/>
+      <c r="N354" t="inlineStr"/>
+      <c r="O354" t="inlineStr"/>
+      <c r="P354" t="inlineStr"/>
+      <c r="Q354" t="inlineStr"/>
+      <c r="R354" t="inlineStr"/>
+      <c r="S354" t="inlineStr"/>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_7135</t>
+        </is>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V354" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W354" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="X354" t="inlineStr">
+        <is>
+          <t>p103:l11</t>
+        </is>
+      </c>
+      <c r="Y354" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z354" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA354" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB354" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_1136</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_1136</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr"/>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>After the assertion of i_end_of_conversion a number of times equals to i_n_average_ecg_bia_gsr (in case of ECG, BIA and GSR) or i_n_average_ppg (in case of PPG without frame repetitions) , after at least one clock cycle o_data_result shall be computed and o_write_enable shall rise</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr"/>
+      <c r="H355" t="inlineStr"/>
+      <c r="I355" t="inlineStr"/>
+      <c r="J355" t="inlineStr"/>
+      <c r="K355" t="inlineStr"/>
+      <c r="L355" t="inlineStr"/>
+      <c r="M355" t="inlineStr"/>
+      <c r="N355" t="inlineStr"/>
+      <c r="O355" t="inlineStr"/>
+      <c r="P355" t="inlineStr"/>
+      <c r="Q355" t="inlineStr"/>
+      <c r="R355" t="inlineStr"/>
+      <c r="S355" t="inlineStr"/>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_1136</t>
+        </is>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V355" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W355" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="X355" t="inlineStr">
+        <is>
+          <t>p106:l20</t>
+        </is>
+      </c>
+      <c r="Y355" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z355" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA355" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB355" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_139</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_139</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr"/>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>When a PPG Raw data ( i_data_valid_ppg_adc set to 1) or a PPG_Noise (i_data_valid_noise_ppg_adc set to 1) data is sampled (i_end_of_conversion set to 1) the data shall be accumulated until i_n_average_ppg is not reached.</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr"/>
+      <c r="H356" t="inlineStr"/>
+      <c r="I356" t="inlineStr"/>
+      <c r="J356" t="inlineStr"/>
+      <c r="K356" t="inlineStr"/>
+      <c r="L356" t="inlineStr"/>
+      <c r="M356" t="inlineStr"/>
+      <c r="N356" t="inlineStr"/>
+      <c r="O356" t="inlineStr"/>
+      <c r="P356" t="inlineStr"/>
+      <c r="Q356" t="inlineStr"/>
+      <c r="R356" t="inlineStr"/>
+      <c r="S356" t="inlineStr"/>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_139</t>
+        </is>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V356" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W356" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="X356" t="inlineStr">
+        <is>
+          <t>p107:l15</t>
+        </is>
+      </c>
+      <c r="Y356" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z356" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB356" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_9139</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_9139</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr"/>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>If during the PPG Frame computation, the i_alc_mask (ALC Disabled) is enabled, the final result shall be only the ppg acquisition and the subtraction of the alc data shall not be performed.</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr"/>
+      <c r="H357" t="inlineStr"/>
+      <c r="I357" t="inlineStr"/>
+      <c r="J357" t="inlineStr"/>
+      <c r="K357" t="inlineStr"/>
+      <c r="L357" t="inlineStr"/>
+      <c r="M357" t="inlineStr"/>
+      <c r="N357" t="inlineStr"/>
+      <c r="O357" t="inlineStr"/>
+      <c r="P357" t="inlineStr"/>
+      <c r="Q357" t="inlineStr"/>
+      <c r="R357" t="inlineStr"/>
+      <c r="S357" t="inlineStr"/>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_9139</t>
+        </is>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V357" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W357" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="X357" t="inlineStr">
+        <is>
+          <t>p108:l2</t>
+        </is>
+      </c>
+      <c r="Y357" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z357" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA357" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB357" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_143</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_143</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Supplementary</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr"/>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>When i_end_of_conversion is set to 1 and i_n_average_ecg_bia_gsr (average ecg,bia and gsr) or i_n_average_ppg (Frame_X_Parameter_1) is equal to their limit values, an average operation shall be done and o_write_enable shall be set to 1.</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr"/>
+      <c r="H358" t="inlineStr"/>
+      <c r="I358" t="inlineStr"/>
+      <c r="J358" t="inlineStr"/>
+      <c r="K358" t="inlineStr"/>
+      <c r="L358" t="inlineStr"/>
+      <c r="M358" t="inlineStr"/>
+      <c r="N358" t="inlineStr"/>
+      <c r="O358" t="inlineStr"/>
+      <c r="P358" t="inlineStr"/>
+      <c r="Q358" t="inlineStr"/>
+      <c r="R358" t="inlineStr"/>
+      <c r="S358" t="inlineStr"/>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_143</t>
+        </is>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="V358" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W358" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="X358" t="inlineStr">
+        <is>
+          <t>p108:l5</t>
+        </is>
+      </c>
+      <c r="Y358" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="Z358" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260921_143819</t>
+        </is>
+      </c>
+      <c r="AA358" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB358" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -26835,7 +30413,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05T14:30:20+00:00</t>
+          <t>2026-10-13T18:27:32+00:00</t>
         </is>
       </c>
     </row>
@@ -26847,7 +30425,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>snap-b2e8101b00dc6909feaed885</t>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
         </is>
       </c>
     </row>
@@ -26859,7 +30437,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>b2e8101b00dc6909feaed8858c8391a595fd7fe52538e9b17b233477d99c8a6d</t>
+          <t>0c71eaa9e10d8478c2ac3726113d42cead2cf039a4bd64b4fab7e6c9dc116eac</t>
         </is>
       </c>
     </row>
@@ -26871,7 +30449,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>C:\Users\iannuzza\LOCAL_PROJ\Github_copilot_proj\STBIO_AI\data\canonical\canonical_store.sqlite</t>
+          <t>C:\Users\iannuzza\LOCAL_PROJ\Github_copilot_proj\Deterministic_Reqs_workflow\data\canonical\canonical_store.sqlite</t>
         </is>
       </c>
     </row>
@@ -26883,7 +30461,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>C:\Users\iannuzza\LOCAL_PROJ\Github_copilot_proj\STBIO_AI\artifacts\traceability_reports\source_spec_integrated_reqs.xlsx</t>
+          <t>C:\Users\iannuzza\LOCAL_PROJ\Github_copilot_proj\Deterministic_Reqs_workflow\artifacts\traceability_reports\source_spec_integrated_reqs.xlsx</t>
         </is>
       </c>
     </row>
@@ -26894,7 +30472,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>314</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -26917,7 +30495,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>C:\Users\iannuzza\LOCAL_PROJ\Github_copilot_proj\STBIO_AI\artifacts\stage1_requirements\integrated_requirements.csv</t>
+          <t>C:\Users\iannuzza\LOCAL_PROJ\Github_copilot_proj\Deterministic_Reqs_workflow\artifacts\stage1_requirements\integrated_requirements.csv</t>
         </is>
       </c>
     </row>
@@ -26936,4 +30514,1069 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:P12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="49" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="33" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="31" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>covering_level</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>covering_block</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>covered_upstream_level</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>covered_upstream_block</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>denominator_scope</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>covered_unique_upstream_requirements</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>total_unique_upstream_requirements</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>uncovered_upstream_requirements</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_percentage</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_status</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_basis</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>covered_upstream_requirement_ids</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>uncovered_upstream_requirement_ids</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>snapshot_id</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>covering_node_id</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>covered_upstream_node_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Digital IPOS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Main Controller</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Supplementary specification: IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Entire upstream document</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>166</v>
+      </c>
+      <c r="G2" t="n">
+        <v>166</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>covered</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Unique upstream IDs resolved by central approved Covers contract; not publication gate status</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_002;IPOS_STBIO1_MAIN_CONTROLLER_004;IPOS_STBIO1_MAIN_CONTROLLER_008;IPOS_STBIO1_MAIN_CONTROLLER_009;IPOS_STBIO1_MAIN_CONTROLLER_010;IPOS_STBIO1_MAIN_CONTROLLER_011;IPOS_STBIO1_MAIN_CONTROLLER_015;IPOS_STBIO1_MAIN_CONTROLLER_0152;IPOS_STBIO1_MAIN_CONTROLLER_016;IPOS_STBIO1_MAIN_CONTROLLER_017;IPOS_STBIO1_MAIN_CONTROLLER_018;IPOS_STBIO1_MAIN_CONTROLLER_019;IPOS_STBIO1_MAIN_CONTROLLER_020;IPOS_STBIO1_MAIN_CONTROLLER_021;IPOS_STBIO1_MAIN_CONTROLLER_022;IPOS_STBIO1_MAIN_CONTROLLER_023;IPOS_STBIO1_MAIN_CONTROLLER_024;IPOS_STBIO1_MAIN_CONTROLLER_026;IPOS_STBIO1_MAIN_CONTROLLER_027;IPOS_STBIO1_MAIN_CONTROLLER_028;IPOS_STBIO1_MAIN_CONTROLLER_029;IPOS_STBIO1_MAIN_CONTROLLER_030;IPOS_STBIO1_MAIN_CONTROLLER_031;IPOS_STBIO1_MAIN_CONTROLLER_032;IPOS_STBIO1_MAIN_CONTROLLER_033;IPOS_STBIO1_MAIN_CONTROLLER_034;IPOS_STBIO1_MAIN_CONTROLLER_035;IPOS_STBIO1_MAIN_CONTROLLER_036;IPOS_STBIO1_MAIN_CONTROLLER_037;IPOS_STBIO1_MAIN_CONTROLLER_038;IPOS_STBIO1_MAIN_CONTROLLER_039;IPOS_STBIO1_MAIN_CONTROLLER_040;IPOS_STBIO1_MAIN_CONTROLLER_043;IPOS_STBIO1_MAIN_CONTROLLER_044;IPOS_STBIO1_MAIN_CONTROLLER_045;IPOS_STBIO1_MAIN_CONTROLLER_047;IPOS_STBIO1_MAIN_CONTROLLER_048;IPOS_STBIO1_MAIN_CONTROLLER_049;IPOS_STBIO1_MAIN_CONTROLLER_051;IPOS_STBIO1_MAIN_CONTROLLER_052;IPOS_STBIO1_MAIN_CONTROLLER_053;IPOS_STBIO1_MAIN_CONTROLLER_054;IPOS_STBIO1_MAIN_CONTROLLER_055;IPOS_STBIO1_MAIN_CONTROLLER_058;IPOS_STBIO1_MAIN_CONTROLLER_059;IPOS_STBIO1_MAIN_CONTROLLER_060;IPOS_STBIO1_MAIN_CONTROLLER_061;IPOS_STBIO1_MAIN_CONTROLLER_062;IPOS_STBIO1_MAIN_CONTROLLER_063;IPOS_STBIO1_MAIN_CONTROLLER_064;IPOS_STBIO1_MAIN_CONTROLLER_072;IPOS_STBIO1_MAIN_CONTROLLER_073;IPOS_STBIO1_MAIN_CONTROLLER_074;IPOS_STBIO1_MAIN_CONTROLLER_075;IPOS_STBIO1_MAIN_CONTROLLER_076;IPOS_STBIO1_MAIN_CONTROLLER_077;IPOS_STBIO1_MAIN_CONTROLLER_078;IPOS_STBIO1_MAIN_CONTROLLER_080;IPOS_STBIO1_MAIN_CONTROLLER_081;IPOS_STBIO1_MAIN_CONTROLLER_082;IPOS_STBIO1_MAIN_CONTROLLER_083;IPOS_STBIO1_MAIN_CONTROLLER_084;IPOS_STBIO1_MAIN_CONTROLLER_085;IPOS_STBIO1_MAIN_CONTROLLER_086;IPOS_STBIO1_MAIN_CONTROLLER_087;IPOS_STBIO1_MAIN_CONTROLLER_088;IPOS_STBIO1_MAIN_CONTROLLER_089;IPOS_STBIO1_MAIN_CONTROLLER_090;IPOS_STBIO1_MAIN_CONTROLLER_092;IPOS_STBIO1_MAIN_CONTROLLER_093;IPOS_STBIO1_MAIN_CONTROLLER_094;IPOS_STBIO1_MAIN_CONTROLLER_095;IPOS_STBIO1_MAIN_CONTROLLER_096;IPOS_STBIO1_MAIN_CONTROLLER_097;IPOS_STBIO1_MAIN_CONTROLLER_098;IPOS_STBIO1_MAIN_CONTROLLER_099;IPOS_STBIO1_MAIN_CONTROLLER_100;IPOS_STBIO1_MAIN_CONTROLLER_1004;IPOS_STBIO1_MAIN_CONTROLLER_1005;IPOS_STBIO1_MAIN_CONTROLLER_1007;IPOS_STBIO1_MAIN_CONTROLLER_1008;IPOS_STBIO1_MAIN_CONTROLLER_1009;IPOS_STBIO1_MAIN_CONTROLLER_101;IPOS_STBIO1_MAIN_CONTROLLER_1010;IPOS_STBIO1_MAIN_CONTROLLER_1011;IPOS_STBIO1_MAIN_CONTROLLER_102;IPOS_STBIO1_MAIN_CONTROLLER_103;IPOS_STBIO1_MAIN_CONTROLLER_1034;IPOS_STBIO1_MAIN_CONTROLLER_104;IPOS_STBIO1_MAIN_CONTROLLER_105;IPOS_STBIO1_MAIN_CONTROLLER_106;IPOS_STBIO1_MAIN_CONTROLLER_107;IPOS_STBIO1_MAIN_CONTROLLER_108;IPOS_STBIO1_MAIN_CONTROLLER_109;IPOS_STBIO1_MAIN_CONTROLLER_1095;IPOS_STBIO1_MAIN_CONTROLLER_110;IPOS_STBIO1_MAIN_CONTROLLER_1102;IPOS_STBIO1_MAIN_CONTROLLER_1104;IPOS_STBIO1_MAIN_CONTROLLER_1105;IPOS_STBIO1_MAIN_CONTROLLER_111;IPOS_STBIO1_MAIN_CONTROLLER_1116;IPOS_STBIO1_MAIN_CONTROLLER_1118;IPOS_STBIO1_MAIN_CONTROLLER_1119;IPOS_STBIO1_MAIN_CONTROLLER_112;IPOS_STBIO1_MAIN_CONTROLLER_113;IPOS_STBIO1_MAIN_CONTROLLER_1136;IPOS_STBIO1_MAIN_CONTROLLER_1139;IPOS_STBIO1_MAIN_CONTROLLER_1143;IPOS_STBIO1_MAIN_CONTROLLER_115;IPOS_STBIO1_MAIN_CONTROLLER_118;IPOS_STBIO1_MAIN_CONTROLLER_120;IPOS_STBIO1_MAIN_CONTROLLER_121;IPOS_STBIO1_MAIN_CONTROLLER_122;IPOS_STBIO1_MAIN_CONTROLLER_123;IPOS_STBIO1_MAIN_CONTROLLER_124;IPOS_STBIO1_MAIN_CONTROLLER_125;IPOS_STBIO1_MAIN_CONTROLLER_126;IPOS_STBIO1_MAIN_CONTROLLER_127;IPOS_STBIO1_MAIN_CONTROLLER_128;IPOS_STBIO1_MAIN_CONTROLLER_129;IPOS_STBIO1_MAIN_CONTROLLER_132;IPOS_STBIO1_MAIN_CONTROLLER_133;IPOS_STBIO1_MAIN_CONTROLLER_134;IPOS_STBIO1_MAIN_CONTROLLER_137;IPOS_STBIO1_MAIN_CONTROLLER_138;IPOS_STBIO1_MAIN_CONTROLLER_139;IPOS_STBIO1_MAIN_CONTROLLER_140;IPOS_STBIO1_MAIN_CONTROLLER_143;IPOS_STBIO1_MAIN_CONTROLLER_2117;IPOS_STBIO1_MAIN_CONTROLLER_2143;IPOS_STBIO1_MAIN_CONTROLLER_2144;IPOS_STBIO1_MAIN_CONTROLLER_2145;IPOS_STBIO1_MAIN_CONTROLLER_2146;IPOS_STBIO1_MAIN_CONTROLLER_300;IPOS_STBIO1_MAIN_CONTROLLER_3124;IPOS_STBIO1_MAIN_CONTROLLER_3125;IPOS_STBIO1_MAIN_CONTROLLER_3126;IPOS_STBIO1_MAIN_CONTROLLER_3127;IPOS_STBIO1_MAIN_CONTROLLER_3128;IPOS_STBIO1_MAIN_CONTROLLER_3129;IPOS_STBIO1_MAIN_CONTROLLER_3130;IPOS_STBIO1_MAIN_CONTROLLER_3131;IPOS_STBIO1_MAIN_CONTROLLER_4034;IPOS_STBIO1_MAIN_CONTROLLER_4079;IPOS_STBIO1_MAIN_CONTROLLER_4080;IPOS_STBIO1_MAIN_CONTROLLER_4090;IPOS_STBIO1_MAIN_CONTROLLER_4091;IPOS_STBIO1_MAIN_CONTROLLER_436;IPOS_STBIO1_MAIN_CONTROLLER_5004;IPOS_STBIO1_MAIN_CONTROLLER_5005;IPOS_STBIO1_MAIN_CONTROLLER_5015;IPOS_STBIO1_MAIN_CONTROLLER_5016;IPOS_STBIO1_MAIN_CONTROLLER_5080;IPOS_STBIO1_MAIN_CONTROLLER_5091;IPOS_STBIO1_MAIN_CONTROLLER_5092;IPOS_STBIO1_MAIN_CONTROLLER_6059;IPOS_STBIO1_MAIN_CONTROLLER_6070;IPOS_STBIO1_MAIN_CONTROLLER_6098;IPOS_STBIO1_MAIN_CONTROLLER_6129;IPOS_STBIO1_MAIN_CONTROLLER_7095;IPOS_STBIO1_MAIN_CONTROLLER_7135;IPOS_STBIO1_MAIN_CONTROLLER_728;IPOS_STBIO1_MAIN_CONTROLLER_8106;IPOS_STBIO1_MAIN_CONTROLLER_8116;IPOS_STBIO1_MAIN_CONTROLLER_9116;IPOS_STBIO1_MAIN_CONTROLLER_9139</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Digital_IPOS:main-controller</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>supplementary:ipos_main_ctrl.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DRS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Primary source specification: dds_stbio1.pdf</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Approved source ledger</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>55</v>
+      </c>
+      <c r="G3" t="n">
+        <v>357</v>
+      </c>
+      <c r="H3" t="n">
+        <v>302</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>15.40616246498599</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Unique upstream IDs resolved by central approved Covers contract; not publication gate status</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_0032;DDS_STBIO1_0036;DDS_STBIO1_0116;DDS_STBIO1_0141;DDS_STBIO1_0142;DDS_STBIO1_0143;DDS_STBIO1_0144;DDS_STBIO1_0145;DDS_STBIO1_0146;DDS_STBIO1_0147;DDS_STBIO1_0148;DDS_STBIO1_0149;DDS_STBIO1_0201;DDS_STBIO1_0202;DDS_STBIO1_0203;DDS_STBIO1_0204;DDS_STBIO1_0206;DDS_STBIO1_0207;DDS_STBIO1_0208;DDS_STBIO1_0209;DDS_STBIO1_0210;DDS_STBIO1_0211;DDS_STBIO1_0212;DDS_STBIO1_0213;DDS_STBIO1_0215;DDS_STBIO1_0216;DDS_STBIO1_0217;DDS_STBIO1_0218;DDS_STBIO1_0219;DDS_STBIO1_0220;DDS_STBIO1_0221;DDS_STBIO1_0222;DDS_STBIO1_0223;DDS_STBIO1_0501;DDS_STBIO1_05010;DDS_STBIO1_05011;DDS_STBIO1_0502;DDS_STBIO1_0503;DDS_STBIO1_0504;DDS_STBIO1_0505;DDS_STBIO1_0507;DDS_STBIO1_0508;DDS_STBIO1_0509;DDS_STBIO1_0699;DDS_STBIO1_0700;DDS_STBIO1_0701;DDS_STBIO1_0702;DDS_STBIO1_1114;DDS_STBIO1_1507;DDS_STBIO1_2507;DDS_STBIO1_9004;DDS_STBIO1_9011;DDS_STBIO1_9012;DDS_STBIO1_9013;DDS_STBIO1_9014</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_00000008;DDS_STBIO1_00000102;DDS_STBIO1_00000199;DDS_STBIO1_00000202;DDS_STBIO1_00001199;DDS_STBIO1_0013;DDS_STBIO1_0014;DDS_STBIO1_0015;DDS_STBIO1_0016;DDS_STBIO1_0017;DDS_STBIO1_0018;DDS_STBIO1_0019;DDS_STBIO1_0020;DDS_STBIO1_0021;DDS_STBIO1_0022;DDS_STBIO1_0023;DDS_STBIO1_0024;DDS_STBIO1_0025;DDS_STBIO1_0026;DDS_STBIO1_0027;DDS_STBIO1_0028;DDS_STBIO1_0033;DDS_STBIO1_0034;DDS_STBIO1_0035;DDS_STBIO1_0104;DDS_STBIO1_0105;DDS_STBIO1_0106;DDS_STBIO1_0107;DDS_STBIO1_0108;DDS_STBIO1_0109;DDS_STBIO1_0110;DDS_STBIO1_0111;DDS_STBIO1_0112;DDS_STBIO1_0113;DDS_STBIO1_0114;DDS_STBIO1_0115;DDS_STBIO1_0117;DDS_STBIO1_0118;DDS_STBIO1_0119;DDS_STBIO1_0120;DDS_STBIO1_0121;DDS_STBIO1_0122;DDS_STBIO1_0123;DDS_STBIO1_0124;DDS_STBIO1_0125;DDS_STBIO1_0126;DDS_STBIO1_0127;DDS_STBIO1_0128;DDS_STBIO1_0129;DDS_STBIO1_0130;DDS_STBIO1_0140;DDS_STBIO1_1020;DDS_STBIO1_1021;DDS_STBIO1_1022;DDS_STBIO1_1023;DDS_STBIO1_1024;DDS_STBIO1_1025;DDS_STBIO1_1026;DDS_STBIO1_1027;DDS_STBIO1_1050;DDS_STBIO1_1051;DDS_STBIO1_1052;DDS_STBIO1_1053;DDS_STBIO1_1054;DDS_STBIO1_2024;DDS_STBIO1_2025;DDS_STBIO1_2026;DDS_STBIO1_2052;DDS_STBIO1_2053;DDS_STBIO1_2054;DDS_STBIO1_3000;DDS_STBIO1_3001;DDS_STBIO1_3002;DDS_STBIO1_3003;DDS_STBIO1_3004;DDS_STBIO1_3005;DDS_STBIO1_3006;DDS_STBIO1_302;DDS_STBIO1_303;DDS_STBIO1_304;DDS_STBIO1_305;DDS_STBIO1_306;DDS_STBIO1_307;DDS_STBIO1_308;DDS_STBIO1_309;DDS_STBIO1_310;DDS_STBIO1_311;DDS_STBIO1_312;DDS_STBIO1_313;DDS_STBIO1_314;DDS_STBIO1_392;DDS_STBIO1_393;DDS_STBIO1_394;DDS_STBIO1_395;DDS_STBIO1_4000;DDS_STBIO1_8000;DDS_STBIO1_8001;DDS_STBIO1_8002;DDS_STBIO1_8003;DDS_STBIO1_8004;DDS_STBIO1_8005;DDS_STBIO1_8006;DDS_STBIO1_8007;DDS_STBIO1_8100;DDS_STBIO1_8101;DDS_STBIO1_8102;DDS_STBIO1_8103;DDS_STBIO1_8104;DDS_STBIO1_8105;DDS_STBIO1_8106;DDS_STBIO1_89455232;DDS_STBIO1_89455261;DDS_STBIO1_89455449;DDS_STBIO1_89456557;DDS_STBIO1_89456975;DDS_STBIO1_89457435;DDS_STBIO1_89457790;DDS_STBIO1_89459082;DDS_STBIO1_9017;DDS_STBIO1_9018;DDS_STBIO1_9024;DDS_STBIO1_9027;DDS_STBIO1_9029;DDS_STBIO1_9030;DDS_STBIO1_9031;DDS_STBIO1_9032;DDS_STBIO1_9033;DDS_STBIO1_9034;DDS_STBIO1_9035;DDS_STBIO1_9260;DDS_STBIO1_9261;DDS_STBIO1_9262;DDS_STBIO1_9263;DDS_STBIO1_9300;DDS_STBIO1_9317;DDS_STBIO1_9500;IPOS_STBIO1_MAIN_CONTROLLER_002;IPOS_STBIO1_MAIN_CONTROLLER_004;IPOS_STBIO1_MAIN_CONTROLLER_008;IPOS_STBIO1_MAIN_CONTROLLER_009;IPOS_STBIO1_MAIN_CONTROLLER_010;IPOS_STBIO1_MAIN_CONTROLLER_011;IPOS_STBIO1_MAIN_CONTROLLER_015;IPOS_STBIO1_MAIN_CONTROLLER_0152;IPOS_STBIO1_MAIN_CONTROLLER_016;IPOS_STBIO1_MAIN_CONTROLLER_017;IPOS_STBIO1_MAIN_CONTROLLER_018;IPOS_STBIO1_MAIN_CONTROLLER_019;IPOS_STBIO1_MAIN_CONTROLLER_020;IPOS_STBIO1_MAIN_CONTROLLER_021;IPOS_STBIO1_MAIN_CONTROLLER_022;IPOS_STBIO1_MAIN_CONTROLLER_023;IPOS_STBIO1_MAIN_CONTROLLER_024;IPOS_STBIO1_MAIN_CONTROLLER_026;IPOS_STBIO1_MAIN_CONTROLLER_027;IPOS_STBIO1_MAIN_CONTROLLER_028;IPOS_STBIO1_MAIN_CONTROLLER_029;IPOS_STBIO1_MAIN_CONTROLLER_030;IPOS_STBIO1_MAIN_CONTROLLER_031;IPOS_STBIO1_MAIN_CONTROLLER_032;IPOS_STBIO1_MAIN_CONTROLLER_033;IPOS_STBIO1_MAIN_CONTROLLER_034;IPOS_STBIO1_MAIN_CONTROLLER_035;IPOS_STBIO1_MAIN_CONTROLLER_036;IPOS_STBIO1_MAIN_CONTROLLER_037;IPOS_STBIO1_MAIN_CONTROLLER_038;IPOS_STBIO1_MAIN_CONTROLLER_039;IPOS_STBIO1_MAIN_CONTROLLER_040;IPOS_STBIO1_MAIN_CONTROLLER_043;IPOS_STBIO1_MAIN_CONTROLLER_044;IPOS_STBIO1_MAIN_CONTROLLER_045;IPOS_STBIO1_MAIN_CONTROLLER_047;IPOS_STBIO1_MAIN_CONTROLLER_048;IPOS_STBIO1_MAIN_CONTROLLER_049;IPOS_STBIO1_MAIN_CONTROLLER_051;IPOS_STBIO1_MAIN_CONTROLLER_052;IPOS_STBIO1_MAIN_CONTROLLER_053;IPOS_STBIO1_MAIN_CONTROLLER_054;IPOS_STBIO1_MAIN_CONTROLLER_055;IPOS_STBIO1_MAIN_CONTROLLER_058;IPOS_STBIO1_MAIN_CONTROLLER_059;IPOS_STBIO1_MAIN_CONTROLLER_060;IPOS_STBIO1_MAIN_CONTROLLER_061;IPOS_STBIO1_MAIN_CONTROLLER_062;IPOS_STBIO1_MAIN_CONTROLLER_063;IPOS_STBIO1_MAIN_CONTROLLER_064;IPOS_STBIO1_MAIN_CONTROLLER_072;IPOS_STBIO1_MAIN_CONTROLLER_073;IPOS_STBIO1_MAIN_CONTROLLER_074;IPOS_STBIO1_MAIN_CONTROLLER_075;IPOS_STBIO1_MAIN_CONTROLLER_076;IPOS_STBIO1_MAIN_CONTROLLER_077;IPOS_STBIO1_MAIN_CONTROLLER_078;IPOS_STBIO1_MAIN_CONTROLLER_080;IPOS_STBIO1_MAIN_CONTROLLER_081;IPOS_STBIO1_MAIN_CONTROLLER_082;IPOS_STBIO1_MAIN_CONTROLLER_083;IPOS_STBIO1_MAIN_CONTROLLER_084;IPOS_STBIO1_MAIN_CONTROLLER_085;IPOS_STBIO1_MAIN_CONTROLLER_086;IPOS_STBIO1_MAIN_CONTROLLER_087;IPOS_STBIO1_MAIN_CONTROLLER_088;IPOS_STBIO1_MAIN_CONTROLLER_089;IPOS_STBIO1_MAIN_CONTROLLER_090;IPOS_STBIO1_MAIN_CONTROLLER_092;IPOS_STBIO1_MAIN_CONTROLLER_093;IPOS_STBIO1_MAIN_CONTROLLER_094;IPOS_STBIO1_MAIN_CONTROLLER_095;IPOS_STBIO1_MAIN_CONTROLLER_096;IPOS_STBIO1_MAIN_CONTROLLER_097;IPOS_STBIO1_MAIN_CONTROLLER_098;IPOS_STBIO1_MAIN_CONTROLLER_099;IPOS_STBIO1_MAIN_CONTROLLER_100;IPOS_STBIO1_MAIN_CONTROLLER_1004;IPOS_STBIO1_MAIN_CONTROLLER_1005;IPOS_STBIO1_MAIN_CONTROLLER_1007;IPOS_STBIO1_MAIN_CONTROLLER_1008;IPOS_STBIO1_MAIN_CONTROLLER_1009;IPOS_STBIO1_MAIN_CONTROLLER_101;IPOS_STBIO1_MAIN_CONTROLLER_1010;IPOS_STBIO1_MAIN_CONTROLLER_1011;IPOS_STBIO1_MAIN_CONTROLLER_102;IPOS_STBIO1_MAIN_CONTROLLER_103;IPOS_STBIO1_MAIN_CONTROLLER_1034;IPOS_STBIO1_MAIN_CONTROLLER_104;IPOS_STBIO1_MAIN_CONTROLLER_105;IPOS_STBIO1_MAIN_CONTROLLER_106;IPOS_STBIO1_MAIN_CONTROLLER_107;IPOS_STBIO1_MAIN_CONTROLLER_108;IPOS_STBIO1_MAIN_CONTROLLER_109;IPOS_STBIO1_MAIN_CONTROLLER_1095;IPOS_STBIO1_MAIN_CONTROLLER_110;IPOS_STBIO1_MAIN_CONTROLLER_1102;IPOS_STBIO1_MAIN_CONTROLLER_1104;IPOS_STBIO1_MAIN_CONTROLLER_1105;IPOS_STBIO1_MAIN_CONTROLLER_111;IPOS_STBIO1_MAIN_CONTROLLER_1116;IPOS_STBIO1_MAIN_CONTROLLER_1118;IPOS_STBIO1_MAIN_CONTROLLER_1119;IPOS_STBIO1_MAIN_CONTROLLER_112;IPOS_STBIO1_MAIN_CONTROLLER_113;IPOS_STBIO1_MAIN_CONTROLLER_1136;IPOS_STBIO1_MAIN_CONTROLLER_1139;IPOS_STBIO1_MAIN_CONTROLLER_1143;IPOS_STBIO1_MAIN_CONTROLLER_115;IPOS_STBIO1_MAIN_CONTROLLER_118;IPOS_STBIO1_MAIN_CONTROLLER_120;IPOS_STBIO1_MAIN_CONTROLLER_121;IPOS_STBIO1_MAIN_CONTROLLER_122;IPOS_STBIO1_MAIN_CONTROLLER_123;IPOS_STBIO1_MAIN_CONTROLLER_124;IPOS_STBIO1_MAIN_CONTROLLER_125;IPOS_STBIO1_MAIN_CONTROLLER_126;IPOS_STBIO1_MAIN_CONTROLLER_127;IPOS_STBIO1_MAIN_CONTROLLER_128;IPOS_STBIO1_MAIN_CONTROLLER_129;IPOS_STBIO1_MAIN_CONTROLLER_132;IPOS_STBIO1_MAIN_CONTROLLER_133;IPOS_STBIO1_MAIN_CONTROLLER_134;IPOS_STBIO1_MAIN_CONTROLLER_137;IPOS_STBIO1_MAIN_CONTROLLER_138;IPOS_STBIO1_MAIN_CONTROLLER_139;IPOS_STBIO1_MAIN_CONTROLLER_140;IPOS_STBIO1_MAIN_CONTROLLER_143;IPOS_STBIO1_MAIN_CONTROLLER_2117;IPOS_STBIO1_MAIN_CONTROLLER_2143;IPOS_STBIO1_MAIN_CONTROLLER_2144;IPOS_STBIO1_MAIN_CONTROLLER_2145;IPOS_STBIO1_MAIN_CONTROLLER_2146;IPOS_STBIO1_MAIN_CONTROLLER_300;IPOS_STBIO1_MAIN_CONTROLLER_3124;IPOS_STBIO1_MAIN_CONTROLLER_3125;IPOS_STBIO1_MAIN_CONTROLLER_3126;IPOS_STBIO1_MAIN_CONTROLLER_3127;IPOS_STBIO1_MAIN_CONTROLLER_3128;IPOS_STBIO1_MAIN_CONTROLLER_3129;IPOS_STBIO1_MAIN_CONTROLLER_3130;IPOS_STBIO1_MAIN_CONTROLLER_3131;IPOS_STBIO1_MAIN_CONTROLLER_4034;IPOS_STBIO1_MAIN_CONTROLLER_4079;IPOS_STBIO1_MAIN_CONTROLLER_4080;IPOS_STBIO1_MAIN_CONTROLLER_4090;IPOS_STBIO1_MAIN_CONTROLLER_4091;IPOS_STBIO1_MAIN_CONTROLLER_436;IPOS_STBIO1_MAIN_CONTROLLER_5004;IPOS_STBIO1_MAIN_CONTROLLER_5005;IPOS_STBIO1_MAIN_CONTROLLER_5015;IPOS_STBIO1_MAIN_CONTROLLER_5016;IPOS_STBIO1_MAIN_CONTROLLER_5080;IPOS_STBIO1_MAIN_CONTROLLER_5091;IPOS_STBIO1_MAIN_CONTROLLER_5092;IPOS_STBIO1_MAIN_CONTROLLER_6059;IPOS_STBIO1_MAIN_CONTROLLER_6070;IPOS_STBIO1_MAIN_CONTROLLER_6098;IPOS_STBIO1_MAIN_CONTROLLER_6129;IPOS_STBIO1_MAIN_CONTROLLER_7095;IPOS_STBIO1_MAIN_CONTROLLER_7135;IPOS_STBIO1_MAIN_CONTROLLER_728;IPOS_STBIO1_MAIN_CONTROLLER_8106;IPOS_STBIO1_MAIN_CONTROLLER_8116;IPOS_STBIO1_MAIN_CONTROLLER_9116;IPOS_STBIO1_MAIN_CONTROLLER_9139</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>DRS</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>source:dds_stbio1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Digital IPOS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ADSP</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Primary source specification: dds_stbio1.pdf</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Approved source ledger</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>19</v>
+      </c>
+      <c r="G4" t="n">
+        <v>357</v>
+      </c>
+      <c r="H4" t="n">
+        <v>338</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>5.322128851540616</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Central source-spec provenance/trace ID coverage; not generated-document Covers or publication gate status</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_0013;DDS_STBIO1_0014;DDS_STBIO1_0015;DDS_STBIO1_0016;DDS_STBIO1_0017;DDS_STBIO1_0018;DDS_STBIO1_0019;DDS_STBIO1_0020;DDS_STBIO1_0021;DDS_STBIO1_0022;DDS_STBIO1_0023;DDS_STBIO1_0024;DDS_STBIO1_0025;DDS_STBIO1_0026;DDS_STBIO1_0027;DDS_STBIO1_0028;DDS_STBIO1_0033;DDS_STBIO1_0034;DDS_STBIO1_0035</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_00000008;DDS_STBIO1_00000102;DDS_STBIO1_00000199;DDS_STBIO1_00000202;DDS_STBIO1_00001199;DDS_STBIO1_0032;DDS_STBIO1_0036;DDS_STBIO1_0104;DDS_STBIO1_0105;DDS_STBIO1_0106;DDS_STBIO1_0107;DDS_STBIO1_0108;DDS_STBIO1_0109;DDS_STBIO1_0110;DDS_STBIO1_0111;DDS_STBIO1_0112;DDS_STBIO1_0113;DDS_STBIO1_0114;DDS_STBIO1_0115;DDS_STBIO1_0116;DDS_STBIO1_0117;DDS_STBIO1_0118;DDS_STBIO1_0119;DDS_STBIO1_0120;DDS_STBIO1_0121;DDS_STBIO1_0122;DDS_STBIO1_0123;DDS_STBIO1_0124;DDS_STBIO1_0125;DDS_STBIO1_0126;DDS_STBIO1_0127;DDS_STBIO1_0128;DDS_STBIO1_0129;DDS_STBIO1_0130;DDS_STBIO1_0140;DDS_STBIO1_0141;DDS_STBIO1_0142;DDS_STBIO1_0143;DDS_STBIO1_0144;DDS_STBIO1_0145;DDS_STBIO1_0146;DDS_STBIO1_0147;DDS_STBIO1_0148;DDS_STBIO1_0149;DDS_STBIO1_0201;DDS_STBIO1_0202;DDS_STBIO1_0203;DDS_STBIO1_0204;DDS_STBIO1_0206;DDS_STBIO1_0207;DDS_STBIO1_0208;DDS_STBIO1_0209;DDS_STBIO1_0210;DDS_STBIO1_0211;DDS_STBIO1_0212;DDS_STBIO1_0213;DDS_STBIO1_0215;DDS_STBIO1_0216;DDS_STBIO1_0217;DDS_STBIO1_0218;DDS_STBIO1_0219;DDS_STBIO1_0220;DDS_STBIO1_0221;DDS_STBIO1_0222;DDS_STBIO1_0223;DDS_STBIO1_0501;DDS_STBIO1_05010;DDS_STBIO1_05011;DDS_STBIO1_0502;DDS_STBIO1_0503;DDS_STBIO1_0504;DDS_STBIO1_0505;DDS_STBIO1_0507;DDS_STBIO1_0508;DDS_STBIO1_0509;DDS_STBIO1_0699;DDS_STBIO1_0700;DDS_STBIO1_0701;DDS_STBIO1_0702;DDS_STBIO1_1020;DDS_STBIO1_1021;DDS_STBIO1_1022;DDS_STBIO1_1023;DDS_STBIO1_1024;DDS_STBIO1_1025;DDS_STBIO1_1026;DDS_STBIO1_1027;DDS_STBIO1_1050;DDS_STBIO1_1051;DDS_STBIO1_1052;DDS_STBIO1_1053;DDS_STBIO1_1054;DDS_STBIO1_1114;DDS_STBIO1_1507;DDS_STBIO1_2024;DDS_STBIO1_2025;DDS_STBIO1_2026;DDS_STBIO1_2052;DDS_STBIO1_2053;DDS_STBIO1_2054;DDS_STBIO1_2507;DDS_STBIO1_3000;DDS_STBIO1_3001;DDS_STBIO1_3002;DDS_STBIO1_3003;DDS_STBIO1_3004;DDS_STBIO1_3005;DDS_STBIO1_3006;DDS_STBIO1_302;DDS_STBIO1_303;DDS_STBIO1_304;DDS_STBIO1_305;DDS_STBIO1_306;DDS_STBIO1_307;DDS_STBIO1_308;DDS_STBIO1_309;DDS_STBIO1_310;DDS_STBIO1_311;DDS_STBIO1_312;DDS_STBIO1_313;DDS_STBIO1_314;DDS_STBIO1_392;DDS_STBIO1_393;DDS_STBIO1_394;DDS_STBIO1_395;DDS_STBIO1_4000;DDS_STBIO1_8000;DDS_STBIO1_8001;DDS_STBIO1_8002;DDS_STBIO1_8003;DDS_STBIO1_8004;DDS_STBIO1_8005;DDS_STBIO1_8006;DDS_STBIO1_8007;DDS_STBIO1_8100;DDS_STBIO1_8101;DDS_STBIO1_8102;DDS_STBIO1_8103;DDS_STBIO1_8104;DDS_STBIO1_8105;DDS_STBIO1_8106;DDS_STBIO1_89455232;DDS_STBIO1_89455261;DDS_STBIO1_89455449;DDS_STBIO1_89456557;DDS_STBIO1_89456975;DDS_STBIO1_89457435;DDS_STBIO1_89457790;DDS_STBIO1_89459082;DDS_STBIO1_9004;DDS_STBIO1_9011;DDS_STBIO1_9012;DDS_STBIO1_9013;DDS_STBIO1_9014;DDS_STBIO1_9017;DDS_STBIO1_9018;DDS_STBIO1_9024;DDS_STBIO1_9027;DDS_STBIO1_9029;DDS_STBIO1_9030;DDS_STBIO1_9031;DDS_STBIO1_9032;DDS_STBIO1_9033;DDS_STBIO1_9034;DDS_STBIO1_9035;DDS_STBIO1_9260;DDS_STBIO1_9261;DDS_STBIO1_9262;DDS_STBIO1_9263;DDS_STBIO1_9300;DDS_STBIO1_9317;DDS_STBIO1_9500;IPOS_STBIO1_MAIN_CONTROLLER_002;IPOS_STBIO1_MAIN_CONTROLLER_004;IPOS_STBIO1_MAIN_CONTROLLER_008;IPOS_STBIO1_MAIN_CONTROLLER_009;IPOS_STBIO1_MAIN_CONTROLLER_010;IPOS_STBIO1_MAIN_CONTROLLER_011;IPOS_STBIO1_MAIN_CONTROLLER_015;IPOS_STBIO1_MAIN_CONTROLLER_0152;IPOS_STBIO1_MAIN_CONTROLLER_016;IPOS_STBIO1_MAIN_CONTROLLER_017;IPOS_STBIO1_MAIN_CONTROLLER_018;IPOS_STBIO1_MAIN_CONTROLLER_019;IPOS_STBIO1_MAIN_CONTROLLER_020;IPOS_STBIO1_MAIN_CONTROLLER_021;IPOS_STBIO1_MAIN_CONTROLLER_022;IPOS_STBIO1_MAIN_CONTROLLER_023;IPOS_STBIO1_MAIN_CONTROLLER_024;IPOS_STBIO1_MAIN_CONTROLLER_026;IPOS_STBIO1_MAIN_CONTROLLER_027;IPOS_STBIO1_MAIN_CONTROLLER_028;IPOS_STBIO1_MAIN_CONTROLLER_029;IPOS_STBIO1_MAIN_CONTROLLER_030;IPOS_STBIO1_MAIN_CONTROLLER_031;IPOS_STBIO1_MAIN_CONTROLLER_032;IPOS_STBIO1_MAIN_CONTROLLER_033;IPOS_STBIO1_MAIN_CONTROLLER_034;IPOS_STBIO1_MAIN_CONTROLLER_035;IPOS_STBIO1_MAIN_CONTROLLER_036;IPOS_STBIO1_MAIN_CONTROLLER_037;IPOS_STBIO1_MAIN_CONTROLLER_038;IPOS_STBIO1_MAIN_CONTROLLER_039;IPOS_STBIO1_MAIN_CONTROLLER_040;IPOS_STBIO1_MAIN_CONTROLLER_043;IPOS_STBIO1_MAIN_CONTROLLER_044;IPOS_STBIO1_MAIN_CONTROLLER_045;IPOS_STBIO1_MAIN_CONTROLLER_047;IPOS_STBIO1_MAIN_CONTROLLER_048;IPOS_STBIO1_MAIN_CONTROLLER_049;IPOS_STBIO1_MAIN_CONTROLLER_051;IPOS_STBIO1_MAIN_CONTROLLER_052;IPOS_STBIO1_MAIN_CONTROLLER_053;IPOS_STBIO1_MAIN_CONTROLLER_054;IPOS_STBIO1_MAIN_CONTROLLER_055;IPOS_STBIO1_MAIN_CONTROLLER_058;IPOS_STBIO1_MAIN_CONTROLLER_059;IPOS_STBIO1_MAIN_CONTROLLER_060;IPOS_STBIO1_MAIN_CONTROLLER_061;IPOS_STBIO1_MAIN_CONTROLLER_062;IPOS_STBIO1_MAIN_CONTROLLER_063;IPOS_STBIO1_MAIN_CONTROLLER_064;IPOS_STBIO1_MAIN_CONTROLLER_072;IPOS_STBIO1_MAIN_CONTROLLER_073;IPOS_STBIO1_MAIN_CONTROLLER_074;IPOS_STBIO1_MAIN_CONTROLLER_075;IPOS_STBIO1_MAIN_CONTROLLER_076;IPOS_STBIO1_MAIN_CONTROLLER_077;IPOS_STBIO1_MAIN_CONTROLLER_078;IPOS_STBIO1_MAIN_CONTROLLER_080;IPOS_STBIO1_MAIN_CONTROLLER_081;IPOS_STBIO1_MAIN_CONTROLLER_082;IPOS_STBIO1_MAIN_CONTROLLER_083;IPOS_STBIO1_MAIN_CONTROLLER_084;IPOS_STBIO1_MAIN_CONTROLLER_085;IPOS_STBIO1_MAIN_CONTROLLER_086;IPOS_STBIO1_MAIN_CONTROLLER_087;IPOS_STBIO1_MAIN_CONTROLLER_088;IPOS_STBIO1_MAIN_CONTROLLER_089;IPOS_STBIO1_MAIN_CONTROLLER_090;IPOS_STBIO1_MAIN_CONTROLLER_092;IPOS_STBIO1_MAIN_CONTROLLER_093;IPOS_STBIO1_MAIN_CONTROLLER_094;IPOS_STBIO1_MAIN_CONTROLLER_095;IPOS_STBIO1_MAIN_CONTROLLER_096;IPOS_STBIO1_MAIN_CONTROLLER_097;IPOS_STBIO1_MAIN_CONTROLLER_098;IPOS_STBIO1_MAIN_CONTROLLER_099;IPOS_STBIO1_MAIN_CONTROLLER_100;IPOS_STBIO1_MAIN_CONTROLLER_1004;IPOS_STBIO1_MAIN_CONTROLLER_1005;IPOS_STBIO1_MAIN_CONTROLLER_1007;IPOS_STBIO1_MAIN_CONTROLLER_1008;IPOS_STBIO1_MAIN_CONTROLLER_1009;IPOS_STBIO1_MAIN_CONTROLLER_101;IPOS_STBIO1_MAIN_CONTROLLER_1010;IPOS_STBIO1_MAIN_CONTROLLER_1011;IPOS_STBIO1_MAIN_CONTROLLER_102;IPOS_STBIO1_MAIN_CONTROLLER_103;IPOS_STBIO1_MAIN_CONTROLLER_1034;IPOS_STBIO1_MAIN_CONTROLLER_104;IPOS_STBIO1_MAIN_CONTROLLER_105;IPOS_STBIO1_MAIN_CONTROLLER_106;IPOS_STBIO1_MAIN_CONTROLLER_107;IPOS_STBIO1_MAIN_CONTROLLER_108;IPOS_STBIO1_MAIN_CONTROLLER_109;IPOS_STBIO1_MAIN_CONTROLLER_1095;IPOS_STBIO1_MAIN_CONTROLLER_110;IPOS_STBIO1_MAIN_CONTROLLER_1102;IPOS_STBIO1_MAIN_CONTROLLER_1104;IPOS_STBIO1_MAIN_CONTROLLER_1105;IPOS_STBIO1_MAIN_CONTROLLER_111;IPOS_STBIO1_MAIN_CONTROLLER_1116;IPOS_STBIO1_MAIN_CONTROLLER_1118;IPOS_STBIO1_MAIN_CONTROLLER_1119;IPOS_STBIO1_MAIN_CONTROLLER_112;IPOS_STBIO1_MAIN_CONTROLLER_113;IPOS_STBIO1_MAIN_CONTROLLER_1136;IPOS_STBIO1_MAIN_CONTROLLER_1139;IPOS_STBIO1_MAIN_CONTROLLER_1143;IPOS_STBIO1_MAIN_CONTROLLER_115;IPOS_STBIO1_MAIN_CONTROLLER_118;IPOS_STBIO1_MAIN_CONTROLLER_120;IPOS_STBIO1_MAIN_CONTROLLER_121;IPOS_STBIO1_MAIN_CONTROLLER_122;IPOS_STBIO1_MAIN_CONTROLLER_123;IPOS_STBIO1_MAIN_CONTROLLER_124;IPOS_STBIO1_MAIN_CONTROLLER_125;IPOS_STBIO1_MAIN_CONTROLLER_126;IPOS_STBIO1_MAIN_CONTROLLER_127;IPOS_STBIO1_MAIN_CONTROLLER_128;IPOS_STBIO1_MAIN_CONTROLLER_129;IPOS_STBIO1_MAIN_CONTROLLER_132;IPOS_STBIO1_MAIN_CONTROLLER_133;IPOS_STBIO1_MAIN_CONTROLLER_134;IPOS_STBIO1_MAIN_CONTROLLER_137;IPOS_STBIO1_MAIN_CONTROLLER_138;IPOS_STBIO1_MAIN_CONTROLLER_139;IPOS_STBIO1_MAIN_CONTROLLER_140;IPOS_STBIO1_MAIN_CONTROLLER_143;IPOS_STBIO1_MAIN_CONTROLLER_2117;IPOS_STBIO1_MAIN_CONTROLLER_2143;IPOS_STBIO1_MAIN_CONTROLLER_2144;IPOS_STBIO1_MAIN_CONTROLLER_2145;IPOS_STBIO1_MAIN_CONTROLLER_2146;IPOS_STBIO1_MAIN_CONTROLLER_300;IPOS_STBIO1_MAIN_CONTROLLER_3124;IPOS_STBIO1_MAIN_CONTROLLER_3125;IPOS_STBIO1_MAIN_CONTROLLER_3126;IPOS_STBIO1_MAIN_CONTROLLER_3127;IPOS_STBIO1_MAIN_CONTROLLER_3128;IPOS_STBIO1_MAIN_CONTROLLER_3129;IPOS_STBIO1_MAIN_CONTROLLER_3130;IPOS_STBIO1_MAIN_CONTROLLER_3131;IPOS_STBIO1_MAIN_CONTROLLER_4034;IPOS_STBIO1_MAIN_CONTROLLER_4079;IPOS_STBIO1_MAIN_CONTROLLER_4080;IPOS_STBIO1_MAIN_CONTROLLER_4090;IPOS_STBIO1_MAIN_CONTROLLER_4091;IPOS_STBIO1_MAIN_CONTROLLER_436;IPOS_STBIO1_MAIN_CONTROLLER_5004;IPOS_STBIO1_MAIN_CONTROLLER_5005;IPOS_STBIO1_MAIN_CONTROLLER_5015;IPOS_STBIO1_MAIN_CONTROLLER_5016;IPOS_STBIO1_MAIN_CONTROLLER_5080;IPOS_STBIO1_MAIN_CONTROLLER_5091;IPOS_STBIO1_MAIN_CONTROLLER_5092;IPOS_STBIO1_MAIN_CONTROLLER_6059;IPOS_STBIO1_MAIN_CONTROLLER_6070;IPOS_STBIO1_MAIN_CONTROLLER_6098;IPOS_STBIO1_MAIN_CONTROLLER_6129;IPOS_STBIO1_MAIN_CONTROLLER_7095;IPOS_STBIO1_MAIN_CONTROLLER_7135;IPOS_STBIO1_MAIN_CONTROLLER_728;IPOS_STBIO1_MAIN_CONTROLLER_8106;IPOS_STBIO1_MAIN_CONTROLLER_8116;IPOS_STBIO1_MAIN_CONTROLLER_9116;IPOS_STBIO1_MAIN_CONTROLLER_9139</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Digital_IPOS:adsp</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>source:dds_stbio1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Digital IPOS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>I2C_SPI_AHB</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Primary source specification: dds_stbio1.pdf</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Approved source ledger</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G5" t="n">
+        <v>357</v>
+      </c>
+      <c r="H5" t="n">
+        <v>342</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>4.201680672268908</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Central source-spec provenance/trace ID coverage; not generated-document Covers or publication gate status</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_8000;DDS_STBIO1_8001;DDS_STBIO1_8002;DDS_STBIO1_8003;DDS_STBIO1_8004;DDS_STBIO1_8005;DDS_STBIO1_8006;DDS_STBIO1_8007;DDS_STBIO1_8100;DDS_STBIO1_8101;DDS_STBIO1_8102;DDS_STBIO1_8103;DDS_STBIO1_8104;DDS_STBIO1_8105;DDS_STBIO1_8106</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_00000008;DDS_STBIO1_00000102;DDS_STBIO1_00000199;DDS_STBIO1_00000202;DDS_STBIO1_00001199;DDS_STBIO1_0013;DDS_STBIO1_0014;DDS_STBIO1_0015;DDS_STBIO1_0016;DDS_STBIO1_0017;DDS_STBIO1_0018;DDS_STBIO1_0019;DDS_STBIO1_0020;DDS_STBIO1_0021;DDS_STBIO1_0022;DDS_STBIO1_0023;DDS_STBIO1_0024;DDS_STBIO1_0025;DDS_STBIO1_0026;DDS_STBIO1_0027;DDS_STBIO1_0028;DDS_STBIO1_0032;DDS_STBIO1_0033;DDS_STBIO1_0034;DDS_STBIO1_0035;DDS_STBIO1_0036;DDS_STBIO1_0104;DDS_STBIO1_0105;DDS_STBIO1_0106;DDS_STBIO1_0107;DDS_STBIO1_0108;DDS_STBIO1_0109;DDS_STBIO1_0110;DDS_STBIO1_0111;DDS_STBIO1_0112;DDS_STBIO1_0113;DDS_STBIO1_0114;DDS_STBIO1_0115;DDS_STBIO1_0116;DDS_STBIO1_0117;DDS_STBIO1_0118;DDS_STBIO1_0119;DDS_STBIO1_0120;DDS_STBIO1_0121;DDS_STBIO1_0122;DDS_STBIO1_0123;DDS_STBIO1_0124;DDS_STBIO1_0125;DDS_STBIO1_0126;DDS_STBIO1_0127;DDS_STBIO1_0128;DDS_STBIO1_0129;DDS_STBIO1_0130;DDS_STBIO1_0140;DDS_STBIO1_0141;DDS_STBIO1_0142;DDS_STBIO1_0143;DDS_STBIO1_0144;DDS_STBIO1_0145;DDS_STBIO1_0146;DDS_STBIO1_0147;DDS_STBIO1_0148;DDS_STBIO1_0149;DDS_STBIO1_0201;DDS_STBIO1_0202;DDS_STBIO1_0203;DDS_STBIO1_0204;DDS_STBIO1_0206;DDS_STBIO1_0207;DDS_STBIO1_0208;DDS_STBIO1_0209;DDS_STBIO1_0210;DDS_STBIO1_0211;DDS_STBIO1_0212;DDS_STBIO1_0213;DDS_STBIO1_0215;DDS_STBIO1_0216;DDS_STBIO1_0217;DDS_STBIO1_0218;DDS_STBIO1_0219;DDS_STBIO1_0220;DDS_STBIO1_0221;DDS_STBIO1_0222;DDS_STBIO1_0223;DDS_STBIO1_0501;DDS_STBIO1_05010;DDS_STBIO1_05011;DDS_STBIO1_0502;DDS_STBIO1_0503;DDS_STBIO1_0504;DDS_STBIO1_0505;DDS_STBIO1_0507;DDS_STBIO1_0508;DDS_STBIO1_0509;DDS_STBIO1_0699;DDS_STBIO1_0700;DDS_STBIO1_0701;DDS_STBIO1_0702;DDS_STBIO1_1020;DDS_STBIO1_1021;DDS_STBIO1_1022;DDS_STBIO1_1023;DDS_STBIO1_1024;DDS_STBIO1_1025;DDS_STBIO1_1026;DDS_STBIO1_1027;DDS_STBIO1_1050;DDS_STBIO1_1051;DDS_STBIO1_1052;DDS_STBIO1_1053;DDS_STBIO1_1054;DDS_STBIO1_1114;DDS_STBIO1_1507;DDS_STBIO1_2024;DDS_STBIO1_2025;DDS_STBIO1_2026;DDS_STBIO1_2052;DDS_STBIO1_2053;DDS_STBIO1_2054;DDS_STBIO1_2507;DDS_STBIO1_3000;DDS_STBIO1_3001;DDS_STBIO1_3002;DDS_STBIO1_3003;DDS_STBIO1_3004;DDS_STBIO1_3005;DDS_STBIO1_3006;DDS_STBIO1_302;DDS_STBIO1_303;DDS_STBIO1_304;DDS_STBIO1_305;DDS_STBIO1_306;DDS_STBIO1_307;DDS_STBIO1_308;DDS_STBIO1_309;DDS_STBIO1_310;DDS_STBIO1_311;DDS_STBIO1_312;DDS_STBIO1_313;DDS_STBIO1_314;DDS_STBIO1_392;DDS_STBIO1_393;DDS_STBIO1_394;DDS_STBIO1_395;DDS_STBIO1_4000;DDS_STBIO1_89455232;DDS_STBIO1_89455261;DDS_STBIO1_89455449;DDS_STBIO1_89456557;DDS_STBIO1_89456975;DDS_STBIO1_89457435;DDS_STBIO1_89457790;DDS_STBIO1_89459082;DDS_STBIO1_9004;DDS_STBIO1_9011;DDS_STBIO1_9012;DDS_STBIO1_9013;DDS_STBIO1_9014;DDS_STBIO1_9017;DDS_STBIO1_9018;DDS_STBIO1_9024;DDS_STBIO1_9027;DDS_STBIO1_9029;DDS_STBIO1_9030;DDS_STBIO1_9031;DDS_STBIO1_9032;DDS_STBIO1_9033;DDS_STBIO1_9034;DDS_STBIO1_9035;DDS_STBIO1_9260;DDS_STBIO1_9261;DDS_STBIO1_9262;DDS_STBIO1_9263;DDS_STBIO1_9300;DDS_STBIO1_9317;DDS_STBIO1_9500;IPOS_STBIO1_MAIN_CONTROLLER_002;IPOS_STBIO1_MAIN_CONTROLLER_004;IPOS_STBIO1_MAIN_CONTROLLER_008;IPOS_STBIO1_MAIN_CONTROLLER_009;IPOS_STBIO1_MAIN_CONTROLLER_010;IPOS_STBIO1_MAIN_CONTROLLER_011;IPOS_STBIO1_MAIN_CONTROLLER_015;IPOS_STBIO1_MAIN_CONTROLLER_0152;IPOS_STBIO1_MAIN_CONTROLLER_016;IPOS_STBIO1_MAIN_CONTROLLER_017;IPOS_STBIO1_MAIN_CONTROLLER_018;IPOS_STBIO1_MAIN_CONTROLLER_019;IPOS_STBIO1_MAIN_CONTROLLER_020;IPOS_STBIO1_MAIN_CONTROLLER_021;IPOS_STBIO1_MAIN_CONTROLLER_022;IPOS_STBIO1_MAIN_CONTROLLER_023;IPOS_STBIO1_MAIN_CONTROLLER_024;IPOS_STBIO1_MAIN_CONTROLLER_026;IPOS_STBIO1_MAIN_CONTROLLER_027;IPOS_STBIO1_MAIN_CONTROLLER_028;IPOS_STBIO1_MAIN_CONTROLLER_029;IPOS_STBIO1_MAIN_CONTROLLER_030;IPOS_STBIO1_MAIN_CONTROLLER_031;IPOS_STBIO1_MAIN_CONTROLLER_032;IPOS_STBIO1_MAIN_CONTROLLER_033;IPOS_STBIO1_MAIN_CONTROLLER_034;IPOS_STBIO1_MAIN_CONTROLLER_035;IPOS_STBIO1_MAIN_CONTROLLER_036;IPOS_STBIO1_MAIN_CONTROLLER_037;IPOS_STBIO1_MAIN_CONTROLLER_038;IPOS_STBIO1_MAIN_CONTROLLER_039;IPOS_STBIO1_MAIN_CONTROLLER_040;IPOS_STBIO1_MAIN_CONTROLLER_043;IPOS_STBIO1_MAIN_CONTROLLER_044;IPOS_STBIO1_MAIN_CONTROLLER_045;IPOS_STBIO1_MAIN_CONTROLLER_047;IPOS_STBIO1_MAIN_CONTROLLER_048;IPOS_STBIO1_MAIN_CONTROLLER_049;IPOS_STBIO1_MAIN_CONTROLLER_051;IPOS_STBIO1_MAIN_CONTROLLER_052;IPOS_STBIO1_MAIN_CONTROLLER_053;IPOS_STBIO1_MAIN_CONTROLLER_054;IPOS_STBIO1_MAIN_CONTROLLER_055;IPOS_STBIO1_MAIN_CONTROLLER_058;IPOS_STBIO1_MAIN_CONTROLLER_059;IPOS_STBIO1_MAIN_CONTROLLER_060;IPOS_STBIO1_MAIN_CONTROLLER_061;IPOS_STBIO1_MAIN_CONTROLLER_062;IPOS_STBIO1_MAIN_CONTROLLER_063;IPOS_STBIO1_MAIN_CONTROLLER_064;IPOS_STBIO1_MAIN_CONTROLLER_072;IPOS_STBIO1_MAIN_CONTROLLER_073;IPOS_STBIO1_MAIN_CONTROLLER_074;IPOS_STBIO1_MAIN_CONTROLLER_075;IPOS_STBIO1_MAIN_CONTROLLER_076;IPOS_STBIO1_MAIN_CONTROLLER_077;IPOS_STBIO1_MAIN_CONTROLLER_078;IPOS_STBIO1_MAIN_CONTROLLER_080;IPOS_STBIO1_MAIN_CONTROLLER_081;IPOS_STBIO1_MAIN_CONTROLLER_082;IPOS_STBIO1_MAIN_CONTROLLER_083;IPOS_STBIO1_MAIN_CONTROLLER_084;IPOS_STBIO1_MAIN_CONTROLLER_085;IPOS_STBIO1_MAIN_CONTROLLER_086;IPOS_STBIO1_MAIN_CONTROLLER_087;IPOS_STBIO1_MAIN_CONTROLLER_088;IPOS_STBIO1_MAIN_CONTROLLER_089;IPOS_STBIO1_MAIN_CONTROLLER_090;IPOS_STBIO1_MAIN_CONTROLLER_092;IPOS_STBIO1_MAIN_CONTROLLER_093;IPOS_STBIO1_MAIN_CONTROLLER_094;IPOS_STBIO1_MAIN_CONTROLLER_095;IPOS_STBIO1_MAIN_CONTROLLER_096;IPOS_STBIO1_MAIN_CONTROLLER_097;IPOS_STBIO1_MAIN_CONTROLLER_098;IPOS_STBIO1_MAIN_CONTROLLER_099;IPOS_STBIO1_MAIN_CONTROLLER_100;IPOS_STBIO1_MAIN_CONTROLLER_1004;IPOS_STBIO1_MAIN_CONTROLLER_1005;IPOS_STBIO1_MAIN_CONTROLLER_1007;IPOS_STBIO1_MAIN_CONTROLLER_1008;IPOS_STBIO1_MAIN_CONTROLLER_1009;IPOS_STBIO1_MAIN_CONTROLLER_101;IPOS_STBIO1_MAIN_CONTROLLER_1010;IPOS_STBIO1_MAIN_CONTROLLER_1011;IPOS_STBIO1_MAIN_CONTROLLER_102;IPOS_STBIO1_MAIN_CONTROLLER_103;IPOS_STBIO1_MAIN_CONTROLLER_1034;IPOS_STBIO1_MAIN_CONTROLLER_104;IPOS_STBIO1_MAIN_CONTROLLER_105;IPOS_STBIO1_MAIN_CONTROLLER_106;IPOS_STBIO1_MAIN_CONTROLLER_107;IPOS_STBIO1_MAIN_CONTROLLER_108;IPOS_STBIO1_MAIN_CONTROLLER_109;IPOS_STBIO1_MAIN_CONTROLLER_1095;IPOS_STBIO1_MAIN_CONTROLLER_110;IPOS_STBIO1_MAIN_CONTROLLER_1102;IPOS_STBIO1_MAIN_CONTROLLER_1104;IPOS_STBIO1_MAIN_CONTROLLER_1105;IPOS_STBIO1_MAIN_CONTROLLER_111;IPOS_STBIO1_MAIN_CONTROLLER_1116;IPOS_STBIO1_MAIN_CONTROLLER_1118;IPOS_STBIO1_MAIN_CONTROLLER_1119;IPOS_STBIO1_MAIN_CONTROLLER_112;IPOS_STBIO1_MAIN_CONTROLLER_113;IPOS_STBIO1_MAIN_CONTROLLER_1136;IPOS_STBIO1_MAIN_CONTROLLER_1139;IPOS_STBIO1_MAIN_CONTROLLER_1143;IPOS_STBIO1_MAIN_CONTROLLER_115;IPOS_STBIO1_MAIN_CONTROLLER_118;IPOS_STBIO1_MAIN_CONTROLLER_120;IPOS_STBIO1_MAIN_CONTROLLER_121;IPOS_STBIO1_MAIN_CONTROLLER_122;IPOS_STBIO1_MAIN_CONTROLLER_123;IPOS_STBIO1_MAIN_CONTROLLER_124;IPOS_STBIO1_MAIN_CONTROLLER_125;IPOS_STBIO1_MAIN_CONTROLLER_126;IPOS_STBIO1_MAIN_CONTROLLER_127;IPOS_STBIO1_MAIN_CONTROLLER_128;IPOS_STBIO1_MAIN_CONTROLLER_129;IPOS_STBIO1_MAIN_CONTROLLER_132;IPOS_STBIO1_MAIN_CONTROLLER_133;IPOS_STBIO1_MAIN_CONTROLLER_134;IPOS_STBIO1_MAIN_CONTROLLER_137;IPOS_STBIO1_MAIN_CONTROLLER_138;IPOS_STBIO1_MAIN_CONTROLLER_139;IPOS_STBIO1_MAIN_CONTROLLER_140;IPOS_STBIO1_MAIN_CONTROLLER_143;IPOS_STBIO1_MAIN_CONTROLLER_2117;IPOS_STBIO1_MAIN_CONTROLLER_2143;IPOS_STBIO1_MAIN_CONTROLLER_2144;IPOS_STBIO1_MAIN_CONTROLLER_2145;IPOS_STBIO1_MAIN_CONTROLLER_2146;IPOS_STBIO1_MAIN_CONTROLLER_300;IPOS_STBIO1_MAIN_CONTROLLER_3124;IPOS_STBIO1_MAIN_CONTROLLER_3125;IPOS_STBIO1_MAIN_CONTROLLER_3126;IPOS_STBIO1_MAIN_CONTROLLER_3127;IPOS_STBIO1_MAIN_CONTROLLER_3128;IPOS_STBIO1_MAIN_CONTROLLER_3129;IPOS_STBIO1_MAIN_CONTROLLER_3130;IPOS_STBIO1_MAIN_CONTROLLER_3131;IPOS_STBIO1_MAIN_CONTROLLER_4034;IPOS_STBIO1_MAIN_CONTROLLER_4079;IPOS_STBIO1_MAIN_CONTROLLER_4080;IPOS_STBIO1_MAIN_CONTROLLER_4090;IPOS_STBIO1_MAIN_CONTROLLER_4091;IPOS_STBIO1_MAIN_CONTROLLER_436;IPOS_STBIO1_MAIN_CONTROLLER_5004;IPOS_STBIO1_MAIN_CONTROLLER_5005;IPOS_STBIO1_MAIN_CONTROLLER_5015;IPOS_STBIO1_MAIN_CONTROLLER_5016;IPOS_STBIO1_MAIN_CONTROLLER_5080;IPOS_STBIO1_MAIN_CONTROLLER_5091;IPOS_STBIO1_MAIN_CONTROLLER_5092;IPOS_STBIO1_MAIN_CONTROLLER_6059;IPOS_STBIO1_MAIN_CONTROLLER_6070;IPOS_STBIO1_MAIN_CONTROLLER_6098;IPOS_STBIO1_MAIN_CONTROLLER_6129;IPOS_STBIO1_MAIN_CONTROLLER_7095;IPOS_STBIO1_MAIN_CONTROLLER_7135;IPOS_STBIO1_MAIN_CONTROLLER_728;IPOS_STBIO1_MAIN_CONTROLLER_8106;IPOS_STBIO1_MAIN_CONTROLLER_8116;IPOS_STBIO1_MAIN_CONTROLLER_9116;IPOS_STBIO1_MAIN_CONTROLLER_9139</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Digital_IPOS:i2c-spi-ahb</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>source:dds_stbio1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Digital IPOS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Main Controller</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Primary source specification: dds_stbio1.pdf</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Approved source ledger</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>181</v>
+      </c>
+      <c r="G6" t="n">
+        <v>357</v>
+      </c>
+      <c r="H6" t="n">
+        <v>176</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>50.70028011204482</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Central source-spec provenance/trace ID coverage; not generated-document Covers or publication gate status</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_0117;DDS_STBIO1_0118;DDS_STBIO1_0119;DDS_STBIO1_0120;DDS_STBIO1_0121;DDS_STBIO1_0122;DDS_STBIO1_0123;DDS_STBIO1_0124;DDS_STBIO1_0125;DDS_STBIO1_0126;DDS_STBIO1_0127;DDS_STBIO1_0128;DDS_STBIO1_0129;DDS_STBIO1_0130;DDS_STBIO1_0140;IPOS_STBIO1_MAIN_CONTROLLER_002;IPOS_STBIO1_MAIN_CONTROLLER_004;IPOS_STBIO1_MAIN_CONTROLLER_008;IPOS_STBIO1_MAIN_CONTROLLER_009;IPOS_STBIO1_MAIN_CONTROLLER_010;IPOS_STBIO1_MAIN_CONTROLLER_011;IPOS_STBIO1_MAIN_CONTROLLER_015;IPOS_STBIO1_MAIN_CONTROLLER_0152;IPOS_STBIO1_MAIN_CONTROLLER_016;IPOS_STBIO1_MAIN_CONTROLLER_017;IPOS_STBIO1_MAIN_CONTROLLER_018;IPOS_STBIO1_MAIN_CONTROLLER_019;IPOS_STBIO1_MAIN_CONTROLLER_020;IPOS_STBIO1_MAIN_CONTROLLER_021;IPOS_STBIO1_MAIN_CONTROLLER_022;IPOS_STBIO1_MAIN_CONTROLLER_023;IPOS_STBIO1_MAIN_CONTROLLER_024;IPOS_STBIO1_MAIN_CONTROLLER_026;IPOS_STBIO1_MAIN_CONTROLLER_027;IPOS_STBIO1_MAIN_CONTROLLER_028;IPOS_STBIO1_MAIN_CONTROLLER_029;IPOS_STBIO1_MAIN_CONTROLLER_030;IPOS_STBIO1_MAIN_CONTROLLER_031;IPOS_STBIO1_MAIN_CONTROLLER_032;IPOS_STBIO1_MAIN_CONTROLLER_033;IPOS_STBIO1_MAIN_CONTROLLER_034;IPOS_STBIO1_MAIN_CONTROLLER_035;IPOS_STBIO1_MAIN_CONTROLLER_036;IPOS_STBIO1_MAIN_CONTROLLER_037;IPOS_STBIO1_MAIN_CONTROLLER_038;IPOS_STBIO1_MAIN_CONTROLLER_039;IPOS_STBIO1_MAIN_CONTROLLER_040;IPOS_STBIO1_MAIN_CONTROLLER_043;IPOS_STBIO1_MAIN_CONTROLLER_044;IPOS_STBIO1_MAIN_CONTROLLER_045;IPOS_STBIO1_MAIN_CONTROLLER_047;IPOS_STBIO1_MAIN_CONTROLLER_048;IPOS_STBIO1_MAIN_CONTROLLER_049;IPOS_STBIO1_MAIN_CONTROLLER_051;IPOS_STBIO1_MAIN_CONTROLLER_052;IPOS_STBIO1_MAIN_CONTROLLER_053;IPOS_STBIO1_MAIN_CONTROLLER_054;IPOS_STBIO1_MAIN_CONTROLLER_055;IPOS_STBIO1_MAIN_CONTROLLER_058;IPOS_STBIO1_MAIN_CONTROLLER_059;IPOS_STBIO1_MAIN_CONTROLLER_060;IPOS_STBIO1_MAIN_CONTROLLER_061;IPOS_STBIO1_MAIN_CONTROLLER_062;IPOS_STBIO1_MAIN_CONTROLLER_063;IPOS_STBIO1_MAIN_CONTROLLER_064;IPOS_STBIO1_MAIN_CONTROLLER_072;IPOS_STBIO1_MAIN_CONTROLLER_073;IPOS_STBIO1_MAIN_CONTROLLER_074;IPOS_STBIO1_MAIN_CONTROLLER_075;IPOS_STBIO1_MAIN_CONTROLLER_076;IPOS_STBIO1_MAIN_CONTROLLER_077;IPOS_STBIO1_MAIN_CONTROLLER_078;IPOS_STBIO1_MAIN_CONTROLLER_080;IPOS_STBIO1_MAIN_CONTROLLER_081;IPOS_STBIO1_MAIN_CONTROLLER_082;IPOS_STBIO1_MAIN_CONTROLLER_083;IPOS_STBIO1_MAIN_CONTROLLER_084;IPOS_STBIO1_MAIN_CONTROLLER_085;IPOS_STBIO1_MAIN_CONTROLLER_086;IPOS_STBIO1_MAIN_CONTROLLER_087;IPOS_STBIO1_MAIN_CONTROLLER_088;IPOS_STBIO1_MAIN_CONTROLLER_089;IPOS_STBIO1_MAIN_CONTROLLER_090;IPOS_STBIO1_MAIN_CONTROLLER_092;IPOS_STBIO1_MAIN_CONTROLLER_093;IPOS_STBIO1_MAIN_CONTROLLER_094;IPOS_STBIO1_MAIN_CONTROLLER_095;IPOS_STBIO1_MAIN_CONTROLLER_096;IPOS_STBIO1_MAIN_CONTROLLER_097;IPOS_STBIO1_MAIN_CONTROLLER_098;IPOS_STBIO1_MAIN_CONTROLLER_099;IPOS_STBIO1_MAIN_CONTROLLER_100;IPOS_STBIO1_MAIN_CONTROLLER_1004;IPOS_STBIO1_MAIN_CONTROLLER_1005;IPOS_STBIO1_MAIN_CONTROLLER_1007;IPOS_STBIO1_MAIN_CONTROLLER_1008;IPOS_STBIO1_MAIN_CONTROLLER_1009;IPOS_STBIO1_MAIN_CONTROLLER_101;IPOS_STBIO1_MAIN_CONTROLLER_1010;IPOS_STBIO1_MAIN_CONTROLLER_1011;IPOS_STBIO1_MAIN_CONTROLLER_102;IPOS_STBIO1_MAIN_CONTROLLER_103;IPOS_STBIO1_MAIN_CONTROLLER_1034;IPOS_STBIO1_MAIN_CONTROLLER_104;IPOS_STBIO1_MAIN_CONTROLLER_105;IPOS_STBIO1_MAIN_CONTROLLER_106;IPOS_STBIO1_MAIN_CONTROLLER_107;IPOS_STBIO1_MAIN_CONTROLLER_108;IPOS_STBIO1_MAIN_CONTROLLER_109;IPOS_STBIO1_MAIN_CONTROLLER_1095;IPOS_STBIO1_MAIN_CONTROLLER_110;IPOS_STBIO1_MAIN_CONTROLLER_1102;IPOS_STBIO1_MAIN_CONTROLLER_1104;IPOS_STBIO1_MAIN_CONTROLLER_1105;IPOS_STBIO1_MAIN_CONTROLLER_111;IPOS_STBIO1_MAIN_CONTROLLER_1116;IPOS_STBIO1_MAIN_CONTROLLER_1118;IPOS_STBIO1_MAIN_CONTROLLER_1119;IPOS_STBIO1_MAIN_CONTROLLER_112;IPOS_STBIO1_MAIN_CONTROLLER_113;IPOS_STBIO1_MAIN_CONTROLLER_1136;IPOS_STBIO1_MAIN_CONTROLLER_1139;IPOS_STBIO1_MAIN_CONTROLLER_1143;IPOS_STBIO1_MAIN_CONTROLLER_115;IPOS_STBIO1_MAIN_CONTROLLER_118;IPOS_STBIO1_MAIN_CONTROLLER_120;IPOS_STBIO1_MAIN_CONTROLLER_121;IPOS_STBIO1_MAIN_CONTROLLER_122;IPOS_STBIO1_MAIN_CONTROLLER_123;IPOS_STBIO1_MAIN_CONTROLLER_124;IPOS_STBIO1_MAIN_CONTROLLER_125;IPOS_STBIO1_MAIN_CONTROLLER_126;IPOS_STBIO1_MAIN_CONTROLLER_127;IPOS_STBIO1_MAIN_CONTROLLER_128;IPOS_STBIO1_MAIN_CONTROLLER_129;IPOS_STBIO1_MAIN_CONTROLLER_132;IPOS_STBIO1_MAIN_CONTROLLER_133;IPOS_STBIO1_MAIN_CONTROLLER_134;IPOS_STBIO1_MAIN_CONTROLLER_137;IPOS_STBIO1_MAIN_CONTROLLER_138;IPOS_STBIO1_MAIN_CONTROLLER_139;IPOS_STBIO1_MAIN_CONTROLLER_140;IPOS_STBIO1_MAIN_CONTROLLER_143;IPOS_STBIO1_MAIN_CONTROLLER_2117;IPOS_STBIO1_MAIN_CONTROLLER_2143;IPOS_STBIO1_MAIN_CONTROLLER_2144;IPOS_STBIO1_MAIN_CONTROLLER_2145;IPOS_STBIO1_MAIN_CONTROLLER_2146;IPOS_STBIO1_MAIN_CONTROLLER_300;IPOS_STBIO1_MAIN_CONTROLLER_3124;IPOS_STBIO1_MAIN_CONTROLLER_3125;IPOS_STBIO1_MAIN_CONTROLLER_3126;IPOS_STBIO1_MAIN_CONTROLLER_3127;IPOS_STBIO1_MAIN_CONTROLLER_3128;IPOS_STBIO1_MAIN_CONTROLLER_3129;IPOS_STBIO1_MAIN_CONTROLLER_3130;IPOS_STBIO1_MAIN_CONTROLLER_3131;IPOS_STBIO1_MAIN_CONTROLLER_4034;IPOS_STBIO1_MAIN_CONTROLLER_4079;IPOS_STBIO1_MAIN_CONTROLLER_4080;IPOS_STBIO1_MAIN_CONTROLLER_4090;IPOS_STBIO1_MAIN_CONTROLLER_4091;IPOS_STBIO1_MAIN_CONTROLLER_436;IPOS_STBIO1_MAIN_CONTROLLER_5004;IPOS_STBIO1_MAIN_CONTROLLER_5005;IPOS_STBIO1_MAIN_CONTROLLER_5015;IPOS_STBIO1_MAIN_CONTROLLER_5016;IPOS_STBIO1_MAIN_CONTROLLER_5080;IPOS_STBIO1_MAIN_CONTROLLER_5091;IPOS_STBIO1_MAIN_CONTROLLER_5092;IPOS_STBIO1_MAIN_CONTROLLER_6059;IPOS_STBIO1_MAIN_CONTROLLER_6070;IPOS_STBIO1_MAIN_CONTROLLER_6098;IPOS_STBIO1_MAIN_CONTROLLER_6129;IPOS_STBIO1_MAIN_CONTROLLER_7095;IPOS_STBIO1_MAIN_CONTROLLER_7135;IPOS_STBIO1_MAIN_CONTROLLER_728;IPOS_STBIO1_MAIN_CONTROLLER_8106;IPOS_STBIO1_MAIN_CONTROLLER_8116;IPOS_STBIO1_MAIN_CONTROLLER_9116;IPOS_STBIO1_MAIN_CONTROLLER_9139</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_00000008;DDS_STBIO1_00000102;DDS_STBIO1_00000199;DDS_STBIO1_00000202;DDS_STBIO1_00001199;DDS_STBIO1_0013;DDS_STBIO1_0014;DDS_STBIO1_0015;DDS_STBIO1_0016;DDS_STBIO1_0017;DDS_STBIO1_0018;DDS_STBIO1_0019;DDS_STBIO1_0020;DDS_STBIO1_0021;DDS_STBIO1_0022;DDS_STBIO1_0023;DDS_STBIO1_0024;DDS_STBIO1_0025;DDS_STBIO1_0026;DDS_STBIO1_0027;DDS_STBIO1_0028;DDS_STBIO1_0032;DDS_STBIO1_0033;DDS_STBIO1_0034;DDS_STBIO1_0035;DDS_STBIO1_0036;DDS_STBIO1_0104;DDS_STBIO1_0105;DDS_STBIO1_0106;DDS_STBIO1_0107;DDS_STBIO1_0108;DDS_STBIO1_0109;DDS_STBIO1_0110;DDS_STBIO1_0111;DDS_STBIO1_0112;DDS_STBIO1_0113;DDS_STBIO1_0114;DDS_STBIO1_0115;DDS_STBIO1_0116;DDS_STBIO1_0141;DDS_STBIO1_0142;DDS_STBIO1_0143;DDS_STBIO1_0144;DDS_STBIO1_0145;DDS_STBIO1_0146;DDS_STBIO1_0147;DDS_STBIO1_0148;DDS_STBIO1_0149;DDS_STBIO1_0201;DDS_STBIO1_0202;DDS_STBIO1_0203;DDS_STBIO1_0204;DDS_STBIO1_0206;DDS_STBIO1_0207;DDS_STBIO1_0208;DDS_STBIO1_0209;DDS_STBIO1_0210;DDS_STBIO1_0211;DDS_STBIO1_0212;DDS_STBIO1_0213;DDS_STBIO1_0215;DDS_STBIO1_0216;DDS_STBIO1_0217;DDS_STBIO1_0218;DDS_STBIO1_0219;DDS_STBIO1_0220;DDS_STBIO1_0221;DDS_STBIO1_0222;DDS_STBIO1_0223;DDS_STBIO1_0501;DDS_STBIO1_05010;DDS_STBIO1_05011;DDS_STBIO1_0502;DDS_STBIO1_0503;DDS_STBIO1_0504;DDS_STBIO1_0505;DDS_STBIO1_0507;DDS_STBIO1_0508;DDS_STBIO1_0509;DDS_STBIO1_0699;DDS_STBIO1_0700;DDS_STBIO1_0701;DDS_STBIO1_0702;DDS_STBIO1_1020;DDS_STBIO1_1021;DDS_STBIO1_1022;DDS_STBIO1_1023;DDS_STBIO1_1024;DDS_STBIO1_1025;DDS_STBIO1_1026;DDS_STBIO1_1027;DDS_STBIO1_1050;DDS_STBIO1_1051;DDS_STBIO1_1052;DDS_STBIO1_1053;DDS_STBIO1_1054;DDS_STBIO1_1114;DDS_STBIO1_1507;DDS_STBIO1_2024;DDS_STBIO1_2025;DDS_STBIO1_2026;DDS_STBIO1_2052;DDS_STBIO1_2053;DDS_STBIO1_2054;DDS_STBIO1_2507;DDS_STBIO1_3000;DDS_STBIO1_3001;DDS_STBIO1_3002;DDS_STBIO1_3003;DDS_STBIO1_3004;DDS_STBIO1_3005;DDS_STBIO1_3006;DDS_STBIO1_302;DDS_STBIO1_303;DDS_STBIO1_304;DDS_STBIO1_305;DDS_STBIO1_306;DDS_STBIO1_307;DDS_STBIO1_308;DDS_STBIO1_309;DDS_STBIO1_310;DDS_STBIO1_311;DDS_STBIO1_312;DDS_STBIO1_313;DDS_STBIO1_314;DDS_STBIO1_392;DDS_STBIO1_393;DDS_STBIO1_394;DDS_STBIO1_395;DDS_STBIO1_4000;DDS_STBIO1_8000;DDS_STBIO1_8001;DDS_STBIO1_8002;DDS_STBIO1_8003;DDS_STBIO1_8004;DDS_STBIO1_8005;DDS_STBIO1_8006;DDS_STBIO1_8007;DDS_STBIO1_8100;DDS_STBIO1_8101;DDS_STBIO1_8102;DDS_STBIO1_8103;DDS_STBIO1_8104;DDS_STBIO1_8105;DDS_STBIO1_8106;DDS_STBIO1_89455232;DDS_STBIO1_89455261;DDS_STBIO1_89455449;DDS_STBIO1_89456557;DDS_STBIO1_89456975;DDS_STBIO1_89457435;DDS_STBIO1_89457790;DDS_STBIO1_89459082;DDS_STBIO1_9004;DDS_STBIO1_9011;DDS_STBIO1_9012;DDS_STBIO1_9013;DDS_STBIO1_9014;DDS_STBIO1_9017;DDS_STBIO1_9018;DDS_STBIO1_9024;DDS_STBIO1_9027;DDS_STBIO1_9029;DDS_STBIO1_9030;DDS_STBIO1_9031;DDS_STBIO1_9032;DDS_STBIO1_9033;DDS_STBIO1_9034;DDS_STBIO1_9035;DDS_STBIO1_9260;DDS_STBIO1_9261;DDS_STBIO1_9262;DDS_STBIO1_9263;DDS_STBIO1_9300;DDS_STBIO1_9317;DDS_STBIO1_9500</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Digital_IPOS:main-controller</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>source:dds_stbio1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Digital IPOS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pad Mux</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Primary source specification: dds_stbio1.pdf</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Approved source ledger</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>17</v>
+      </c>
+      <c r="G7" t="n">
+        <v>357</v>
+      </c>
+      <c r="H7" t="n">
+        <v>340</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Central source-spec provenance/trace ID coverage; not generated-document Covers or publication gate status</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_302;DDS_STBIO1_303;DDS_STBIO1_304;DDS_STBIO1_305;DDS_STBIO1_306;DDS_STBIO1_307;DDS_STBIO1_308;DDS_STBIO1_309;DDS_STBIO1_310;DDS_STBIO1_311;DDS_STBIO1_312;DDS_STBIO1_313;DDS_STBIO1_314;DDS_STBIO1_392;DDS_STBIO1_393;DDS_STBIO1_394;DDS_STBIO1_395</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_00000008;DDS_STBIO1_00000102;DDS_STBIO1_00000199;DDS_STBIO1_00000202;DDS_STBIO1_00001199;DDS_STBIO1_0013;DDS_STBIO1_0014;DDS_STBIO1_0015;DDS_STBIO1_0016;DDS_STBIO1_0017;DDS_STBIO1_0018;DDS_STBIO1_0019;DDS_STBIO1_0020;DDS_STBIO1_0021;DDS_STBIO1_0022;DDS_STBIO1_0023;DDS_STBIO1_0024;DDS_STBIO1_0025;DDS_STBIO1_0026;DDS_STBIO1_0027;DDS_STBIO1_0028;DDS_STBIO1_0032;DDS_STBIO1_0033;DDS_STBIO1_0034;DDS_STBIO1_0035;DDS_STBIO1_0036;DDS_STBIO1_0104;DDS_STBIO1_0105;DDS_STBIO1_0106;DDS_STBIO1_0107;DDS_STBIO1_0108;DDS_STBIO1_0109;DDS_STBIO1_0110;DDS_STBIO1_0111;DDS_STBIO1_0112;DDS_STBIO1_0113;DDS_STBIO1_0114;DDS_STBIO1_0115;DDS_STBIO1_0116;DDS_STBIO1_0117;DDS_STBIO1_0118;DDS_STBIO1_0119;DDS_STBIO1_0120;DDS_STBIO1_0121;DDS_STBIO1_0122;DDS_STBIO1_0123;DDS_STBIO1_0124;DDS_STBIO1_0125;DDS_STBIO1_0126;DDS_STBIO1_0127;DDS_STBIO1_0128;DDS_STBIO1_0129;DDS_STBIO1_0130;DDS_STBIO1_0140;DDS_STBIO1_0141;DDS_STBIO1_0142;DDS_STBIO1_0143;DDS_STBIO1_0144;DDS_STBIO1_0145;DDS_STBIO1_0146;DDS_STBIO1_0147;DDS_STBIO1_0148;DDS_STBIO1_0149;DDS_STBIO1_0201;DDS_STBIO1_0202;DDS_STBIO1_0203;DDS_STBIO1_0204;DDS_STBIO1_0206;DDS_STBIO1_0207;DDS_STBIO1_0208;DDS_STBIO1_0209;DDS_STBIO1_0210;DDS_STBIO1_0211;DDS_STBIO1_0212;DDS_STBIO1_0213;DDS_STBIO1_0215;DDS_STBIO1_0216;DDS_STBIO1_0217;DDS_STBIO1_0218;DDS_STBIO1_0219;DDS_STBIO1_0220;DDS_STBIO1_0221;DDS_STBIO1_0222;DDS_STBIO1_0223;DDS_STBIO1_0501;DDS_STBIO1_05010;DDS_STBIO1_05011;DDS_STBIO1_0502;DDS_STBIO1_0503;DDS_STBIO1_0504;DDS_STBIO1_0505;DDS_STBIO1_0507;DDS_STBIO1_0508;DDS_STBIO1_0509;DDS_STBIO1_0699;DDS_STBIO1_0700;DDS_STBIO1_0701;DDS_STBIO1_0702;DDS_STBIO1_1020;DDS_STBIO1_1021;DDS_STBIO1_1022;DDS_STBIO1_1023;DDS_STBIO1_1024;DDS_STBIO1_1025;DDS_STBIO1_1026;DDS_STBIO1_1027;DDS_STBIO1_1050;DDS_STBIO1_1051;DDS_STBIO1_1052;DDS_STBIO1_1053;DDS_STBIO1_1054;DDS_STBIO1_1114;DDS_STBIO1_1507;DDS_STBIO1_2024;DDS_STBIO1_2025;DDS_STBIO1_2026;DDS_STBIO1_2052;DDS_STBIO1_2053;DDS_STBIO1_2054;DDS_STBIO1_2507;DDS_STBIO1_3000;DDS_STBIO1_3001;DDS_STBIO1_3002;DDS_STBIO1_3003;DDS_STBIO1_3004;DDS_STBIO1_3005;DDS_STBIO1_3006;DDS_STBIO1_4000;DDS_STBIO1_8000;DDS_STBIO1_8001;DDS_STBIO1_8002;DDS_STBIO1_8003;DDS_STBIO1_8004;DDS_STBIO1_8005;DDS_STBIO1_8006;DDS_STBIO1_8007;DDS_STBIO1_8100;DDS_STBIO1_8101;DDS_STBIO1_8102;DDS_STBIO1_8103;DDS_STBIO1_8104;DDS_STBIO1_8105;DDS_STBIO1_8106;DDS_STBIO1_89455232;DDS_STBIO1_89455261;DDS_STBIO1_89455449;DDS_STBIO1_89456557;DDS_STBIO1_89456975;DDS_STBIO1_89457435;DDS_STBIO1_89457790;DDS_STBIO1_89459082;DDS_STBIO1_9004;DDS_STBIO1_9011;DDS_STBIO1_9012;DDS_STBIO1_9013;DDS_STBIO1_9014;DDS_STBIO1_9017;DDS_STBIO1_9018;DDS_STBIO1_9024;DDS_STBIO1_9027;DDS_STBIO1_9029;DDS_STBIO1_9030;DDS_STBIO1_9031;DDS_STBIO1_9032;DDS_STBIO1_9033;DDS_STBIO1_9034;DDS_STBIO1_9035;DDS_STBIO1_9260;DDS_STBIO1_9261;DDS_STBIO1_9262;DDS_STBIO1_9263;DDS_STBIO1_9300;DDS_STBIO1_9317;DDS_STBIO1_9500;IPOS_STBIO1_MAIN_CONTROLLER_002;IPOS_STBIO1_MAIN_CONTROLLER_004;IPOS_STBIO1_MAIN_CONTROLLER_008;IPOS_STBIO1_MAIN_CONTROLLER_009;IPOS_STBIO1_MAIN_CONTROLLER_010;IPOS_STBIO1_MAIN_CONTROLLER_011;IPOS_STBIO1_MAIN_CONTROLLER_015;IPOS_STBIO1_MAIN_CONTROLLER_0152;IPOS_STBIO1_MAIN_CONTROLLER_016;IPOS_STBIO1_MAIN_CONTROLLER_017;IPOS_STBIO1_MAIN_CONTROLLER_018;IPOS_STBIO1_MAIN_CONTROLLER_019;IPOS_STBIO1_MAIN_CONTROLLER_020;IPOS_STBIO1_MAIN_CONTROLLER_021;IPOS_STBIO1_MAIN_CONTROLLER_022;IPOS_STBIO1_MAIN_CONTROLLER_023;IPOS_STBIO1_MAIN_CONTROLLER_024;IPOS_STBIO1_MAIN_CONTROLLER_026;IPOS_STBIO1_MAIN_CONTROLLER_027;IPOS_STBIO1_MAIN_CONTROLLER_028;IPOS_STBIO1_MAIN_CONTROLLER_029;IPOS_STBIO1_MAIN_CONTROLLER_030;IPOS_STBIO1_MAIN_CONTROLLER_031;IPOS_STBIO1_MAIN_CONTROLLER_032;IPOS_STBIO1_MAIN_CONTROLLER_033;IPOS_STBIO1_MAIN_CONTROLLER_034;IPOS_STBIO1_MAIN_CONTROLLER_035;IPOS_STBIO1_MAIN_CONTROLLER_036;IPOS_STBIO1_MAIN_CONTROLLER_037;IPOS_STBIO1_MAIN_CONTROLLER_038;IPOS_STBIO1_MAIN_CONTROLLER_039;IPOS_STBIO1_MAIN_CONTROLLER_040;IPOS_STBIO1_MAIN_CONTROLLER_043;IPOS_STBIO1_MAIN_CONTROLLER_044;IPOS_STBIO1_MAIN_CONTROLLER_045;IPOS_STBIO1_MAIN_CONTROLLER_047;IPOS_STBIO1_MAIN_CONTROLLER_048;IPOS_STBIO1_MAIN_CONTROLLER_049;IPOS_STBIO1_MAIN_CONTROLLER_051;IPOS_STBIO1_MAIN_CONTROLLER_052;IPOS_STBIO1_MAIN_CONTROLLER_053;IPOS_STBIO1_MAIN_CONTROLLER_054;IPOS_STBIO1_MAIN_CONTROLLER_055;IPOS_STBIO1_MAIN_CONTROLLER_058;IPOS_STBIO1_MAIN_CONTROLLER_059;IPOS_STBIO1_MAIN_CONTROLLER_060;IPOS_STBIO1_MAIN_CONTROLLER_061;IPOS_STBIO1_MAIN_CONTROLLER_062;IPOS_STBIO1_MAIN_CONTROLLER_063;IPOS_STBIO1_MAIN_CONTROLLER_064;IPOS_STBIO1_MAIN_CONTROLLER_072;IPOS_STBIO1_MAIN_CONTROLLER_073;IPOS_STBIO1_MAIN_CONTROLLER_074;IPOS_STBIO1_MAIN_CONTROLLER_075;IPOS_STBIO1_MAIN_CONTROLLER_076;IPOS_STBIO1_MAIN_CONTROLLER_077;IPOS_STBIO1_MAIN_CONTROLLER_078;IPOS_STBIO1_MAIN_CONTROLLER_080;IPOS_STBIO1_MAIN_CONTROLLER_081;IPOS_STBIO1_MAIN_CONTROLLER_082;IPOS_STBIO1_MAIN_CONTROLLER_083;IPOS_STBIO1_MAIN_CONTROLLER_084;IPOS_STBIO1_MAIN_CONTROLLER_085;IPOS_STBIO1_MAIN_CONTROLLER_086;IPOS_STBIO1_MAIN_CONTROLLER_087;IPOS_STBIO1_MAIN_CONTROLLER_088;IPOS_STBIO1_MAIN_CONTROLLER_089;IPOS_STBIO1_MAIN_CONTROLLER_090;IPOS_STBIO1_MAIN_CONTROLLER_092;IPOS_STBIO1_MAIN_CONTROLLER_093;IPOS_STBIO1_MAIN_CONTROLLER_094;IPOS_STBIO1_MAIN_CONTROLLER_095;IPOS_STBIO1_MAIN_CONTROLLER_096;IPOS_STBIO1_MAIN_CONTROLLER_097;IPOS_STBIO1_MAIN_CONTROLLER_098;IPOS_STBIO1_MAIN_CONTROLLER_099;IPOS_STBIO1_MAIN_CONTROLLER_100;IPOS_STBIO1_MAIN_CONTROLLER_1004;IPOS_STBIO1_MAIN_CONTROLLER_1005;IPOS_STBIO1_MAIN_CONTROLLER_1007;IPOS_STBIO1_MAIN_CONTROLLER_1008;IPOS_STBIO1_MAIN_CONTROLLER_1009;IPOS_STBIO1_MAIN_CONTROLLER_101;IPOS_STBIO1_MAIN_CONTROLLER_1010;IPOS_STBIO1_MAIN_CONTROLLER_1011;IPOS_STBIO1_MAIN_CONTROLLER_102;IPOS_STBIO1_MAIN_CONTROLLER_103;IPOS_STBIO1_MAIN_CONTROLLER_1034;IPOS_STBIO1_MAIN_CONTROLLER_104;IPOS_STBIO1_MAIN_CONTROLLER_105;IPOS_STBIO1_MAIN_CONTROLLER_106;IPOS_STBIO1_MAIN_CONTROLLER_107;IPOS_STBIO1_MAIN_CONTROLLER_108;IPOS_STBIO1_MAIN_CONTROLLER_109;IPOS_STBIO1_MAIN_CONTROLLER_1095;IPOS_STBIO1_MAIN_CONTROLLER_110;IPOS_STBIO1_MAIN_CONTROLLER_1102;IPOS_STBIO1_MAIN_CONTROLLER_1104;IPOS_STBIO1_MAIN_CONTROLLER_1105;IPOS_STBIO1_MAIN_CONTROLLER_111;IPOS_STBIO1_MAIN_CONTROLLER_1116;IPOS_STBIO1_MAIN_CONTROLLER_1118;IPOS_STBIO1_MAIN_CONTROLLER_1119;IPOS_STBIO1_MAIN_CONTROLLER_112;IPOS_STBIO1_MAIN_CONTROLLER_113;IPOS_STBIO1_MAIN_CONTROLLER_1136;IPOS_STBIO1_MAIN_CONTROLLER_1139;IPOS_STBIO1_MAIN_CONTROLLER_1143;IPOS_STBIO1_MAIN_CONTROLLER_115;IPOS_STBIO1_MAIN_CONTROLLER_118;IPOS_STBIO1_MAIN_CONTROLLER_120;IPOS_STBIO1_MAIN_CONTROLLER_121;IPOS_STBIO1_MAIN_CONTROLLER_122;IPOS_STBIO1_MAIN_CONTROLLER_123;IPOS_STBIO1_MAIN_CONTROLLER_124;IPOS_STBIO1_MAIN_CONTROLLER_125;IPOS_STBIO1_MAIN_CONTROLLER_126;IPOS_STBIO1_MAIN_CONTROLLER_127;IPOS_STBIO1_MAIN_CONTROLLER_128;IPOS_STBIO1_MAIN_CONTROLLER_129;IPOS_STBIO1_MAIN_CONTROLLER_132;IPOS_STBIO1_MAIN_CONTROLLER_133;IPOS_STBIO1_MAIN_CONTROLLER_134;IPOS_STBIO1_MAIN_CONTROLLER_137;IPOS_STBIO1_MAIN_CONTROLLER_138;IPOS_STBIO1_MAIN_CONTROLLER_139;IPOS_STBIO1_MAIN_CONTROLLER_140;IPOS_STBIO1_MAIN_CONTROLLER_143;IPOS_STBIO1_MAIN_CONTROLLER_2117;IPOS_STBIO1_MAIN_CONTROLLER_2143;IPOS_STBIO1_MAIN_CONTROLLER_2144;IPOS_STBIO1_MAIN_CONTROLLER_2145;IPOS_STBIO1_MAIN_CONTROLLER_2146;IPOS_STBIO1_MAIN_CONTROLLER_300;IPOS_STBIO1_MAIN_CONTROLLER_3124;IPOS_STBIO1_MAIN_CONTROLLER_3125;IPOS_STBIO1_MAIN_CONTROLLER_3126;IPOS_STBIO1_MAIN_CONTROLLER_3127;IPOS_STBIO1_MAIN_CONTROLLER_3128;IPOS_STBIO1_MAIN_CONTROLLER_3129;IPOS_STBIO1_MAIN_CONTROLLER_3130;IPOS_STBIO1_MAIN_CONTROLLER_3131;IPOS_STBIO1_MAIN_CONTROLLER_4034;IPOS_STBIO1_MAIN_CONTROLLER_4079;IPOS_STBIO1_MAIN_CONTROLLER_4080;IPOS_STBIO1_MAIN_CONTROLLER_4090;IPOS_STBIO1_MAIN_CONTROLLER_4091;IPOS_STBIO1_MAIN_CONTROLLER_436;IPOS_STBIO1_MAIN_CONTROLLER_5004;IPOS_STBIO1_MAIN_CONTROLLER_5005;IPOS_STBIO1_MAIN_CONTROLLER_5015;IPOS_STBIO1_MAIN_CONTROLLER_5016;IPOS_STBIO1_MAIN_CONTROLLER_5080;IPOS_STBIO1_MAIN_CONTROLLER_5091;IPOS_STBIO1_MAIN_CONTROLLER_5092;IPOS_STBIO1_MAIN_CONTROLLER_6059;IPOS_STBIO1_MAIN_CONTROLLER_6070;IPOS_STBIO1_MAIN_CONTROLLER_6098;IPOS_STBIO1_MAIN_CONTROLLER_6129;IPOS_STBIO1_MAIN_CONTROLLER_7095;IPOS_STBIO1_MAIN_CONTROLLER_7135;IPOS_STBIO1_MAIN_CONTROLLER_728;IPOS_STBIO1_MAIN_CONTROLLER_8106;IPOS_STBIO1_MAIN_CONTROLLER_8116;IPOS_STBIO1_MAIN_CONTROLLER_9116;IPOS_STBIO1_MAIN_CONTROLLER_9139</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Digital_IPOS:pad-mux</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>source:dds_stbio1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Digital IPOS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PMU</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Primary source specification: dds_stbio1.pdf</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Approved source ledger</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>31</v>
+      </c>
+      <c r="G8" t="n">
+        <v>357</v>
+      </c>
+      <c r="H8" t="n">
+        <v>326</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>8.683473389355742</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Central source-spec provenance/trace ID coverage; not generated-document Covers or publication gate status</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_0104;DDS_STBIO1_0105;DDS_STBIO1_0106;DDS_STBIO1_0107;DDS_STBIO1_0108;DDS_STBIO1_0109;DDS_STBIO1_0110;DDS_STBIO1_0111;DDS_STBIO1_0112;DDS_STBIO1_0113;DDS_STBIO1_0114;DDS_STBIO1_0115;DDS_STBIO1_1020;DDS_STBIO1_1021;DDS_STBIO1_1022;DDS_STBIO1_1023;DDS_STBIO1_1024;DDS_STBIO1_1025;DDS_STBIO1_1026;DDS_STBIO1_1027;DDS_STBIO1_1050;DDS_STBIO1_1051;DDS_STBIO1_1052;DDS_STBIO1_1053;DDS_STBIO1_1054;DDS_STBIO1_2024;DDS_STBIO1_2025;DDS_STBIO1_2026;DDS_STBIO1_2052;DDS_STBIO1_2053;DDS_STBIO1_2054</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_00000008;DDS_STBIO1_00000102;DDS_STBIO1_00000199;DDS_STBIO1_00000202;DDS_STBIO1_00001199;DDS_STBIO1_0013;DDS_STBIO1_0014;DDS_STBIO1_0015;DDS_STBIO1_0016;DDS_STBIO1_0017;DDS_STBIO1_0018;DDS_STBIO1_0019;DDS_STBIO1_0020;DDS_STBIO1_0021;DDS_STBIO1_0022;DDS_STBIO1_0023;DDS_STBIO1_0024;DDS_STBIO1_0025;DDS_STBIO1_0026;DDS_STBIO1_0027;DDS_STBIO1_0028;DDS_STBIO1_0032;DDS_STBIO1_0033;DDS_STBIO1_0034;DDS_STBIO1_0035;DDS_STBIO1_0036;DDS_STBIO1_0116;DDS_STBIO1_0117;DDS_STBIO1_0118;DDS_STBIO1_0119;DDS_STBIO1_0120;DDS_STBIO1_0121;DDS_STBIO1_0122;DDS_STBIO1_0123;DDS_STBIO1_0124;DDS_STBIO1_0125;DDS_STBIO1_0126;DDS_STBIO1_0127;DDS_STBIO1_0128;DDS_STBIO1_0129;DDS_STBIO1_0130;DDS_STBIO1_0140;DDS_STBIO1_0141;DDS_STBIO1_0142;DDS_STBIO1_0143;DDS_STBIO1_0144;DDS_STBIO1_0145;DDS_STBIO1_0146;DDS_STBIO1_0147;DDS_STBIO1_0148;DDS_STBIO1_0149;DDS_STBIO1_0201;DDS_STBIO1_0202;DDS_STBIO1_0203;DDS_STBIO1_0204;DDS_STBIO1_0206;DDS_STBIO1_0207;DDS_STBIO1_0208;DDS_STBIO1_0209;DDS_STBIO1_0210;DDS_STBIO1_0211;DDS_STBIO1_0212;DDS_STBIO1_0213;DDS_STBIO1_0215;DDS_STBIO1_0216;DDS_STBIO1_0217;DDS_STBIO1_0218;DDS_STBIO1_0219;DDS_STBIO1_0220;DDS_STBIO1_0221;DDS_STBIO1_0222;DDS_STBIO1_0223;DDS_STBIO1_0501;DDS_STBIO1_05010;DDS_STBIO1_05011;DDS_STBIO1_0502;DDS_STBIO1_0503;DDS_STBIO1_0504;DDS_STBIO1_0505;DDS_STBIO1_0507;DDS_STBIO1_0508;DDS_STBIO1_0509;DDS_STBIO1_0699;DDS_STBIO1_0700;DDS_STBIO1_0701;DDS_STBIO1_0702;DDS_STBIO1_1114;DDS_STBIO1_1507;DDS_STBIO1_2507;DDS_STBIO1_3000;DDS_STBIO1_3001;DDS_STBIO1_3002;DDS_STBIO1_3003;DDS_STBIO1_3004;DDS_STBIO1_3005;DDS_STBIO1_3006;DDS_STBIO1_302;DDS_STBIO1_303;DDS_STBIO1_304;DDS_STBIO1_305;DDS_STBIO1_306;DDS_STBIO1_307;DDS_STBIO1_308;DDS_STBIO1_309;DDS_STBIO1_310;DDS_STBIO1_311;DDS_STBIO1_312;DDS_STBIO1_313;DDS_STBIO1_314;DDS_STBIO1_392;DDS_STBIO1_393;DDS_STBIO1_394;DDS_STBIO1_395;DDS_STBIO1_4000;DDS_STBIO1_8000;DDS_STBIO1_8001;DDS_STBIO1_8002;DDS_STBIO1_8003;DDS_STBIO1_8004;DDS_STBIO1_8005;DDS_STBIO1_8006;DDS_STBIO1_8007;DDS_STBIO1_8100;DDS_STBIO1_8101;DDS_STBIO1_8102;DDS_STBIO1_8103;DDS_STBIO1_8104;DDS_STBIO1_8105;DDS_STBIO1_8106;DDS_STBIO1_89455232;DDS_STBIO1_89455261;DDS_STBIO1_89455449;DDS_STBIO1_89456557;DDS_STBIO1_89456975;DDS_STBIO1_89457435;DDS_STBIO1_89457790;DDS_STBIO1_89459082;DDS_STBIO1_9004;DDS_STBIO1_9011;DDS_STBIO1_9012;DDS_STBIO1_9013;DDS_STBIO1_9014;DDS_STBIO1_9017;DDS_STBIO1_9018;DDS_STBIO1_9024;DDS_STBIO1_9027;DDS_STBIO1_9029;DDS_STBIO1_9030;DDS_STBIO1_9031;DDS_STBIO1_9032;DDS_STBIO1_9033;DDS_STBIO1_9034;DDS_STBIO1_9035;DDS_STBIO1_9260;DDS_STBIO1_9261;DDS_STBIO1_9262;DDS_STBIO1_9263;DDS_STBIO1_9300;DDS_STBIO1_9317;DDS_STBIO1_9500;IPOS_STBIO1_MAIN_CONTROLLER_002;IPOS_STBIO1_MAIN_CONTROLLER_004;IPOS_STBIO1_MAIN_CONTROLLER_008;IPOS_STBIO1_MAIN_CONTROLLER_009;IPOS_STBIO1_MAIN_CONTROLLER_010;IPOS_STBIO1_MAIN_CONTROLLER_011;IPOS_STBIO1_MAIN_CONTROLLER_015;IPOS_STBIO1_MAIN_CONTROLLER_0152;IPOS_STBIO1_MAIN_CONTROLLER_016;IPOS_STBIO1_MAIN_CONTROLLER_017;IPOS_STBIO1_MAIN_CONTROLLER_018;IPOS_STBIO1_MAIN_CONTROLLER_019;IPOS_STBIO1_MAIN_CONTROLLER_020;IPOS_STBIO1_MAIN_CONTROLLER_021;IPOS_STBIO1_MAIN_CONTROLLER_022;IPOS_STBIO1_MAIN_CONTROLLER_023;IPOS_STBIO1_MAIN_CONTROLLER_024;IPOS_STBIO1_MAIN_CONTROLLER_026;IPOS_STBIO1_MAIN_CONTROLLER_027;IPOS_STBIO1_MAIN_CONTROLLER_028;IPOS_STBIO1_MAIN_CONTROLLER_029;IPOS_STBIO1_MAIN_CONTROLLER_030;IPOS_STBIO1_MAIN_CONTROLLER_031;IPOS_STBIO1_MAIN_CONTROLLER_032;IPOS_STBIO1_MAIN_CONTROLLER_033;IPOS_STBIO1_MAIN_CONTROLLER_034;IPOS_STBIO1_MAIN_CONTROLLER_035;IPOS_STBIO1_MAIN_CONTROLLER_036;IPOS_STBIO1_MAIN_CONTROLLER_037;IPOS_STBIO1_MAIN_CONTROLLER_038;IPOS_STBIO1_MAIN_CONTROLLER_039;IPOS_STBIO1_MAIN_CONTROLLER_040;IPOS_STBIO1_MAIN_CONTROLLER_043;IPOS_STBIO1_MAIN_CONTROLLER_044;IPOS_STBIO1_MAIN_CONTROLLER_045;IPOS_STBIO1_MAIN_CONTROLLER_047;IPOS_STBIO1_MAIN_CONTROLLER_048;IPOS_STBIO1_MAIN_CONTROLLER_049;IPOS_STBIO1_MAIN_CONTROLLER_051;IPOS_STBIO1_MAIN_CONTROLLER_052;IPOS_STBIO1_MAIN_CONTROLLER_053;IPOS_STBIO1_MAIN_CONTROLLER_054;IPOS_STBIO1_MAIN_CONTROLLER_055;IPOS_STBIO1_MAIN_CONTROLLER_058;IPOS_STBIO1_MAIN_CONTROLLER_059;IPOS_STBIO1_MAIN_CONTROLLER_060;IPOS_STBIO1_MAIN_CONTROLLER_061;IPOS_STBIO1_MAIN_CONTROLLER_062;IPOS_STBIO1_MAIN_CONTROLLER_063;IPOS_STBIO1_MAIN_CONTROLLER_064;IPOS_STBIO1_MAIN_CONTROLLER_072;IPOS_STBIO1_MAIN_CONTROLLER_073;IPOS_STBIO1_MAIN_CONTROLLER_074;IPOS_STBIO1_MAIN_CONTROLLER_075;IPOS_STBIO1_MAIN_CONTROLLER_076;IPOS_STBIO1_MAIN_CONTROLLER_077;IPOS_STBIO1_MAIN_CONTROLLER_078;IPOS_STBIO1_MAIN_CONTROLLER_080;IPOS_STBIO1_MAIN_CONTROLLER_081;IPOS_STBIO1_MAIN_CONTROLLER_082;IPOS_STBIO1_MAIN_CONTROLLER_083;IPOS_STBIO1_MAIN_CONTROLLER_084;IPOS_STBIO1_MAIN_CONTROLLER_085;IPOS_STBIO1_MAIN_CONTROLLER_086;IPOS_STBIO1_MAIN_CONTROLLER_087;IPOS_STBIO1_MAIN_CONTROLLER_088;IPOS_STBIO1_MAIN_CONTROLLER_089;IPOS_STBIO1_MAIN_CONTROLLER_090;IPOS_STBIO1_MAIN_CONTROLLER_092;IPOS_STBIO1_MAIN_CONTROLLER_093;IPOS_STBIO1_MAIN_CONTROLLER_094;IPOS_STBIO1_MAIN_CONTROLLER_095;IPOS_STBIO1_MAIN_CONTROLLER_096;IPOS_STBIO1_MAIN_CONTROLLER_097;IPOS_STBIO1_MAIN_CONTROLLER_098;IPOS_STBIO1_MAIN_CONTROLLER_099;IPOS_STBIO1_MAIN_CONTROLLER_100;IPOS_STBIO1_MAIN_CONTROLLER_1004;IPOS_STBIO1_MAIN_CONTROLLER_1005;IPOS_STBIO1_MAIN_CONTROLLER_1007;IPOS_STBIO1_MAIN_CONTROLLER_1008;IPOS_STBIO1_MAIN_CONTROLLER_1009;IPOS_STBIO1_MAIN_CONTROLLER_101;IPOS_STBIO1_MAIN_CONTROLLER_1010;IPOS_STBIO1_MAIN_CONTROLLER_1011;IPOS_STBIO1_MAIN_CONTROLLER_102;IPOS_STBIO1_MAIN_CONTROLLER_103;IPOS_STBIO1_MAIN_CONTROLLER_1034;IPOS_STBIO1_MAIN_CONTROLLER_104;IPOS_STBIO1_MAIN_CONTROLLER_105;IPOS_STBIO1_MAIN_CONTROLLER_106;IPOS_STBIO1_MAIN_CONTROLLER_107;IPOS_STBIO1_MAIN_CONTROLLER_108;IPOS_STBIO1_MAIN_CONTROLLER_109;IPOS_STBIO1_MAIN_CONTROLLER_1095;IPOS_STBIO1_MAIN_CONTROLLER_110;IPOS_STBIO1_MAIN_CONTROLLER_1102;IPOS_STBIO1_MAIN_CONTROLLER_1104;IPOS_STBIO1_MAIN_CONTROLLER_1105;IPOS_STBIO1_MAIN_CONTROLLER_111;IPOS_STBIO1_MAIN_CONTROLLER_1116;IPOS_STBIO1_MAIN_CONTROLLER_1118;IPOS_STBIO1_MAIN_CONTROLLER_1119;IPOS_STBIO1_MAIN_CONTROLLER_112;IPOS_STBIO1_MAIN_CONTROLLER_113;IPOS_STBIO1_MAIN_CONTROLLER_1136;IPOS_STBIO1_MAIN_CONTROLLER_1139;IPOS_STBIO1_MAIN_CONTROLLER_1143;IPOS_STBIO1_MAIN_CONTROLLER_115;IPOS_STBIO1_MAIN_CONTROLLER_118;IPOS_STBIO1_MAIN_CONTROLLER_120;IPOS_STBIO1_MAIN_CONTROLLER_121;IPOS_STBIO1_MAIN_CONTROLLER_122;IPOS_STBIO1_MAIN_CONTROLLER_123;IPOS_STBIO1_MAIN_CONTROLLER_124;IPOS_STBIO1_MAIN_CONTROLLER_125;IPOS_STBIO1_MAIN_CONTROLLER_126;IPOS_STBIO1_MAIN_CONTROLLER_127;IPOS_STBIO1_MAIN_CONTROLLER_128;IPOS_STBIO1_MAIN_CONTROLLER_129;IPOS_STBIO1_MAIN_CONTROLLER_132;IPOS_STBIO1_MAIN_CONTROLLER_133;IPOS_STBIO1_MAIN_CONTROLLER_134;IPOS_STBIO1_MAIN_CONTROLLER_137;IPOS_STBIO1_MAIN_CONTROLLER_138;IPOS_STBIO1_MAIN_CONTROLLER_139;IPOS_STBIO1_MAIN_CONTROLLER_140;IPOS_STBIO1_MAIN_CONTROLLER_143;IPOS_STBIO1_MAIN_CONTROLLER_2117;IPOS_STBIO1_MAIN_CONTROLLER_2143;IPOS_STBIO1_MAIN_CONTROLLER_2144;IPOS_STBIO1_MAIN_CONTROLLER_2145;IPOS_STBIO1_MAIN_CONTROLLER_2146;IPOS_STBIO1_MAIN_CONTROLLER_300;IPOS_STBIO1_MAIN_CONTROLLER_3124;IPOS_STBIO1_MAIN_CONTROLLER_3125;IPOS_STBIO1_MAIN_CONTROLLER_3126;IPOS_STBIO1_MAIN_CONTROLLER_3127;IPOS_STBIO1_MAIN_CONTROLLER_3128;IPOS_STBIO1_MAIN_CONTROLLER_3129;IPOS_STBIO1_MAIN_CONTROLLER_3130;IPOS_STBIO1_MAIN_CONTROLLER_3131;IPOS_STBIO1_MAIN_CONTROLLER_4034;IPOS_STBIO1_MAIN_CONTROLLER_4079;IPOS_STBIO1_MAIN_CONTROLLER_4080;IPOS_STBIO1_MAIN_CONTROLLER_4090;IPOS_STBIO1_MAIN_CONTROLLER_4091;IPOS_STBIO1_MAIN_CONTROLLER_436;IPOS_STBIO1_MAIN_CONTROLLER_5004;IPOS_STBIO1_MAIN_CONTROLLER_5005;IPOS_STBIO1_MAIN_CONTROLLER_5015;IPOS_STBIO1_MAIN_CONTROLLER_5016;IPOS_STBIO1_MAIN_CONTROLLER_5080;IPOS_STBIO1_MAIN_CONTROLLER_5091;IPOS_STBIO1_MAIN_CONTROLLER_5092;IPOS_STBIO1_MAIN_CONTROLLER_6059;IPOS_STBIO1_MAIN_CONTROLLER_6070;IPOS_STBIO1_MAIN_CONTROLLER_6098;IPOS_STBIO1_MAIN_CONTROLLER_6129;IPOS_STBIO1_MAIN_CONTROLLER_7095;IPOS_STBIO1_MAIN_CONTROLLER_7135;IPOS_STBIO1_MAIN_CONTROLLER_728;IPOS_STBIO1_MAIN_CONTROLLER_8106;IPOS_STBIO1_MAIN_CONTROLLER_8116;IPOS_STBIO1_MAIN_CONTROLLER_9116;IPOS_STBIO1_MAIN_CONTROLLER_9139</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Digital_IPOS:pmu</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>source:dds_stbio1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Digital IPOS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Regmap</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Primary source specification: dds_stbio1.pdf</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Approved source ledger</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>357</v>
+      </c>
+      <c r="H9" t="n">
+        <v>349</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>2.240896358543417</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Central source-spec provenance/trace ID coverage; not generated-document Covers or publication gate status</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_3000;DDS_STBIO1_3001;DDS_STBIO1_3002;DDS_STBIO1_3003;DDS_STBIO1_3004;DDS_STBIO1_3005;DDS_STBIO1_3006;DDS_STBIO1_4000</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_00000008;DDS_STBIO1_00000102;DDS_STBIO1_00000199;DDS_STBIO1_00000202;DDS_STBIO1_00001199;DDS_STBIO1_0013;DDS_STBIO1_0014;DDS_STBIO1_0015;DDS_STBIO1_0016;DDS_STBIO1_0017;DDS_STBIO1_0018;DDS_STBIO1_0019;DDS_STBIO1_0020;DDS_STBIO1_0021;DDS_STBIO1_0022;DDS_STBIO1_0023;DDS_STBIO1_0024;DDS_STBIO1_0025;DDS_STBIO1_0026;DDS_STBIO1_0027;DDS_STBIO1_0028;DDS_STBIO1_0032;DDS_STBIO1_0033;DDS_STBIO1_0034;DDS_STBIO1_0035;DDS_STBIO1_0036;DDS_STBIO1_0104;DDS_STBIO1_0105;DDS_STBIO1_0106;DDS_STBIO1_0107;DDS_STBIO1_0108;DDS_STBIO1_0109;DDS_STBIO1_0110;DDS_STBIO1_0111;DDS_STBIO1_0112;DDS_STBIO1_0113;DDS_STBIO1_0114;DDS_STBIO1_0115;DDS_STBIO1_0116;DDS_STBIO1_0117;DDS_STBIO1_0118;DDS_STBIO1_0119;DDS_STBIO1_0120;DDS_STBIO1_0121;DDS_STBIO1_0122;DDS_STBIO1_0123;DDS_STBIO1_0124;DDS_STBIO1_0125;DDS_STBIO1_0126;DDS_STBIO1_0127;DDS_STBIO1_0128;DDS_STBIO1_0129;DDS_STBIO1_0130;DDS_STBIO1_0140;DDS_STBIO1_0141;DDS_STBIO1_0142;DDS_STBIO1_0143;DDS_STBIO1_0144;DDS_STBIO1_0145;DDS_STBIO1_0146;DDS_STBIO1_0147;DDS_STBIO1_0148;DDS_STBIO1_0149;DDS_STBIO1_0201;DDS_STBIO1_0202;DDS_STBIO1_0203;DDS_STBIO1_0204;DDS_STBIO1_0206;DDS_STBIO1_0207;DDS_STBIO1_0208;DDS_STBIO1_0209;DDS_STBIO1_0210;DDS_STBIO1_0211;DDS_STBIO1_0212;DDS_STBIO1_0213;DDS_STBIO1_0215;DDS_STBIO1_0216;DDS_STBIO1_0217;DDS_STBIO1_0218;DDS_STBIO1_0219;DDS_STBIO1_0220;DDS_STBIO1_0221;DDS_STBIO1_0222;DDS_STBIO1_0223;DDS_STBIO1_0501;DDS_STBIO1_05010;DDS_STBIO1_05011;DDS_STBIO1_0502;DDS_STBIO1_0503;DDS_STBIO1_0504;DDS_STBIO1_0505;DDS_STBIO1_0507;DDS_STBIO1_0508;DDS_STBIO1_0509;DDS_STBIO1_0699;DDS_STBIO1_0700;DDS_STBIO1_0701;DDS_STBIO1_0702;DDS_STBIO1_1020;DDS_STBIO1_1021;DDS_STBIO1_1022;DDS_STBIO1_1023;DDS_STBIO1_1024;DDS_STBIO1_1025;DDS_STBIO1_1026;DDS_STBIO1_1027;DDS_STBIO1_1050;DDS_STBIO1_1051;DDS_STBIO1_1052;DDS_STBIO1_1053;DDS_STBIO1_1054;DDS_STBIO1_1114;DDS_STBIO1_1507;DDS_STBIO1_2024;DDS_STBIO1_2025;DDS_STBIO1_2026;DDS_STBIO1_2052;DDS_STBIO1_2053;DDS_STBIO1_2054;DDS_STBIO1_2507;DDS_STBIO1_302;DDS_STBIO1_303;DDS_STBIO1_304;DDS_STBIO1_305;DDS_STBIO1_306;DDS_STBIO1_307;DDS_STBIO1_308;DDS_STBIO1_309;DDS_STBIO1_310;DDS_STBIO1_311;DDS_STBIO1_312;DDS_STBIO1_313;DDS_STBIO1_314;DDS_STBIO1_392;DDS_STBIO1_393;DDS_STBIO1_394;DDS_STBIO1_395;DDS_STBIO1_8000;DDS_STBIO1_8001;DDS_STBIO1_8002;DDS_STBIO1_8003;DDS_STBIO1_8004;DDS_STBIO1_8005;DDS_STBIO1_8006;DDS_STBIO1_8007;DDS_STBIO1_8100;DDS_STBIO1_8101;DDS_STBIO1_8102;DDS_STBIO1_8103;DDS_STBIO1_8104;DDS_STBIO1_8105;DDS_STBIO1_8106;DDS_STBIO1_89455232;DDS_STBIO1_89455261;DDS_STBIO1_89455449;DDS_STBIO1_89456557;DDS_STBIO1_89456975;DDS_STBIO1_89457435;DDS_STBIO1_89457790;DDS_STBIO1_89459082;DDS_STBIO1_9004;DDS_STBIO1_9011;DDS_STBIO1_9012;DDS_STBIO1_9013;DDS_STBIO1_9014;DDS_STBIO1_9017;DDS_STBIO1_9018;DDS_STBIO1_9024;DDS_STBIO1_9027;DDS_STBIO1_9029;DDS_STBIO1_9030;DDS_STBIO1_9031;DDS_STBIO1_9032;DDS_STBIO1_9033;DDS_STBIO1_9034;DDS_STBIO1_9035;DDS_STBIO1_9260;DDS_STBIO1_9261;DDS_STBIO1_9262;DDS_STBIO1_9263;DDS_STBIO1_9300;DDS_STBIO1_9317;DDS_STBIO1_9500;IPOS_STBIO1_MAIN_CONTROLLER_002;IPOS_STBIO1_MAIN_CONTROLLER_004;IPOS_STBIO1_MAIN_CONTROLLER_008;IPOS_STBIO1_MAIN_CONTROLLER_009;IPOS_STBIO1_MAIN_CONTROLLER_010;IPOS_STBIO1_MAIN_CONTROLLER_011;IPOS_STBIO1_MAIN_CONTROLLER_015;IPOS_STBIO1_MAIN_CONTROLLER_0152;IPOS_STBIO1_MAIN_CONTROLLER_016;IPOS_STBIO1_MAIN_CONTROLLER_017;IPOS_STBIO1_MAIN_CONTROLLER_018;IPOS_STBIO1_MAIN_CONTROLLER_019;IPOS_STBIO1_MAIN_CONTROLLER_020;IPOS_STBIO1_MAIN_CONTROLLER_021;IPOS_STBIO1_MAIN_CONTROLLER_022;IPOS_STBIO1_MAIN_CONTROLLER_023;IPOS_STBIO1_MAIN_CONTROLLER_024;IPOS_STBIO1_MAIN_CONTROLLER_026;IPOS_STBIO1_MAIN_CONTROLLER_027;IPOS_STBIO1_MAIN_CONTROLLER_028;IPOS_STBIO1_MAIN_CONTROLLER_029;IPOS_STBIO1_MAIN_CONTROLLER_030;IPOS_STBIO1_MAIN_CONTROLLER_031;IPOS_STBIO1_MAIN_CONTROLLER_032;IPOS_STBIO1_MAIN_CONTROLLER_033;IPOS_STBIO1_MAIN_CONTROLLER_034;IPOS_STBIO1_MAIN_CONTROLLER_035;IPOS_STBIO1_MAIN_CONTROLLER_036;IPOS_STBIO1_MAIN_CONTROLLER_037;IPOS_STBIO1_MAIN_CONTROLLER_038;IPOS_STBIO1_MAIN_CONTROLLER_039;IPOS_STBIO1_MAIN_CONTROLLER_040;IPOS_STBIO1_MAIN_CONTROLLER_043;IPOS_STBIO1_MAIN_CONTROLLER_044;IPOS_STBIO1_MAIN_CONTROLLER_045;IPOS_STBIO1_MAIN_CONTROLLER_047;IPOS_STBIO1_MAIN_CONTROLLER_048;IPOS_STBIO1_MAIN_CONTROLLER_049;IPOS_STBIO1_MAIN_CONTROLLER_051;IPOS_STBIO1_MAIN_CONTROLLER_052;IPOS_STBIO1_MAIN_CONTROLLER_053;IPOS_STBIO1_MAIN_CONTROLLER_054;IPOS_STBIO1_MAIN_CONTROLLER_055;IPOS_STBIO1_MAIN_CONTROLLER_058;IPOS_STBIO1_MAIN_CONTROLLER_059;IPOS_STBIO1_MAIN_CONTROLLER_060;IPOS_STBIO1_MAIN_CONTROLLER_061;IPOS_STBIO1_MAIN_CONTROLLER_062;IPOS_STBIO1_MAIN_CONTROLLER_063;IPOS_STBIO1_MAIN_CONTROLLER_064;IPOS_STBIO1_MAIN_CONTROLLER_072;IPOS_STBIO1_MAIN_CONTROLLER_073;IPOS_STBIO1_MAIN_CONTROLLER_074;IPOS_STBIO1_MAIN_CONTROLLER_075;IPOS_STBIO1_MAIN_CONTROLLER_076;IPOS_STBIO1_MAIN_CONTROLLER_077;IPOS_STBIO1_MAIN_CONTROLLER_078;IPOS_STBIO1_MAIN_CONTROLLER_080;IPOS_STBIO1_MAIN_CONTROLLER_081;IPOS_STBIO1_MAIN_CONTROLLER_082;IPOS_STBIO1_MAIN_CONTROLLER_083;IPOS_STBIO1_MAIN_CONTROLLER_084;IPOS_STBIO1_MAIN_CONTROLLER_085;IPOS_STBIO1_MAIN_CONTROLLER_086;IPOS_STBIO1_MAIN_CONTROLLER_087;IPOS_STBIO1_MAIN_CONTROLLER_088;IPOS_STBIO1_MAIN_CONTROLLER_089;IPOS_STBIO1_MAIN_CONTROLLER_090;IPOS_STBIO1_MAIN_CONTROLLER_092;IPOS_STBIO1_MAIN_CONTROLLER_093;IPOS_STBIO1_MAIN_CONTROLLER_094;IPOS_STBIO1_MAIN_CONTROLLER_095;IPOS_STBIO1_MAIN_CONTROLLER_096;IPOS_STBIO1_MAIN_CONTROLLER_097;IPOS_STBIO1_MAIN_CONTROLLER_098;IPOS_STBIO1_MAIN_CONTROLLER_099;IPOS_STBIO1_MAIN_CONTROLLER_100;IPOS_STBIO1_MAIN_CONTROLLER_1004;IPOS_STBIO1_MAIN_CONTROLLER_1005;IPOS_STBIO1_MAIN_CONTROLLER_1007;IPOS_STBIO1_MAIN_CONTROLLER_1008;IPOS_STBIO1_MAIN_CONTROLLER_1009;IPOS_STBIO1_MAIN_CONTROLLER_101;IPOS_STBIO1_MAIN_CONTROLLER_1010;IPOS_STBIO1_MAIN_CONTROLLER_1011;IPOS_STBIO1_MAIN_CONTROLLER_102;IPOS_STBIO1_MAIN_CONTROLLER_103;IPOS_STBIO1_MAIN_CONTROLLER_1034;IPOS_STBIO1_MAIN_CONTROLLER_104;IPOS_STBIO1_MAIN_CONTROLLER_105;IPOS_STBIO1_MAIN_CONTROLLER_106;IPOS_STBIO1_MAIN_CONTROLLER_107;IPOS_STBIO1_MAIN_CONTROLLER_108;IPOS_STBIO1_MAIN_CONTROLLER_109;IPOS_STBIO1_MAIN_CONTROLLER_1095;IPOS_STBIO1_MAIN_CONTROLLER_110;IPOS_STBIO1_MAIN_CONTROLLER_1102;IPOS_STBIO1_MAIN_CONTROLLER_1104;IPOS_STBIO1_MAIN_CONTROLLER_1105;IPOS_STBIO1_MAIN_CONTROLLER_111;IPOS_STBIO1_MAIN_CONTROLLER_1116;IPOS_STBIO1_MAIN_CONTROLLER_1118;IPOS_STBIO1_MAIN_CONTROLLER_1119;IPOS_STBIO1_MAIN_CONTROLLER_112;IPOS_STBIO1_MAIN_CONTROLLER_113;IPOS_STBIO1_MAIN_CONTROLLER_1136;IPOS_STBIO1_MAIN_CONTROLLER_1139;IPOS_STBIO1_MAIN_CONTROLLER_1143;IPOS_STBIO1_MAIN_CONTROLLER_115;IPOS_STBIO1_MAIN_CONTROLLER_118;IPOS_STBIO1_MAIN_CONTROLLER_120;IPOS_STBIO1_MAIN_CONTROLLER_121;IPOS_STBIO1_MAIN_CONTROLLER_122;IPOS_STBIO1_MAIN_CONTROLLER_123;IPOS_STBIO1_MAIN_CONTROLLER_124;IPOS_STBIO1_MAIN_CONTROLLER_125;IPOS_STBIO1_MAIN_CONTROLLER_126;IPOS_STBIO1_MAIN_CONTROLLER_127;IPOS_STBIO1_MAIN_CONTROLLER_128;IPOS_STBIO1_MAIN_CONTROLLER_129;IPOS_STBIO1_MAIN_CONTROLLER_132;IPOS_STBIO1_MAIN_CONTROLLER_133;IPOS_STBIO1_MAIN_CONTROLLER_134;IPOS_STBIO1_MAIN_CONTROLLER_137;IPOS_STBIO1_MAIN_CONTROLLER_138;IPOS_STBIO1_MAIN_CONTROLLER_139;IPOS_STBIO1_MAIN_CONTROLLER_140;IPOS_STBIO1_MAIN_CONTROLLER_143;IPOS_STBIO1_MAIN_CONTROLLER_2117;IPOS_STBIO1_MAIN_CONTROLLER_2143;IPOS_STBIO1_MAIN_CONTROLLER_2144;IPOS_STBIO1_MAIN_CONTROLLER_2145;IPOS_STBIO1_MAIN_CONTROLLER_2146;IPOS_STBIO1_MAIN_CONTROLLER_300;IPOS_STBIO1_MAIN_CONTROLLER_3124;IPOS_STBIO1_MAIN_CONTROLLER_3125;IPOS_STBIO1_MAIN_CONTROLLER_3126;IPOS_STBIO1_MAIN_CONTROLLER_3127;IPOS_STBIO1_MAIN_CONTROLLER_3128;IPOS_STBIO1_MAIN_CONTROLLER_3129;IPOS_STBIO1_MAIN_CONTROLLER_3130;IPOS_STBIO1_MAIN_CONTROLLER_3131;IPOS_STBIO1_MAIN_CONTROLLER_4034;IPOS_STBIO1_MAIN_CONTROLLER_4079;IPOS_STBIO1_MAIN_CONTROLLER_4080;IPOS_STBIO1_MAIN_CONTROLLER_4090;IPOS_STBIO1_MAIN_CONTROLLER_4091;IPOS_STBIO1_MAIN_CONTROLLER_436;IPOS_STBIO1_MAIN_CONTROLLER_5004;IPOS_STBIO1_MAIN_CONTROLLER_5005;IPOS_STBIO1_MAIN_CONTROLLER_5015;IPOS_STBIO1_MAIN_CONTROLLER_5016;IPOS_STBIO1_MAIN_CONTROLLER_5080;IPOS_STBIO1_MAIN_CONTROLLER_5091;IPOS_STBIO1_MAIN_CONTROLLER_5092;IPOS_STBIO1_MAIN_CONTROLLER_6059;IPOS_STBIO1_MAIN_CONTROLLER_6070;IPOS_STBIO1_MAIN_CONTROLLER_6098;IPOS_STBIO1_MAIN_CONTROLLER_6129;IPOS_STBIO1_MAIN_CONTROLLER_7095;IPOS_STBIO1_MAIN_CONTROLLER_7135;IPOS_STBIO1_MAIN_CONTROLLER_728;IPOS_STBIO1_MAIN_CONTROLLER_8106;IPOS_STBIO1_MAIN_CONTROLLER_8116;IPOS_STBIO1_MAIN_CONTROLLER_9116;IPOS_STBIO1_MAIN_CONTROLLER_9139</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Digital_IPOS:regmap</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>source:dds_stbio1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Digital IPOS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sensor-Hub</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Primary source specification: dds_stbio1.pdf</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Approved source ledger</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>18</v>
+      </c>
+      <c r="G10" t="n">
+        <v>357</v>
+      </c>
+      <c r="H10" t="n">
+        <v>339</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>5.042016806722689</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Central source-spec provenance/trace ID coverage; not generated-document Covers or publication gate status</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_9017;DDS_STBIO1_9018;DDS_STBIO1_9024;DDS_STBIO1_9027;DDS_STBIO1_9029;DDS_STBIO1_9030;DDS_STBIO1_9031;DDS_STBIO1_9032;DDS_STBIO1_9033;DDS_STBIO1_9034;DDS_STBIO1_9035;DDS_STBIO1_9260;DDS_STBIO1_9261;DDS_STBIO1_9262;DDS_STBIO1_9263;DDS_STBIO1_9300;DDS_STBIO1_9317;DDS_STBIO1_9500</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_00000008;DDS_STBIO1_00000102;DDS_STBIO1_00000199;DDS_STBIO1_00000202;DDS_STBIO1_00001199;DDS_STBIO1_0013;DDS_STBIO1_0014;DDS_STBIO1_0015;DDS_STBIO1_0016;DDS_STBIO1_0017;DDS_STBIO1_0018;DDS_STBIO1_0019;DDS_STBIO1_0020;DDS_STBIO1_0021;DDS_STBIO1_0022;DDS_STBIO1_0023;DDS_STBIO1_0024;DDS_STBIO1_0025;DDS_STBIO1_0026;DDS_STBIO1_0027;DDS_STBIO1_0028;DDS_STBIO1_0032;DDS_STBIO1_0033;DDS_STBIO1_0034;DDS_STBIO1_0035;DDS_STBIO1_0036;DDS_STBIO1_0104;DDS_STBIO1_0105;DDS_STBIO1_0106;DDS_STBIO1_0107;DDS_STBIO1_0108;DDS_STBIO1_0109;DDS_STBIO1_0110;DDS_STBIO1_0111;DDS_STBIO1_0112;DDS_STBIO1_0113;DDS_STBIO1_0114;DDS_STBIO1_0115;DDS_STBIO1_0116;DDS_STBIO1_0117;DDS_STBIO1_0118;DDS_STBIO1_0119;DDS_STBIO1_0120;DDS_STBIO1_0121;DDS_STBIO1_0122;DDS_STBIO1_0123;DDS_STBIO1_0124;DDS_STBIO1_0125;DDS_STBIO1_0126;DDS_STBIO1_0127;DDS_STBIO1_0128;DDS_STBIO1_0129;DDS_STBIO1_0130;DDS_STBIO1_0140;DDS_STBIO1_0141;DDS_STBIO1_0142;DDS_STBIO1_0143;DDS_STBIO1_0144;DDS_STBIO1_0145;DDS_STBIO1_0146;DDS_STBIO1_0147;DDS_STBIO1_0148;DDS_STBIO1_0149;DDS_STBIO1_0201;DDS_STBIO1_0202;DDS_STBIO1_0203;DDS_STBIO1_0204;DDS_STBIO1_0206;DDS_STBIO1_0207;DDS_STBIO1_0208;DDS_STBIO1_0209;DDS_STBIO1_0210;DDS_STBIO1_0211;DDS_STBIO1_0212;DDS_STBIO1_0213;DDS_STBIO1_0215;DDS_STBIO1_0216;DDS_STBIO1_0217;DDS_STBIO1_0218;DDS_STBIO1_0219;DDS_STBIO1_0220;DDS_STBIO1_0221;DDS_STBIO1_0222;DDS_STBIO1_0223;DDS_STBIO1_0501;DDS_STBIO1_05010;DDS_STBIO1_05011;DDS_STBIO1_0502;DDS_STBIO1_0503;DDS_STBIO1_0504;DDS_STBIO1_0505;DDS_STBIO1_0507;DDS_STBIO1_0508;DDS_STBIO1_0509;DDS_STBIO1_0699;DDS_STBIO1_0700;DDS_STBIO1_0701;DDS_STBIO1_0702;DDS_STBIO1_1020;DDS_STBIO1_1021;DDS_STBIO1_1022;DDS_STBIO1_1023;DDS_STBIO1_1024;DDS_STBIO1_1025;DDS_STBIO1_1026;DDS_STBIO1_1027;DDS_STBIO1_1050;DDS_STBIO1_1051;DDS_STBIO1_1052;DDS_STBIO1_1053;DDS_STBIO1_1054;DDS_STBIO1_1114;DDS_STBIO1_1507;DDS_STBIO1_2024;DDS_STBIO1_2025;DDS_STBIO1_2026;DDS_STBIO1_2052;DDS_STBIO1_2053;DDS_STBIO1_2054;DDS_STBIO1_2507;DDS_STBIO1_3000;DDS_STBIO1_3001;DDS_STBIO1_3002;DDS_STBIO1_3003;DDS_STBIO1_3004;DDS_STBIO1_3005;DDS_STBIO1_3006;DDS_STBIO1_302;DDS_STBIO1_303;DDS_STBIO1_304;DDS_STBIO1_305;DDS_STBIO1_306;DDS_STBIO1_307;DDS_STBIO1_308;DDS_STBIO1_309;DDS_STBIO1_310;DDS_STBIO1_311;DDS_STBIO1_312;DDS_STBIO1_313;DDS_STBIO1_314;DDS_STBIO1_392;DDS_STBIO1_393;DDS_STBIO1_394;DDS_STBIO1_395;DDS_STBIO1_4000;DDS_STBIO1_8000;DDS_STBIO1_8001;DDS_STBIO1_8002;DDS_STBIO1_8003;DDS_STBIO1_8004;DDS_STBIO1_8005;DDS_STBIO1_8006;DDS_STBIO1_8007;DDS_STBIO1_8100;DDS_STBIO1_8101;DDS_STBIO1_8102;DDS_STBIO1_8103;DDS_STBIO1_8104;DDS_STBIO1_8105;DDS_STBIO1_8106;DDS_STBIO1_89455232;DDS_STBIO1_89455261;DDS_STBIO1_89455449;DDS_STBIO1_89456557;DDS_STBIO1_89456975;DDS_STBIO1_89457435;DDS_STBIO1_89457790;DDS_STBIO1_89459082;DDS_STBIO1_9004;DDS_STBIO1_9011;DDS_STBIO1_9012;DDS_STBIO1_9013;DDS_STBIO1_9014;IPOS_STBIO1_MAIN_CONTROLLER_002;IPOS_STBIO1_MAIN_CONTROLLER_004;IPOS_STBIO1_MAIN_CONTROLLER_008;IPOS_STBIO1_MAIN_CONTROLLER_009;IPOS_STBIO1_MAIN_CONTROLLER_010;IPOS_STBIO1_MAIN_CONTROLLER_011;IPOS_STBIO1_MAIN_CONTROLLER_015;IPOS_STBIO1_MAIN_CONTROLLER_0152;IPOS_STBIO1_MAIN_CONTROLLER_016;IPOS_STBIO1_MAIN_CONTROLLER_017;IPOS_STBIO1_MAIN_CONTROLLER_018;IPOS_STBIO1_MAIN_CONTROLLER_019;IPOS_STBIO1_MAIN_CONTROLLER_020;IPOS_STBIO1_MAIN_CONTROLLER_021;IPOS_STBIO1_MAIN_CONTROLLER_022;IPOS_STBIO1_MAIN_CONTROLLER_023;IPOS_STBIO1_MAIN_CONTROLLER_024;IPOS_STBIO1_MAIN_CONTROLLER_026;IPOS_STBIO1_MAIN_CONTROLLER_027;IPOS_STBIO1_MAIN_CONTROLLER_028;IPOS_STBIO1_MAIN_CONTROLLER_029;IPOS_STBIO1_MAIN_CONTROLLER_030;IPOS_STBIO1_MAIN_CONTROLLER_031;IPOS_STBIO1_MAIN_CONTROLLER_032;IPOS_STBIO1_MAIN_CONTROLLER_033;IPOS_STBIO1_MAIN_CONTROLLER_034;IPOS_STBIO1_MAIN_CONTROLLER_035;IPOS_STBIO1_MAIN_CONTROLLER_036;IPOS_STBIO1_MAIN_CONTROLLER_037;IPOS_STBIO1_MAIN_CONTROLLER_038;IPOS_STBIO1_MAIN_CONTROLLER_039;IPOS_STBIO1_MAIN_CONTROLLER_040;IPOS_STBIO1_MAIN_CONTROLLER_043;IPOS_STBIO1_MAIN_CONTROLLER_044;IPOS_STBIO1_MAIN_CONTROLLER_045;IPOS_STBIO1_MAIN_CONTROLLER_047;IPOS_STBIO1_MAIN_CONTROLLER_048;IPOS_STBIO1_MAIN_CONTROLLER_049;IPOS_STBIO1_MAIN_CONTROLLER_051;IPOS_STBIO1_MAIN_CONTROLLER_052;IPOS_STBIO1_MAIN_CONTROLLER_053;IPOS_STBIO1_MAIN_CONTROLLER_054;IPOS_STBIO1_MAIN_CONTROLLER_055;IPOS_STBIO1_MAIN_CONTROLLER_058;IPOS_STBIO1_MAIN_CONTROLLER_059;IPOS_STBIO1_MAIN_CONTROLLER_060;IPOS_STBIO1_MAIN_CONTROLLER_061;IPOS_STBIO1_MAIN_CONTROLLER_062;IPOS_STBIO1_MAIN_CONTROLLER_063;IPOS_STBIO1_MAIN_CONTROLLER_064;IPOS_STBIO1_MAIN_CONTROLLER_072;IPOS_STBIO1_MAIN_CONTROLLER_073;IPOS_STBIO1_MAIN_CONTROLLER_074;IPOS_STBIO1_MAIN_CONTROLLER_075;IPOS_STBIO1_MAIN_CONTROLLER_076;IPOS_STBIO1_MAIN_CONTROLLER_077;IPOS_STBIO1_MAIN_CONTROLLER_078;IPOS_STBIO1_MAIN_CONTROLLER_080;IPOS_STBIO1_MAIN_CONTROLLER_081;IPOS_STBIO1_MAIN_CONTROLLER_082;IPOS_STBIO1_MAIN_CONTROLLER_083;IPOS_STBIO1_MAIN_CONTROLLER_084;IPOS_STBIO1_MAIN_CONTROLLER_085;IPOS_STBIO1_MAIN_CONTROLLER_086;IPOS_STBIO1_MAIN_CONTROLLER_087;IPOS_STBIO1_MAIN_CONTROLLER_088;IPOS_STBIO1_MAIN_CONTROLLER_089;IPOS_STBIO1_MAIN_CONTROLLER_090;IPOS_STBIO1_MAIN_CONTROLLER_092;IPOS_STBIO1_MAIN_CONTROLLER_093;IPOS_STBIO1_MAIN_CONTROLLER_094;IPOS_STBIO1_MAIN_CONTROLLER_095;IPOS_STBIO1_MAIN_CONTROLLER_096;IPOS_STBIO1_MAIN_CONTROLLER_097;IPOS_STBIO1_MAIN_CONTROLLER_098;IPOS_STBIO1_MAIN_CONTROLLER_099;IPOS_STBIO1_MAIN_CONTROLLER_100;IPOS_STBIO1_MAIN_CONTROLLER_1004;IPOS_STBIO1_MAIN_CONTROLLER_1005;IPOS_STBIO1_MAIN_CONTROLLER_1007;IPOS_STBIO1_MAIN_CONTROLLER_1008;IPOS_STBIO1_MAIN_CONTROLLER_1009;IPOS_STBIO1_MAIN_CONTROLLER_101;IPOS_STBIO1_MAIN_CONTROLLER_1010;IPOS_STBIO1_MAIN_CONTROLLER_1011;IPOS_STBIO1_MAIN_CONTROLLER_102;IPOS_STBIO1_MAIN_CONTROLLER_103;IPOS_STBIO1_MAIN_CONTROLLER_1034;IPOS_STBIO1_MAIN_CONTROLLER_104;IPOS_STBIO1_MAIN_CONTROLLER_105;IPOS_STBIO1_MAIN_CONTROLLER_106;IPOS_STBIO1_MAIN_CONTROLLER_107;IPOS_STBIO1_MAIN_CONTROLLER_108;IPOS_STBIO1_MAIN_CONTROLLER_109;IPOS_STBIO1_MAIN_CONTROLLER_1095;IPOS_STBIO1_MAIN_CONTROLLER_110;IPOS_STBIO1_MAIN_CONTROLLER_1102;IPOS_STBIO1_MAIN_CONTROLLER_1104;IPOS_STBIO1_MAIN_CONTROLLER_1105;IPOS_STBIO1_MAIN_CONTROLLER_111;IPOS_STBIO1_MAIN_CONTROLLER_1116;IPOS_STBIO1_MAIN_CONTROLLER_1118;IPOS_STBIO1_MAIN_CONTROLLER_1119;IPOS_STBIO1_MAIN_CONTROLLER_112;IPOS_STBIO1_MAIN_CONTROLLER_113;IPOS_STBIO1_MAIN_CONTROLLER_1136;IPOS_STBIO1_MAIN_CONTROLLER_1139;IPOS_STBIO1_MAIN_CONTROLLER_1143;IPOS_STBIO1_MAIN_CONTROLLER_115;IPOS_STBIO1_MAIN_CONTROLLER_118;IPOS_STBIO1_MAIN_CONTROLLER_120;IPOS_STBIO1_MAIN_CONTROLLER_121;IPOS_STBIO1_MAIN_CONTROLLER_122;IPOS_STBIO1_MAIN_CONTROLLER_123;IPOS_STBIO1_MAIN_CONTROLLER_124;IPOS_STBIO1_MAIN_CONTROLLER_125;IPOS_STBIO1_MAIN_CONTROLLER_126;IPOS_STBIO1_MAIN_CONTROLLER_127;IPOS_STBIO1_MAIN_CONTROLLER_128;IPOS_STBIO1_MAIN_CONTROLLER_129;IPOS_STBIO1_MAIN_CONTROLLER_132;IPOS_STBIO1_MAIN_CONTROLLER_133;IPOS_STBIO1_MAIN_CONTROLLER_134;IPOS_STBIO1_MAIN_CONTROLLER_137;IPOS_STBIO1_MAIN_CONTROLLER_138;IPOS_STBIO1_MAIN_CONTROLLER_139;IPOS_STBIO1_MAIN_CONTROLLER_140;IPOS_STBIO1_MAIN_CONTROLLER_143;IPOS_STBIO1_MAIN_CONTROLLER_2117;IPOS_STBIO1_MAIN_CONTROLLER_2143;IPOS_STBIO1_MAIN_CONTROLLER_2144;IPOS_STBIO1_MAIN_CONTROLLER_2145;IPOS_STBIO1_MAIN_CONTROLLER_2146;IPOS_STBIO1_MAIN_CONTROLLER_300;IPOS_STBIO1_MAIN_CONTROLLER_3124;IPOS_STBIO1_MAIN_CONTROLLER_3125;IPOS_STBIO1_MAIN_CONTROLLER_3126;IPOS_STBIO1_MAIN_CONTROLLER_3127;IPOS_STBIO1_MAIN_CONTROLLER_3128;IPOS_STBIO1_MAIN_CONTROLLER_3129;IPOS_STBIO1_MAIN_CONTROLLER_3130;IPOS_STBIO1_MAIN_CONTROLLER_3131;IPOS_STBIO1_MAIN_CONTROLLER_4034;IPOS_STBIO1_MAIN_CONTROLLER_4079;IPOS_STBIO1_MAIN_CONTROLLER_4080;IPOS_STBIO1_MAIN_CONTROLLER_4090;IPOS_STBIO1_MAIN_CONTROLLER_4091;IPOS_STBIO1_MAIN_CONTROLLER_436;IPOS_STBIO1_MAIN_CONTROLLER_5004;IPOS_STBIO1_MAIN_CONTROLLER_5005;IPOS_STBIO1_MAIN_CONTROLLER_5015;IPOS_STBIO1_MAIN_CONTROLLER_5016;IPOS_STBIO1_MAIN_CONTROLLER_5080;IPOS_STBIO1_MAIN_CONTROLLER_5091;IPOS_STBIO1_MAIN_CONTROLLER_5092;IPOS_STBIO1_MAIN_CONTROLLER_6059;IPOS_STBIO1_MAIN_CONTROLLER_6070;IPOS_STBIO1_MAIN_CONTROLLER_6098;IPOS_STBIO1_MAIN_CONTROLLER_6129;IPOS_STBIO1_MAIN_CONTROLLER_7095;IPOS_STBIO1_MAIN_CONTROLLER_7135;IPOS_STBIO1_MAIN_CONTROLLER_728;IPOS_STBIO1_MAIN_CONTROLLER_8106;IPOS_STBIO1_MAIN_CONTROLLER_8116;IPOS_STBIO1_MAIN_CONTROLLER_9116;IPOS_STBIO1_MAIN_CONTROLLER_9139</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Digital_IPOS:sensor-hub</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>source:dds_stbio1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Digital IPOS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Smart FIFO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Primary source specification: dds_stbio1.pdf</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Approved source ledger</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>13</v>
+      </c>
+      <c r="G11" t="n">
+        <v>357</v>
+      </c>
+      <c r="H11" t="n">
+        <v>344</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>3.641456582633054</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Central source-spec provenance/trace ID coverage; not generated-document Covers or publication gate status</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_00000008;DDS_STBIO1_00000102;DDS_STBIO1_00000199;DDS_STBIO1_00000202;DDS_STBIO1_00001199;DDS_STBIO1_89455232;DDS_STBIO1_89455261;DDS_STBIO1_89455449;DDS_STBIO1_89456557;DDS_STBIO1_89456975;DDS_STBIO1_89457435;DDS_STBIO1_89457790;DDS_STBIO1_89459082</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_0013;DDS_STBIO1_0014;DDS_STBIO1_0015;DDS_STBIO1_0016;DDS_STBIO1_0017;DDS_STBIO1_0018;DDS_STBIO1_0019;DDS_STBIO1_0020;DDS_STBIO1_0021;DDS_STBIO1_0022;DDS_STBIO1_0023;DDS_STBIO1_0024;DDS_STBIO1_0025;DDS_STBIO1_0026;DDS_STBIO1_0027;DDS_STBIO1_0028;DDS_STBIO1_0032;DDS_STBIO1_0033;DDS_STBIO1_0034;DDS_STBIO1_0035;DDS_STBIO1_0036;DDS_STBIO1_0104;DDS_STBIO1_0105;DDS_STBIO1_0106;DDS_STBIO1_0107;DDS_STBIO1_0108;DDS_STBIO1_0109;DDS_STBIO1_0110;DDS_STBIO1_0111;DDS_STBIO1_0112;DDS_STBIO1_0113;DDS_STBIO1_0114;DDS_STBIO1_0115;DDS_STBIO1_0116;DDS_STBIO1_0117;DDS_STBIO1_0118;DDS_STBIO1_0119;DDS_STBIO1_0120;DDS_STBIO1_0121;DDS_STBIO1_0122;DDS_STBIO1_0123;DDS_STBIO1_0124;DDS_STBIO1_0125;DDS_STBIO1_0126;DDS_STBIO1_0127;DDS_STBIO1_0128;DDS_STBIO1_0129;DDS_STBIO1_0130;DDS_STBIO1_0140;DDS_STBIO1_0141;DDS_STBIO1_0142;DDS_STBIO1_0143;DDS_STBIO1_0144;DDS_STBIO1_0145;DDS_STBIO1_0146;DDS_STBIO1_0147;DDS_STBIO1_0148;DDS_STBIO1_0149;DDS_STBIO1_0201;DDS_STBIO1_0202;DDS_STBIO1_0203;DDS_STBIO1_0204;DDS_STBIO1_0206;DDS_STBIO1_0207;DDS_STBIO1_0208;DDS_STBIO1_0209;DDS_STBIO1_0210;DDS_STBIO1_0211;DDS_STBIO1_0212;DDS_STBIO1_0213;DDS_STBIO1_0215;DDS_STBIO1_0216;DDS_STBIO1_0217;DDS_STBIO1_0218;DDS_STBIO1_0219;DDS_STBIO1_0220;DDS_STBIO1_0221;DDS_STBIO1_0222;DDS_STBIO1_0223;DDS_STBIO1_0501;DDS_STBIO1_05010;DDS_STBIO1_05011;DDS_STBIO1_0502;DDS_STBIO1_0503;DDS_STBIO1_0504;DDS_STBIO1_0505;DDS_STBIO1_0507;DDS_STBIO1_0508;DDS_STBIO1_0509;DDS_STBIO1_0699;DDS_STBIO1_0700;DDS_STBIO1_0701;DDS_STBIO1_0702;DDS_STBIO1_1020;DDS_STBIO1_1021;DDS_STBIO1_1022;DDS_STBIO1_1023;DDS_STBIO1_1024;DDS_STBIO1_1025;DDS_STBIO1_1026;DDS_STBIO1_1027;DDS_STBIO1_1050;DDS_STBIO1_1051;DDS_STBIO1_1052;DDS_STBIO1_1053;DDS_STBIO1_1054;DDS_STBIO1_1114;DDS_STBIO1_1507;DDS_STBIO1_2024;DDS_STBIO1_2025;DDS_STBIO1_2026;DDS_STBIO1_2052;DDS_STBIO1_2053;DDS_STBIO1_2054;DDS_STBIO1_2507;DDS_STBIO1_3000;DDS_STBIO1_3001;DDS_STBIO1_3002;DDS_STBIO1_3003;DDS_STBIO1_3004;DDS_STBIO1_3005;DDS_STBIO1_3006;DDS_STBIO1_302;DDS_STBIO1_303;DDS_STBIO1_304;DDS_STBIO1_305;DDS_STBIO1_306;DDS_STBIO1_307;DDS_STBIO1_308;DDS_STBIO1_309;DDS_STBIO1_310;DDS_STBIO1_311;DDS_STBIO1_312;DDS_STBIO1_313;DDS_STBIO1_314;DDS_STBIO1_392;DDS_STBIO1_393;DDS_STBIO1_394;DDS_STBIO1_395;DDS_STBIO1_4000;DDS_STBIO1_8000;DDS_STBIO1_8001;DDS_STBIO1_8002;DDS_STBIO1_8003;DDS_STBIO1_8004;DDS_STBIO1_8005;DDS_STBIO1_8006;DDS_STBIO1_8007;DDS_STBIO1_8100;DDS_STBIO1_8101;DDS_STBIO1_8102;DDS_STBIO1_8103;DDS_STBIO1_8104;DDS_STBIO1_8105;DDS_STBIO1_8106;DDS_STBIO1_9004;DDS_STBIO1_9011;DDS_STBIO1_9012;DDS_STBIO1_9013;DDS_STBIO1_9014;DDS_STBIO1_9017;DDS_STBIO1_9018;DDS_STBIO1_9024;DDS_STBIO1_9027;DDS_STBIO1_9029;DDS_STBIO1_9030;DDS_STBIO1_9031;DDS_STBIO1_9032;DDS_STBIO1_9033;DDS_STBIO1_9034;DDS_STBIO1_9035;DDS_STBIO1_9260;DDS_STBIO1_9261;DDS_STBIO1_9262;DDS_STBIO1_9263;DDS_STBIO1_9300;DDS_STBIO1_9317;DDS_STBIO1_9500;IPOS_STBIO1_MAIN_CONTROLLER_002;IPOS_STBIO1_MAIN_CONTROLLER_004;IPOS_STBIO1_MAIN_CONTROLLER_008;IPOS_STBIO1_MAIN_CONTROLLER_009;IPOS_STBIO1_MAIN_CONTROLLER_010;IPOS_STBIO1_MAIN_CONTROLLER_011;IPOS_STBIO1_MAIN_CONTROLLER_015;IPOS_STBIO1_MAIN_CONTROLLER_0152;IPOS_STBIO1_MAIN_CONTROLLER_016;IPOS_STBIO1_MAIN_CONTROLLER_017;IPOS_STBIO1_MAIN_CONTROLLER_018;IPOS_STBIO1_MAIN_CONTROLLER_019;IPOS_STBIO1_MAIN_CONTROLLER_020;IPOS_STBIO1_MAIN_CONTROLLER_021;IPOS_STBIO1_MAIN_CONTROLLER_022;IPOS_STBIO1_MAIN_CONTROLLER_023;IPOS_STBIO1_MAIN_CONTROLLER_024;IPOS_STBIO1_MAIN_CONTROLLER_026;IPOS_STBIO1_MAIN_CONTROLLER_027;IPOS_STBIO1_MAIN_CONTROLLER_028;IPOS_STBIO1_MAIN_CONTROLLER_029;IPOS_STBIO1_MAIN_CONTROLLER_030;IPOS_STBIO1_MAIN_CONTROLLER_031;IPOS_STBIO1_MAIN_CONTROLLER_032;IPOS_STBIO1_MAIN_CONTROLLER_033;IPOS_STBIO1_MAIN_CONTROLLER_034;IPOS_STBIO1_MAIN_CONTROLLER_035;IPOS_STBIO1_MAIN_CONTROLLER_036;IPOS_STBIO1_MAIN_CONTROLLER_037;IPOS_STBIO1_MAIN_CONTROLLER_038;IPOS_STBIO1_MAIN_CONTROLLER_039;IPOS_STBIO1_MAIN_CONTROLLER_040;IPOS_STBIO1_MAIN_CONTROLLER_043;IPOS_STBIO1_MAIN_CONTROLLER_044;IPOS_STBIO1_MAIN_CONTROLLER_045;IPOS_STBIO1_MAIN_CONTROLLER_047;IPOS_STBIO1_MAIN_CONTROLLER_048;IPOS_STBIO1_MAIN_CONTROLLER_049;IPOS_STBIO1_MAIN_CONTROLLER_051;IPOS_STBIO1_MAIN_CONTROLLER_052;IPOS_STBIO1_MAIN_CONTROLLER_053;IPOS_STBIO1_MAIN_CONTROLLER_054;IPOS_STBIO1_MAIN_CONTROLLER_055;IPOS_STBIO1_MAIN_CONTROLLER_058;IPOS_STBIO1_MAIN_CONTROLLER_059;IPOS_STBIO1_MAIN_CONTROLLER_060;IPOS_STBIO1_MAIN_CONTROLLER_061;IPOS_STBIO1_MAIN_CONTROLLER_062;IPOS_STBIO1_MAIN_CONTROLLER_063;IPOS_STBIO1_MAIN_CONTROLLER_064;IPOS_STBIO1_MAIN_CONTROLLER_072;IPOS_STBIO1_MAIN_CONTROLLER_073;IPOS_STBIO1_MAIN_CONTROLLER_074;IPOS_STBIO1_MAIN_CONTROLLER_075;IPOS_STBIO1_MAIN_CONTROLLER_076;IPOS_STBIO1_MAIN_CONTROLLER_077;IPOS_STBIO1_MAIN_CONTROLLER_078;IPOS_STBIO1_MAIN_CONTROLLER_080;IPOS_STBIO1_MAIN_CONTROLLER_081;IPOS_STBIO1_MAIN_CONTROLLER_082;IPOS_STBIO1_MAIN_CONTROLLER_083;IPOS_STBIO1_MAIN_CONTROLLER_084;IPOS_STBIO1_MAIN_CONTROLLER_085;IPOS_STBIO1_MAIN_CONTROLLER_086;IPOS_STBIO1_MAIN_CONTROLLER_087;IPOS_STBIO1_MAIN_CONTROLLER_088;IPOS_STBIO1_MAIN_CONTROLLER_089;IPOS_STBIO1_MAIN_CONTROLLER_090;IPOS_STBIO1_MAIN_CONTROLLER_092;IPOS_STBIO1_MAIN_CONTROLLER_093;IPOS_STBIO1_MAIN_CONTROLLER_094;IPOS_STBIO1_MAIN_CONTROLLER_095;IPOS_STBIO1_MAIN_CONTROLLER_096;IPOS_STBIO1_MAIN_CONTROLLER_097;IPOS_STBIO1_MAIN_CONTROLLER_098;IPOS_STBIO1_MAIN_CONTROLLER_099;IPOS_STBIO1_MAIN_CONTROLLER_100;IPOS_STBIO1_MAIN_CONTROLLER_1004;IPOS_STBIO1_MAIN_CONTROLLER_1005;IPOS_STBIO1_MAIN_CONTROLLER_1007;IPOS_STBIO1_MAIN_CONTROLLER_1008;IPOS_STBIO1_MAIN_CONTROLLER_1009;IPOS_STBIO1_MAIN_CONTROLLER_101;IPOS_STBIO1_MAIN_CONTROLLER_1010;IPOS_STBIO1_MAIN_CONTROLLER_1011;IPOS_STBIO1_MAIN_CONTROLLER_102;IPOS_STBIO1_MAIN_CONTROLLER_103;IPOS_STBIO1_MAIN_CONTROLLER_1034;IPOS_STBIO1_MAIN_CONTROLLER_104;IPOS_STBIO1_MAIN_CONTROLLER_105;IPOS_STBIO1_MAIN_CONTROLLER_106;IPOS_STBIO1_MAIN_CONTROLLER_107;IPOS_STBIO1_MAIN_CONTROLLER_108;IPOS_STBIO1_MAIN_CONTROLLER_109;IPOS_STBIO1_MAIN_CONTROLLER_1095;IPOS_STBIO1_MAIN_CONTROLLER_110;IPOS_STBIO1_MAIN_CONTROLLER_1102;IPOS_STBIO1_MAIN_CONTROLLER_1104;IPOS_STBIO1_MAIN_CONTROLLER_1105;IPOS_STBIO1_MAIN_CONTROLLER_111;IPOS_STBIO1_MAIN_CONTROLLER_1116;IPOS_STBIO1_MAIN_CONTROLLER_1118;IPOS_STBIO1_MAIN_CONTROLLER_1119;IPOS_STBIO1_MAIN_CONTROLLER_112;IPOS_STBIO1_MAIN_CONTROLLER_113;IPOS_STBIO1_MAIN_CONTROLLER_1136;IPOS_STBIO1_MAIN_CONTROLLER_1139;IPOS_STBIO1_MAIN_CONTROLLER_1143;IPOS_STBIO1_MAIN_CONTROLLER_115;IPOS_STBIO1_MAIN_CONTROLLER_118;IPOS_STBIO1_MAIN_CONTROLLER_120;IPOS_STBIO1_MAIN_CONTROLLER_121;IPOS_STBIO1_MAIN_CONTROLLER_122;IPOS_STBIO1_MAIN_CONTROLLER_123;IPOS_STBIO1_MAIN_CONTROLLER_124;IPOS_STBIO1_MAIN_CONTROLLER_125;IPOS_STBIO1_MAIN_CONTROLLER_126;IPOS_STBIO1_MAIN_CONTROLLER_127;IPOS_STBIO1_MAIN_CONTROLLER_128;IPOS_STBIO1_MAIN_CONTROLLER_129;IPOS_STBIO1_MAIN_CONTROLLER_132;IPOS_STBIO1_MAIN_CONTROLLER_133;IPOS_STBIO1_MAIN_CONTROLLER_134;IPOS_STBIO1_MAIN_CONTROLLER_137;IPOS_STBIO1_MAIN_CONTROLLER_138;IPOS_STBIO1_MAIN_CONTROLLER_139;IPOS_STBIO1_MAIN_CONTROLLER_140;IPOS_STBIO1_MAIN_CONTROLLER_143;IPOS_STBIO1_MAIN_CONTROLLER_2117;IPOS_STBIO1_MAIN_CONTROLLER_2143;IPOS_STBIO1_MAIN_CONTROLLER_2144;IPOS_STBIO1_MAIN_CONTROLLER_2145;IPOS_STBIO1_MAIN_CONTROLLER_2146;IPOS_STBIO1_MAIN_CONTROLLER_300;IPOS_STBIO1_MAIN_CONTROLLER_3124;IPOS_STBIO1_MAIN_CONTROLLER_3125;IPOS_STBIO1_MAIN_CONTROLLER_3126;IPOS_STBIO1_MAIN_CONTROLLER_3127;IPOS_STBIO1_MAIN_CONTROLLER_3128;IPOS_STBIO1_MAIN_CONTROLLER_3129;IPOS_STBIO1_MAIN_CONTROLLER_3130;IPOS_STBIO1_MAIN_CONTROLLER_3131;IPOS_STBIO1_MAIN_CONTROLLER_4034;IPOS_STBIO1_MAIN_CONTROLLER_4079;IPOS_STBIO1_MAIN_CONTROLLER_4080;IPOS_STBIO1_MAIN_CONTROLLER_4090;IPOS_STBIO1_MAIN_CONTROLLER_4091;IPOS_STBIO1_MAIN_CONTROLLER_436;IPOS_STBIO1_MAIN_CONTROLLER_5004;IPOS_STBIO1_MAIN_CONTROLLER_5005;IPOS_STBIO1_MAIN_CONTROLLER_5015;IPOS_STBIO1_MAIN_CONTROLLER_5016;IPOS_STBIO1_MAIN_CONTROLLER_5080;IPOS_STBIO1_MAIN_CONTROLLER_5091;IPOS_STBIO1_MAIN_CONTROLLER_5092;IPOS_STBIO1_MAIN_CONTROLLER_6059;IPOS_STBIO1_MAIN_CONTROLLER_6070;IPOS_STBIO1_MAIN_CONTROLLER_6098;IPOS_STBIO1_MAIN_CONTROLLER_6129;IPOS_STBIO1_MAIN_CONTROLLER_7095;IPOS_STBIO1_MAIN_CONTROLLER_7135;IPOS_STBIO1_MAIN_CONTROLLER_728;IPOS_STBIO1_MAIN_CONTROLLER_8106;IPOS_STBIO1_MAIN_CONTROLLER_8116;IPOS_STBIO1_MAIN_CONTROLLER_9116;IPOS_STBIO1_MAIN_CONTROLLER_9139</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Digital_IPOS:smart-fifo</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>source:dds_stbio1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Supplementary specification: IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Primary source specification: dds_stbio1.pdf</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Approved source ledger</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>166</v>
+      </c>
+      <c r="G12" t="n">
+        <v>357</v>
+      </c>
+      <c r="H12" t="n">
+        <v>191</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>46.49859943977591</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Central source-spec provenance/trace ID coverage; not generated-document Covers or publication gate status</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_002;IPOS_STBIO1_MAIN_CONTROLLER_004;IPOS_STBIO1_MAIN_CONTROLLER_008;IPOS_STBIO1_MAIN_CONTROLLER_009;IPOS_STBIO1_MAIN_CONTROLLER_010;IPOS_STBIO1_MAIN_CONTROLLER_011;IPOS_STBIO1_MAIN_CONTROLLER_015;IPOS_STBIO1_MAIN_CONTROLLER_0152;IPOS_STBIO1_MAIN_CONTROLLER_016;IPOS_STBIO1_MAIN_CONTROLLER_017;IPOS_STBIO1_MAIN_CONTROLLER_018;IPOS_STBIO1_MAIN_CONTROLLER_019;IPOS_STBIO1_MAIN_CONTROLLER_020;IPOS_STBIO1_MAIN_CONTROLLER_021;IPOS_STBIO1_MAIN_CONTROLLER_022;IPOS_STBIO1_MAIN_CONTROLLER_023;IPOS_STBIO1_MAIN_CONTROLLER_024;IPOS_STBIO1_MAIN_CONTROLLER_026;IPOS_STBIO1_MAIN_CONTROLLER_027;IPOS_STBIO1_MAIN_CONTROLLER_028;IPOS_STBIO1_MAIN_CONTROLLER_029;IPOS_STBIO1_MAIN_CONTROLLER_030;IPOS_STBIO1_MAIN_CONTROLLER_031;IPOS_STBIO1_MAIN_CONTROLLER_032;IPOS_STBIO1_MAIN_CONTROLLER_033;IPOS_STBIO1_MAIN_CONTROLLER_034;IPOS_STBIO1_MAIN_CONTROLLER_035;IPOS_STBIO1_MAIN_CONTROLLER_036;IPOS_STBIO1_MAIN_CONTROLLER_037;IPOS_STBIO1_MAIN_CONTROLLER_038;IPOS_STBIO1_MAIN_CONTROLLER_039;IPOS_STBIO1_MAIN_CONTROLLER_040;IPOS_STBIO1_MAIN_CONTROLLER_043;IPOS_STBIO1_MAIN_CONTROLLER_044;IPOS_STBIO1_MAIN_CONTROLLER_045;IPOS_STBIO1_MAIN_CONTROLLER_047;IPOS_STBIO1_MAIN_CONTROLLER_048;IPOS_STBIO1_MAIN_CONTROLLER_049;IPOS_STBIO1_MAIN_CONTROLLER_051;IPOS_STBIO1_MAIN_CONTROLLER_052;IPOS_STBIO1_MAIN_CONTROLLER_053;IPOS_STBIO1_MAIN_CONTROLLER_054;IPOS_STBIO1_MAIN_CONTROLLER_055;IPOS_STBIO1_MAIN_CONTROLLER_058;IPOS_STBIO1_MAIN_CONTROLLER_059;IPOS_STBIO1_MAIN_CONTROLLER_060;IPOS_STBIO1_MAIN_CONTROLLER_061;IPOS_STBIO1_MAIN_CONTROLLER_062;IPOS_STBIO1_MAIN_CONTROLLER_063;IPOS_STBIO1_MAIN_CONTROLLER_064;IPOS_STBIO1_MAIN_CONTROLLER_072;IPOS_STBIO1_MAIN_CONTROLLER_073;IPOS_STBIO1_MAIN_CONTROLLER_074;IPOS_STBIO1_MAIN_CONTROLLER_075;IPOS_STBIO1_MAIN_CONTROLLER_076;IPOS_STBIO1_MAIN_CONTROLLER_077;IPOS_STBIO1_MAIN_CONTROLLER_078;IPOS_STBIO1_MAIN_CONTROLLER_080;IPOS_STBIO1_MAIN_CONTROLLER_081;IPOS_STBIO1_MAIN_CONTROLLER_082;IPOS_STBIO1_MAIN_CONTROLLER_083;IPOS_STBIO1_MAIN_CONTROLLER_084;IPOS_STBIO1_MAIN_CONTROLLER_085;IPOS_STBIO1_MAIN_CONTROLLER_086;IPOS_STBIO1_MAIN_CONTROLLER_087;IPOS_STBIO1_MAIN_CONTROLLER_088;IPOS_STBIO1_MAIN_CONTROLLER_089;IPOS_STBIO1_MAIN_CONTROLLER_090;IPOS_STBIO1_MAIN_CONTROLLER_092;IPOS_STBIO1_MAIN_CONTROLLER_093;IPOS_STBIO1_MAIN_CONTROLLER_094;IPOS_STBIO1_MAIN_CONTROLLER_095;IPOS_STBIO1_MAIN_CONTROLLER_096;IPOS_STBIO1_MAIN_CONTROLLER_097;IPOS_STBIO1_MAIN_CONTROLLER_098;IPOS_STBIO1_MAIN_CONTROLLER_099;IPOS_STBIO1_MAIN_CONTROLLER_100;IPOS_STBIO1_MAIN_CONTROLLER_1004;IPOS_STBIO1_MAIN_CONTROLLER_1005;IPOS_STBIO1_MAIN_CONTROLLER_1007;IPOS_STBIO1_MAIN_CONTROLLER_1008;IPOS_STBIO1_MAIN_CONTROLLER_1009;IPOS_STBIO1_MAIN_CONTROLLER_101;IPOS_STBIO1_MAIN_CONTROLLER_1010;IPOS_STBIO1_MAIN_CONTROLLER_1011;IPOS_STBIO1_MAIN_CONTROLLER_102;IPOS_STBIO1_MAIN_CONTROLLER_103;IPOS_STBIO1_MAIN_CONTROLLER_1034;IPOS_STBIO1_MAIN_CONTROLLER_104;IPOS_STBIO1_MAIN_CONTROLLER_105;IPOS_STBIO1_MAIN_CONTROLLER_106;IPOS_STBIO1_MAIN_CONTROLLER_107;IPOS_STBIO1_MAIN_CONTROLLER_108;IPOS_STBIO1_MAIN_CONTROLLER_109;IPOS_STBIO1_MAIN_CONTROLLER_1095;IPOS_STBIO1_MAIN_CONTROLLER_110;IPOS_STBIO1_MAIN_CONTROLLER_1102;IPOS_STBIO1_MAIN_CONTROLLER_1104;IPOS_STBIO1_MAIN_CONTROLLER_1105;IPOS_STBIO1_MAIN_CONTROLLER_111;IPOS_STBIO1_MAIN_CONTROLLER_1116;IPOS_STBIO1_MAIN_CONTROLLER_1118;IPOS_STBIO1_MAIN_CONTROLLER_1119;IPOS_STBIO1_MAIN_CONTROLLER_112;IPOS_STBIO1_MAIN_CONTROLLER_113;IPOS_STBIO1_MAIN_CONTROLLER_1136;IPOS_STBIO1_MAIN_CONTROLLER_1139;IPOS_STBIO1_MAIN_CONTROLLER_1143;IPOS_STBIO1_MAIN_CONTROLLER_115;IPOS_STBIO1_MAIN_CONTROLLER_118;IPOS_STBIO1_MAIN_CONTROLLER_120;IPOS_STBIO1_MAIN_CONTROLLER_121;IPOS_STBIO1_MAIN_CONTROLLER_122;IPOS_STBIO1_MAIN_CONTROLLER_123;IPOS_STBIO1_MAIN_CONTROLLER_124;IPOS_STBIO1_MAIN_CONTROLLER_125;IPOS_STBIO1_MAIN_CONTROLLER_126;IPOS_STBIO1_MAIN_CONTROLLER_127;IPOS_STBIO1_MAIN_CONTROLLER_128;IPOS_STBIO1_MAIN_CONTROLLER_129;IPOS_STBIO1_MAIN_CONTROLLER_132;IPOS_STBIO1_MAIN_CONTROLLER_133;IPOS_STBIO1_MAIN_CONTROLLER_134;IPOS_STBIO1_MAIN_CONTROLLER_137;IPOS_STBIO1_MAIN_CONTROLLER_138;IPOS_STBIO1_MAIN_CONTROLLER_139;IPOS_STBIO1_MAIN_CONTROLLER_140;IPOS_STBIO1_MAIN_CONTROLLER_143;IPOS_STBIO1_MAIN_CONTROLLER_2117;IPOS_STBIO1_MAIN_CONTROLLER_2143;IPOS_STBIO1_MAIN_CONTROLLER_2144;IPOS_STBIO1_MAIN_CONTROLLER_2145;IPOS_STBIO1_MAIN_CONTROLLER_2146;IPOS_STBIO1_MAIN_CONTROLLER_300;IPOS_STBIO1_MAIN_CONTROLLER_3124;IPOS_STBIO1_MAIN_CONTROLLER_3125;IPOS_STBIO1_MAIN_CONTROLLER_3126;IPOS_STBIO1_MAIN_CONTROLLER_3127;IPOS_STBIO1_MAIN_CONTROLLER_3128;IPOS_STBIO1_MAIN_CONTROLLER_3129;IPOS_STBIO1_MAIN_CONTROLLER_3130;IPOS_STBIO1_MAIN_CONTROLLER_3131;IPOS_STBIO1_MAIN_CONTROLLER_4034;IPOS_STBIO1_MAIN_CONTROLLER_4079;IPOS_STBIO1_MAIN_CONTROLLER_4080;IPOS_STBIO1_MAIN_CONTROLLER_4090;IPOS_STBIO1_MAIN_CONTROLLER_4091;IPOS_STBIO1_MAIN_CONTROLLER_436;IPOS_STBIO1_MAIN_CONTROLLER_5004;IPOS_STBIO1_MAIN_CONTROLLER_5005;IPOS_STBIO1_MAIN_CONTROLLER_5015;IPOS_STBIO1_MAIN_CONTROLLER_5016;IPOS_STBIO1_MAIN_CONTROLLER_5080;IPOS_STBIO1_MAIN_CONTROLLER_5091;IPOS_STBIO1_MAIN_CONTROLLER_5092;IPOS_STBIO1_MAIN_CONTROLLER_6059;IPOS_STBIO1_MAIN_CONTROLLER_6070;IPOS_STBIO1_MAIN_CONTROLLER_6098;IPOS_STBIO1_MAIN_CONTROLLER_6129;IPOS_STBIO1_MAIN_CONTROLLER_7095;IPOS_STBIO1_MAIN_CONTROLLER_7135;IPOS_STBIO1_MAIN_CONTROLLER_728;IPOS_STBIO1_MAIN_CONTROLLER_8106;IPOS_STBIO1_MAIN_CONTROLLER_8116;IPOS_STBIO1_MAIN_CONTROLLER_9116;IPOS_STBIO1_MAIN_CONTROLLER_9139</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_00000008;DDS_STBIO1_00000102;DDS_STBIO1_00000199;DDS_STBIO1_00000202;DDS_STBIO1_00001199;DDS_STBIO1_0013;DDS_STBIO1_0014;DDS_STBIO1_0015;DDS_STBIO1_0016;DDS_STBIO1_0017;DDS_STBIO1_0018;DDS_STBIO1_0019;DDS_STBIO1_0020;DDS_STBIO1_0021;DDS_STBIO1_0022;DDS_STBIO1_0023;DDS_STBIO1_0024;DDS_STBIO1_0025;DDS_STBIO1_0026;DDS_STBIO1_0027;DDS_STBIO1_0028;DDS_STBIO1_0032;DDS_STBIO1_0033;DDS_STBIO1_0034;DDS_STBIO1_0035;DDS_STBIO1_0036;DDS_STBIO1_0104;DDS_STBIO1_0105;DDS_STBIO1_0106;DDS_STBIO1_0107;DDS_STBIO1_0108;DDS_STBIO1_0109;DDS_STBIO1_0110;DDS_STBIO1_0111;DDS_STBIO1_0112;DDS_STBIO1_0113;DDS_STBIO1_0114;DDS_STBIO1_0115;DDS_STBIO1_0116;DDS_STBIO1_0117;DDS_STBIO1_0118;DDS_STBIO1_0119;DDS_STBIO1_0120;DDS_STBIO1_0121;DDS_STBIO1_0122;DDS_STBIO1_0123;DDS_STBIO1_0124;DDS_STBIO1_0125;DDS_STBIO1_0126;DDS_STBIO1_0127;DDS_STBIO1_0128;DDS_STBIO1_0129;DDS_STBIO1_0130;DDS_STBIO1_0140;DDS_STBIO1_0141;DDS_STBIO1_0142;DDS_STBIO1_0143;DDS_STBIO1_0144;DDS_STBIO1_0145;DDS_STBIO1_0146;DDS_STBIO1_0147;DDS_STBIO1_0148;DDS_STBIO1_0149;DDS_STBIO1_0201;DDS_STBIO1_0202;DDS_STBIO1_0203;DDS_STBIO1_0204;DDS_STBIO1_0206;DDS_STBIO1_0207;DDS_STBIO1_0208;DDS_STBIO1_0209;DDS_STBIO1_0210;DDS_STBIO1_0211;DDS_STBIO1_0212;DDS_STBIO1_0213;DDS_STBIO1_0215;DDS_STBIO1_0216;DDS_STBIO1_0217;DDS_STBIO1_0218;DDS_STBIO1_0219;DDS_STBIO1_0220;DDS_STBIO1_0221;DDS_STBIO1_0222;DDS_STBIO1_0223;DDS_STBIO1_0501;DDS_STBIO1_05010;DDS_STBIO1_05011;DDS_STBIO1_0502;DDS_STBIO1_0503;DDS_STBIO1_0504;DDS_STBIO1_0505;DDS_STBIO1_0507;DDS_STBIO1_0508;DDS_STBIO1_0509;DDS_STBIO1_0699;DDS_STBIO1_0700;DDS_STBIO1_0701;DDS_STBIO1_0702;DDS_STBIO1_1020;DDS_STBIO1_1021;DDS_STBIO1_1022;DDS_STBIO1_1023;DDS_STBIO1_1024;DDS_STBIO1_1025;DDS_STBIO1_1026;DDS_STBIO1_1027;DDS_STBIO1_1050;DDS_STBIO1_1051;DDS_STBIO1_1052;DDS_STBIO1_1053;DDS_STBIO1_1054;DDS_STBIO1_1114;DDS_STBIO1_1507;DDS_STBIO1_2024;DDS_STBIO1_2025;DDS_STBIO1_2026;DDS_STBIO1_2052;DDS_STBIO1_2053;DDS_STBIO1_2054;DDS_STBIO1_2507;DDS_STBIO1_3000;DDS_STBIO1_3001;DDS_STBIO1_3002;DDS_STBIO1_3003;DDS_STBIO1_3004;DDS_STBIO1_3005;DDS_STBIO1_3006;DDS_STBIO1_302;DDS_STBIO1_303;DDS_STBIO1_304;DDS_STBIO1_305;DDS_STBIO1_306;DDS_STBIO1_307;DDS_STBIO1_308;DDS_STBIO1_309;DDS_STBIO1_310;DDS_STBIO1_311;DDS_STBIO1_312;DDS_STBIO1_313;DDS_STBIO1_314;DDS_STBIO1_392;DDS_STBIO1_393;DDS_STBIO1_394;DDS_STBIO1_395;DDS_STBIO1_4000;DDS_STBIO1_8000;DDS_STBIO1_8001;DDS_STBIO1_8002;DDS_STBIO1_8003;DDS_STBIO1_8004;DDS_STBIO1_8005;DDS_STBIO1_8006;DDS_STBIO1_8007;DDS_STBIO1_8100;DDS_STBIO1_8101;DDS_STBIO1_8102;DDS_STBIO1_8103;DDS_STBIO1_8104;DDS_STBIO1_8105;DDS_STBIO1_8106;DDS_STBIO1_89455232;DDS_STBIO1_89455261;DDS_STBIO1_89455449;DDS_STBIO1_89456557;DDS_STBIO1_89456975;DDS_STBIO1_89457435;DDS_STBIO1_89457790;DDS_STBIO1_89459082;DDS_STBIO1_9004;DDS_STBIO1_9011;DDS_STBIO1_9012;DDS_STBIO1_9013;DDS_STBIO1_9014;DDS_STBIO1_9017;DDS_STBIO1_9018;DDS_STBIO1_9024;DDS_STBIO1_9027;DDS_STBIO1_9029;DDS_STBIO1_9030;DDS_STBIO1_9031;DDS_STBIO1_9032;DDS_STBIO1_9033;DDS_STBIO1_9034;DDS_STBIO1_9035;DDS_STBIO1_9260;DDS_STBIO1_9261;DDS_STBIO1_9262;DDS_STBIO1_9263;DDS_STBIO1_9300;DDS_STBIO1_9317;DDS_STBIO1_9500</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>supplementary:ipos_main_ctrl.pdf</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>source:dds_stbio1.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="31" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>hierarchy_level</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>block</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>expected_requirements</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>represented_requirements</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>missing_requirements</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>presence_percentage</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>presence_status</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_basis</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>missing_requirement_ids</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>snapshot_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Source Spec Integrated Requirements</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Catalog total</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>357</v>
+      </c>
+      <c r="E2" t="n">
+        <v>191</v>
+      </c>
+      <c r="F2" t="n">
+        <v>166</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>53.50140056022409</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Source catalog IDs present in approved snapshot; not publication gate status</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_002;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_004;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_008;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_009;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_010;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_011;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_0152;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_016;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_017;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_018;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_019;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_021;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_023;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_024;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_026;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_028;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_029;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_030;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_031;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_032;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_033;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_034;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_035;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_036;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_037;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_038;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_039;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_044;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_045;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_047;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_049;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_051;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_052;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_053;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_054;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_055;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_058;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_059;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_060;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_061;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_062;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_063;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_064;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_073;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_074;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_077;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_078;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_080;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_082;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_083;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_085;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_087;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_088;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_089;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_092;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_093;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_094;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_095;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_096;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_098;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_099;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_100;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_1004;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_1005;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_1007;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_1008;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_1009;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_101;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_1010;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_1011;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_102;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_103;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_1034;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_104;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_105;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_106;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_108;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_109;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_1095;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_110;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_1102;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_1104;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_111;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_1116;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_112;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_113;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_1139;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_1143;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_115;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_118;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_120;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_126;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_128;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_134;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_137;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_138;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_140;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_2143;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_2144;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_2145;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_2146;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_3124;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_3125;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_3126;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_3127;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_3128;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_3129;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_4079;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_4080;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_4090;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_4091;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_436;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_5004;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_5005;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_5015;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_5016;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_5092;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_6070;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_6098;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_6129;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_7095;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_728;ipos_main_ctrl_20260907_171517:IPOS_STBIO1_MAIN_CONTROLLER_8106;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_015;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_020;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_022;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_027;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_040;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_043;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_048;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_072;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_075;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_076;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_081;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_084;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_086;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_090;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_097;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_107;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_1105;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_1118;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_1119;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_1136;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_121;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_122;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_123;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_124;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_125;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_127;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_129;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_132;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_133;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_139;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_143;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_2117;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_300;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_3130;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_3131;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_4034;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_5080;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_5091;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_6059;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_7135;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_8116;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_9116;ipos_main_ctrl_20260921_143819:IPOS_STBIO1_MAIN_CONTROLLER_9139</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>